--- a/test_predictions.xlsx
+++ b/test_predictions.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f113.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f113.jpeg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,25 +475,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05559999868273735</v>
+        <v>0.05389999970793724</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2124000042676926</v>
+        <v>0.2470999956130981</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4180000126361847</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2770000100135803</v>
+        <v>0.1978999972343445</v>
       </c>
       <c r="H2" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a2.jpg</t>
+          <t>c:\ML_Project\test\Angry\new_a2.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,25 +507,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.06700000166893005</v>
+        <v>0.08940000087022781</v>
       </c>
       <c r="E3" t="n">
-        <v>0.066600002348423</v>
+        <v>0.1588000059127808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6873000264167786</v>
+        <v>0.4891999959945679</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2185000032186508</v>
+        <v>0.2337999939918518</v>
       </c>
       <c r="H3" t="n">
-        <v>35.4</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a36.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a36.jpeg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -539,25 +539,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2640999853610992</v>
+        <v>0.3149999976158142</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1093999966979027</v>
+        <v>0.2234999984502792</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1600999981164932</v>
+        <v>0.1524000018835068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3966000080108643</v>
+        <v>0.3621000051498413</v>
       </c>
       <c r="H4" t="n">
-        <v>52.3</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f103.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f103.jpeg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,16 +571,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03070000000298023</v>
+        <v>0.04919999837875366</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1645999997854233</v>
+        <v>0.2676999866962433</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2366999983787537</v>
+        <v>0.2648000121116638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.449099987745285</v>
+        <v>0.3143999874591827</v>
       </c>
       <c r="H5" t="n">
         <v>35.6</v>
@@ -589,7 +589,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a66.jpg</t>
+          <t>c:\ML_Project\test\Angry\a66.jpg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -603,16 +603,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02659999951720238</v>
+        <v>0.03209999948740005</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04329999908804893</v>
+        <v>0.04780000075697899</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8596000075340271</v>
+        <v>0.9054999947547913</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0738999992609024</v>
+        <v>0.0333000011742115</v>
       </c>
       <c r="H6" t="n">
         <v>32.2</v>
@@ -621,7 +621,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h25.jpg</t>
+          <t>c:\ML_Project\test\Happy\h25.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4745000004768372</v>
+        <v>0.3707000017166138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2178999930620193</v>
+        <v>0.2529000043869019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06030000001192093</v>
+        <v>0.1492000073194504</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1321000009775162</v>
+        <v>0.1636999994516373</v>
       </c>
       <c r="H7" t="n">
-        <v>66.40000000000001</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f71.jpg</t>
+          <t>c:\ML_Project\test\Fear\f71.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -667,25 +667,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1779000014066696</v>
+        <v>0.3361000120639801</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1186999976634979</v>
+        <v>0.130500003695488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1266999989748001</v>
+        <v>0.2016000002622604</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4072000086307526</v>
+        <v>0.2496999949216843</v>
       </c>
       <c r="H8" t="n">
-        <v>47.3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f93.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f93.jpeg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01590000092983246</v>
+        <v>0.03400000184774399</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5094000101089478</v>
+        <v>0.3059000074863434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06650000065565109</v>
+        <v>0.1105000004172325</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3869999945163727</v>
+        <v>0.5080000162124634</v>
       </c>
       <c r="H9" t="n">
-        <v>31</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h46.jpg</t>
+          <t>c:\ML_Project\test\Happy\h46.jpg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,25 +731,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.820900022983551</v>
+        <v>0.8421000242233276</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06030000001192093</v>
+        <v>0.07940000295639038</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06780000030994415</v>
+        <v>0.1121999993920326</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05539999902248383</v>
+        <v>0.08579999953508377</v>
       </c>
       <c r="H10" t="n">
-        <v>88.7</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a86.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a86.jpeg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -763,25 +763,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02400000020861626</v>
+        <v>0.05579999834299088</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05290000140666962</v>
+        <v>0.1678999960422516</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8489000201225281</v>
+        <v>0.6574000120162964</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05640000104904175</v>
+        <v>0.09040000289678574</v>
       </c>
       <c r="H11" t="n">
-        <v>32.2</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h76.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h76.jpeg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8648999929428101</v>
+        <v>0.7445999979972839</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08780000358819962</v>
+        <v>0.1596000045537949</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01620000042021275</v>
+        <v>0.02539999969303608</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06430000066757202</v>
+        <v>0.1429000049829483</v>
       </c>
       <c r="H12" t="n">
-        <v>91.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s62.jpg</t>
+          <t>c:\ML_Project\test\Sad\s62.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -827,25 +827,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0255999993532896</v>
+        <v>0.01970000006258488</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7833999991416931</v>
+        <v>0.7943999767303467</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1377000063657761</v>
+        <v>0.06580000370740891</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1386000066995621</v>
+        <v>0.1993000060319901</v>
       </c>
       <c r="H13" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f90.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f90.jpeg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -859,25 +859,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01940000057220459</v>
+        <v>0.07490000128746033</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09210000187158585</v>
+        <v>0.1414999961853027</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08869999647140503</v>
+        <v>0.2454999983310699</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8015000224113464</v>
+        <v>0.6360999941825867</v>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f18.jpg</t>
+          <t>c:\ML_Project\test\Fear\f18.jpg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.0786999985575676</v>
+        <v>0.04899999871850014</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1571000069379807</v>
+        <v>0.1994999945163727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.286300003528595</v>
+        <v>0.1692000031471252</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5922999978065491</v>
+        <v>0.5539000034332275</v>
       </c>
       <c r="H15" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a88.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a88.jpeg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.05939999967813492</v>
+        <v>0.1023999974131584</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1307999938726425</v>
+        <v>0.1040000021457672</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4708999991416931</v>
+        <v>0.7547000050544739</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3935000002384186</v>
+        <v>0.09570000320672989</v>
       </c>
       <c r="H16" t="n">
-        <v>35.1</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s24.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s24.jpeg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -955,25 +955,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1583999991416931</v>
+        <v>0.1220000013709068</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3815000057220459</v>
+        <v>0.2971999943256378</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1962999999523163</v>
+        <v>0.35589998960495</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2430000007152557</v>
+        <v>0.2948000133037567</v>
       </c>
       <c r="H17" t="n">
-        <v>41.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f89.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f89.jpeg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -987,25 +987,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02089999988675117</v>
+        <v>0.02690000087022781</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6176000237464905</v>
+        <v>0.6812000274658203</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02480000071227551</v>
+        <v>0.01640000008046627</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3925999999046326</v>
+        <v>0.4954000115394592</v>
       </c>
       <c r="H18" t="n">
-        <v>29.7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h51.jpg</t>
+          <t>c:\ML_Project\test\Happy\h51.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1019,25 +1019,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9628999829292297</v>
+        <v>0.9318000078201294</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02160000056028366</v>
+        <v>0.02459999918937683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02630000002682209</v>
+        <v>0.0414000004529953</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01899999938905239</v>
+        <v>0.02449999935925007</v>
       </c>
       <c r="H19" t="n">
-        <v>97.5</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s10.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s10.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1051,25 +1051,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.7993000149726868</v>
+        <v>0.7537000179290771</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09489999711513519</v>
+        <v>0.1099999994039536</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06140000000596046</v>
+        <v>0.08429999649524689</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07020000368356705</v>
+        <v>0.07819999754428864</v>
       </c>
       <c r="H20" t="n">
-        <v>87.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f45.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f45.jpeg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1083,25 +1083,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.02429999969899654</v>
+        <v>0.02859999984502792</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3273999989032745</v>
+        <v>0.2224999964237213</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3136999905109406</v>
+        <v>0.2928000092506409</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2800000011920929</v>
+        <v>0.3452000021934509</v>
       </c>
       <c r="H21" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h55.jpg</t>
+          <t>c:\ML_Project\test\Happy\h55.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1115,25 +1115,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9526000022888184</v>
+        <v>0.9276999831199646</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0296000000089407</v>
+        <v>0.04980000108480453</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02999999932944775</v>
+        <v>0.02180000022053719</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01850000023841858</v>
+        <v>0.04010000079870224</v>
       </c>
       <c r="H22" t="n">
-        <v>96.90000000000001</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s64.jpg</t>
+          <t>c:\ML_Project\test\Sad\s64.jpg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1147,25 +1147,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0142000000923872</v>
+        <v>0.03970000147819519</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8920999765396118</v>
+        <v>0.4086999893188477</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04320000112056732</v>
+        <v>0.1923000067472458</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0625</v>
+        <v>0.3170000016689301</v>
       </c>
       <c r="H23" t="n">
-        <v>26.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s26.jpg</t>
+          <t>c:\ML_Project\test\Sad\s26.jpg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1179,25 +1179,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2937000095844269</v>
+        <v>0.1518000066280365</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1835999935865402</v>
+        <v>0.4496999979019165</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2414000034332275</v>
+        <v>0.3145999908447266</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2725000083446503</v>
+        <v>0.1105000004172325</v>
       </c>
       <c r="H24" t="n">
-        <v>52.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s34.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s34.jpeg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1211,25 +1211,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1781000047922134</v>
+        <v>0.1437000036239624</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3240000009536743</v>
+        <v>0.5530999898910522</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02319999970495701</v>
+        <v>0.03229999914765358</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3393000066280365</v>
+        <v>0.258899986743927</v>
       </c>
       <c r="H25" t="n">
-        <v>45.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h64.jpg</t>
+          <t>c:\ML_Project\test\Happy\h64.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6251999735832214</v>
+        <v>0.445499986410141</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07660000026226044</v>
+        <v>0.1200999990105629</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1120000034570694</v>
+        <v>0.1659999936819077</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1510999947786331</v>
+        <v>0.2703999876976013</v>
       </c>
       <c r="H26" t="n">
-        <v>76.40000000000001</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a40.jpg</t>
+          <t>c:\ML_Project\test\Angry\a40.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1275,25 +1275,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.2788000106811523</v>
+        <v>0.1868000030517578</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1280999928712845</v>
+        <v>0.1703999936580658</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4410000145435333</v>
+        <v>0.5694000124931335</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04809999838471413</v>
+        <v>0.08470000326633453</v>
       </c>
       <c r="H27" t="n">
-        <v>52.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h5.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h5.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7648000121116638</v>
+        <v>0.4172999858856201</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02610000036656857</v>
+        <v>0.1541000008583069</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1805000007152557</v>
+        <v>0.3998999893665314</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08209999650716782</v>
+        <v>0.07639999687671661</v>
       </c>
       <c r="H28" t="n">
-        <v>84.90000000000001</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s4.jpg</t>
+          <t>c:\ML_Project\test\Sad\s4.jpg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.02910000085830688</v>
+        <v>0.06350000202655792</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7300999760627747</v>
+        <v>0.760699987411499</v>
       </c>
       <c r="F29" t="n">
-        <v>0.129600003361702</v>
+        <v>0.1230000033974648</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08990000188350677</v>
+        <v>0.0966000035405159</v>
       </c>
       <c r="H29" t="n">
-        <v>29.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h75.jpg</t>
+          <t>c:\ML_Project\test\Happy\h75.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9535999894142151</v>
+        <v>0.9575999975204468</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02209999971091747</v>
+        <v>0.01439999975264072</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03730000182986259</v>
+        <v>0.01720000058412552</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02740000002086163</v>
+        <v>0.01970000006258488</v>
       </c>
       <c r="H30" t="n">
-        <v>96.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s2.jpg</t>
+          <t>c:\ML_Project\test\Sad\s2.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1403,25 +1403,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.02129999920725822</v>
+        <v>0.04399999976158142</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8429999947547913</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02160000056028366</v>
+        <v>0.07199999690055847</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1809999942779541</v>
+        <v>0.2047999948263168</v>
       </c>
       <c r="H31" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a24.jpg</t>
+          <t>c:\ML_Project\test\Angry\a24.jpg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1435,25 +1435,25 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.04899999871850014</v>
+        <v>0.07150000333786011</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09049999713897705</v>
+        <v>0.06459999829530716</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8055999875068665</v>
+        <v>0.8319000005722046</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1020999997854233</v>
+        <v>0.101000003516674</v>
       </c>
       <c r="H32" t="n">
-        <v>33.2</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s71.jpg</t>
+          <t>c:\ML_Project\test\Sad\s71.jpg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1467,25 +1467,25 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.03089999966323376</v>
+        <v>0.02969999983906746</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1641000062227249</v>
+        <v>0.06639999896287918</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1671999990940094</v>
+        <v>0.05719999969005585</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5976999998092651</v>
+        <v>0.8554999828338623</v>
       </c>
       <c r="H33" t="n">
-        <v>35.1</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s35.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s35.jpeg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1499,25 +1499,25 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.03119999915361404</v>
+        <v>0.04250000044703484</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2874000072479248</v>
+        <v>0.3901999890804291</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0843999981880188</v>
+        <v>0.04690000042319298</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6484000086784363</v>
+        <v>0.6891999840736389</v>
       </c>
       <c r="H34" t="n">
-        <v>33.5</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s32.jpg</t>
+          <t>c:\ML_Project\test\Sad\s32.jpg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.05510000139474869</v>
+        <v>0.04010000079870224</v>
       </c>
       <c r="E35" t="n">
-        <v>0.260699987411499</v>
+        <v>0.6718000173568726</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2275000065565109</v>
+        <v>0.06390000134706497</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4104999899864197</v>
+        <v>0.2685999870300293</v>
       </c>
       <c r="H35" t="n">
-        <v>35.7</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s28.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s28.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1563,25 +1563,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.01549999974668026</v>
+        <v>0.02969999983906746</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6884999871253967</v>
+        <v>0.6711999773979187</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09749999642372131</v>
+        <v>0.1027999967336655</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2239000052213669</v>
+        <v>0.1614000052213669</v>
       </c>
       <c r="H36" t="n">
-        <v>28.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s68.jpg</t>
+          <t>c:\ML_Project\test\Sad\s68.jpg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1595,25 +1595,25 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.02810000069439411</v>
+        <v>0.09309999644756317</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7689999938011169</v>
+        <v>0.4560999870300293</v>
       </c>
       <c r="F37" t="n">
-        <v>0.06620000302791595</v>
+        <v>0.1494999974966049</v>
       </c>
       <c r="G37" t="n">
-        <v>0.183899998664856</v>
+        <v>0.4077000021934509</v>
       </c>
       <c r="H37" t="n">
-        <v>28.6</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a83.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a83.jpeg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1627,25 +1627,25 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.08540000021457672</v>
+        <v>0.03739999979734421</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03669999912381172</v>
+        <v>0.3700000047683716</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8321999907493591</v>
+        <v>0.07760000228881836</v>
       </c>
       <c r="G38" t="n">
-        <v>0.07490000128746033</v>
+        <v>0.4643000066280365</v>
       </c>
       <c r="H38" t="n">
-        <v>36.4</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h77.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h77.jpeg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.9559999704360962</v>
+        <v>0.8736000061035156</v>
       </c>
       <c r="E39" t="n">
-        <v>0.02260000072419643</v>
+        <v>0.05290000140666962</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01759999990463257</v>
+        <v>0.03810000047087669</v>
       </c>
       <c r="G39" t="n">
-        <v>0.03500000014901161</v>
+        <v>0.09030000120401382</v>
       </c>
       <c r="H39" t="n">
-        <v>97.09999999999999</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a114.webp</t>
+          <t>c:\ML_Project\test\Angry\a114.webp</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1691,25 +1691,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.06440000236034393</v>
+        <v>0.07289999723434448</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3246000111103058</v>
+        <v>0.4241000115871429</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1050999984145164</v>
+        <v>0.2267999947071075</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2813999950885773</v>
+        <v>0.2310999929904938</v>
       </c>
       <c r="H40" t="n">
-        <v>38.1</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f81.jpg</t>
+          <t>c:\ML_Project\test\Fear\f81.jpg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1723,25 +1723,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.04170000180602074</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="E41" t="n">
-        <v>0.240899994969368</v>
+        <v>0.1481000036001205</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5618000030517578</v>
+        <v>0.6151999831199646</v>
       </c>
       <c r="G41" t="n">
-        <v>0.125900000333786</v>
+        <v>0.1495999991893768</v>
       </c>
       <c r="H41" t="n">
-        <v>33.2</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h19.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h19.jpg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1755,25 +1755,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.845300018787384</v>
+        <v>0.7777000069618225</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08110000193119049</v>
+        <v>0.1145000010728836</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05200000107288361</v>
+        <v>0.04769999906420708</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1013000011444092</v>
+        <v>0.0632999986410141</v>
       </c>
       <c r="H42" t="n">
-        <v>89.8</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_images (8).jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_images (8).jpeg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1787,25 +1787,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.05840000137686729</v>
+        <v>0.07119999825954437</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1615000069141388</v>
+        <v>0.3310999870300293</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6280999779701233</v>
+        <v>0.4056999981403351</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1764000058174133</v>
+        <v>0.2308000028133392</v>
       </c>
       <c r="H43" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f57.jpg</t>
+          <t>c:\ML_Project\test\Fear\new_f57.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1819,25 +1819,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.03709999844431877</v>
+        <v>0.04019999876618385</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5896000266075134</v>
+        <v>0.6987000107765198</v>
       </c>
       <c r="F44" t="n">
-        <v>0.06620000302791595</v>
+        <v>0.08550000190734863</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3242000043392181</v>
+        <v>0.1833000034093857</v>
       </c>
       <c r="H44" t="n">
-        <v>31.4</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f40.jpg</t>
+          <t>c:\ML_Project\test\Fear\f40.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1851,25 +1851,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.03200000151991844</v>
+        <v>0.04509999975562096</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3079000115394592</v>
+        <v>0.4451999962329865</v>
       </c>
       <c r="F45" t="n">
-        <v>0.04479999840259552</v>
+        <v>0.07810000330209732</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5706999897956848</v>
+        <v>0.5329999923706055</v>
       </c>
       <c r="H45" t="n">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f21.jpg</t>
+          <t>c:\ML_Project\test\Fear\f21.jpg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.02690000087022781</v>
+        <v>0.05319999903440475</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2849000096321106</v>
+        <v>0.07129999995231628</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1489000022411346</v>
+        <v>0.4474999904632568</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3754000067710876</v>
+        <v>0.3325000107288361</v>
       </c>
       <c r="H46" t="n">
-        <v>35</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a106.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a106.jpeg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1915,25 +1915,25 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.08619999885559082</v>
+        <v>0.0502999983727932</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2010000050067902</v>
+        <v>0.2549999952316284</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6287000179290771</v>
+        <v>0.5608999729156494</v>
       </c>
       <c r="G47" t="n">
-        <v>0.191200003027916</v>
+        <v>0.1606999933719635</v>
       </c>
       <c r="H47" t="n">
-        <v>35.2</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a36.jpg</t>
+          <t>c:\ML_Project\test\Angry\a36.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1947,25 +1947,25 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.05469999834895134</v>
+        <v>0.05370000004768372</v>
       </c>
       <c r="E48" t="n">
-        <v>0.07289999723434448</v>
+        <v>0.1124999970197678</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8458999991416931</v>
+        <v>0.8471000194549561</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06379999965429306</v>
+        <v>0.05579999834299088</v>
       </c>
       <c r="H48" t="n">
-        <v>33.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a34.jpg</t>
+          <t>c:\ML_Project\test\Angry\a34.jpg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1979,25 +1979,25 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.06849999725818634</v>
+        <v>0.1327999979257584</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05240000039339066</v>
+        <v>0.06989999860525131</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7991999983787537</v>
+        <v>0.7075999975204468</v>
       </c>
       <c r="G49" t="n">
-        <v>0.09790000319480896</v>
+        <v>0.1278000026941299</v>
       </c>
       <c r="H49" t="n">
-        <v>35.3</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h46.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h46.jpg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2011,25 +2011,25 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.9394000172615051</v>
+        <v>0.8740000128746033</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02439999952912331</v>
+        <v>0.03700000047683716</v>
       </c>
       <c r="F50" t="n">
-        <v>0.04100000113248825</v>
+        <v>0.06939999759197235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.03909999877214432</v>
+        <v>0.04879999905824661</v>
       </c>
       <c r="H50" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a19.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a19.jpeg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2043,25 +2043,25 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.03040000051259995</v>
+        <v>0.05229999870061874</v>
       </c>
       <c r="E51" t="n">
-        <v>0.03480000048875809</v>
+        <v>0.07410000264644623</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2310999929904938</v>
+        <v>0.262800008058548</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7505999803543091</v>
+        <v>0.6079999804496765</v>
       </c>
       <c r="H51" t="n">
-        <v>35.2</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a4.jpg</t>
+          <t>c:\ML_Project\test\Angry\a4.jpg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2075,25 +2075,25 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.04809999838471413</v>
+        <v>0.07769999653100967</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6650999784469604</v>
+        <v>0.5552999973297119</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2495000064373016</v>
+        <v>0.3397000133991241</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1008000001311302</v>
+        <v>0.09109999984502792</v>
       </c>
       <c r="H52" t="n">
-        <v>30.1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s3.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s3.jpg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2107,25 +2107,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.02319999970495701</v>
+        <v>0.04839999973773956</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3504000008106232</v>
+        <v>0.3379000127315521</v>
       </c>
       <c r="F53" t="n">
-        <v>0.03420000150799751</v>
+        <v>0.06440000236034393</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6252999901771545</v>
+        <v>0.5710999965667725</v>
       </c>
       <c r="H53" t="n">
-        <v>32.7</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f43.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f43.jpeg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2139,25 +2139,25 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.01850000023841858</v>
+        <v>0.04019999876618385</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1099999994039536</v>
+        <v>0.1163000017404556</v>
       </c>
       <c r="F54" t="n">
-        <v>0.183799996972084</v>
+        <v>0.2102999985218048</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6399000287055969</v>
+        <v>0.6442999839782715</v>
       </c>
       <c r="H54" t="n">
-        <v>34.8</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f2.jpg</t>
+          <t>c:\ML_Project\test\Fear\f2.jpg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2171,25 +2171,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.03079999983310699</v>
+        <v>0.05180000141263008</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7850000262260437</v>
+        <v>0.4185999929904938</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0771000012755394</v>
+        <v>0.266400009393692</v>
       </c>
       <c r="G55" t="n">
-        <v>0.09040000289678574</v>
+        <v>0.1413999944925308</v>
       </c>
       <c r="H55" t="n">
-        <v>29.3</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h63.jpg</t>
+          <t>c:\ML_Project\test\Happy\h63.jpg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2203,25 +2203,25 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.9139999747276306</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="E56" t="n">
-        <v>0.03799999877810478</v>
+        <v>0.06459999829530716</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03290000185370445</v>
+        <v>0.06679999828338623</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04270000010728836</v>
+        <v>0.08410000056028366</v>
       </c>
       <c r="H56" t="n">
-        <v>94.5</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s47.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s47.jpeg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2235,25 +2235,25 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.02889999933540821</v>
+        <v>0.04259999841451645</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4846999943256378</v>
+        <v>0.4395999908447266</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1899999976158142</v>
+        <v>0.2277999967336655</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2809000015258789</v>
+        <v>0.3203000128269196</v>
       </c>
       <c r="H57" t="n">
-        <v>31.5</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a7.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a7.jpeg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2267,25 +2267,25 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1018000021576881</v>
+        <v>0.1553000062704086</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1652999967336655</v>
+        <v>0.3305999934673309</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2413000017404556</v>
+        <v>0.2460999935865402</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3894000053405762</v>
+        <v>0.324400007724762</v>
       </c>
       <c r="H58" t="n">
-        <v>40.4</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h43.jpg</t>
+          <t>c:\ML_Project\test\Happy\h43.jpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2299,25 +2299,25 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.8337000012397766</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="E59" t="n">
-        <v>0.06230000033974648</v>
+        <v>0.08860000222921371</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06880000233650208</v>
+        <v>0.06449999660253525</v>
       </c>
       <c r="G59" t="n">
-        <v>0.07800000160932541</v>
+        <v>0.08429999649524689</v>
       </c>
       <c r="H59" t="n">
-        <v>89.3</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s98.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s98.jpeg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2331,25 +2331,25 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.03400000184774399</v>
+        <v>0.0357000008225441</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5056999921798706</v>
+        <v>0.5144000053405762</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09759999811649323</v>
+        <v>0.1330000013113022</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3673000037670135</v>
+        <v>0.2858999967575073</v>
       </c>
       <c r="H60" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h59.jpg</t>
+          <t>c:\ML_Project\test\Happy\h59.jpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2363,25 +2363,25 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.8740000128746033</v>
+        <v>0.647599995136261</v>
       </c>
       <c r="E61" t="n">
-        <v>0.06870000064373016</v>
+        <v>0.2236000001430511</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0535999983549118</v>
+        <v>0.1036999970674515</v>
       </c>
       <c r="G61" t="n">
-        <v>0.08049999922513962</v>
+        <v>0.09200000017881393</v>
       </c>
       <c r="H61" t="n">
-        <v>91.7</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f94.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f94.jpeg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2395,25 +2395,25 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.02219999954104424</v>
+        <v>0.05499999970197678</v>
       </c>
       <c r="E62" t="n">
-        <v>0.07159999758005142</v>
+        <v>0.1361999958753586</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1361999958753586</v>
+        <v>0.2148000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7627000212669373</v>
+        <v>0.5978999733924866</v>
       </c>
       <c r="H62" t="n">
-        <v>35.3</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a44.jpg</t>
+          <t>c:\ML_Project\test\Angry\a44.jpg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2427,25 +2427,25 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.06230000033974648</v>
+        <v>0.1062999963760376</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3068999946117401</v>
+        <v>0.2736000120639801</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5691999793052673</v>
+        <v>0.5974000096321106</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0786999985575676</v>
+        <v>0.1149000003933907</v>
       </c>
       <c r="H63" t="n">
-        <v>33.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f77.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f77.jpeg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2459,25 +2459,25 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.1297000050544739</v>
+        <v>0.07900000363588333</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1785999983549118</v>
+        <v>0.5236999988555908</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1439999938011169</v>
+        <v>0.3833999931812286</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6449999809265137</v>
+        <v>0.07760000228881836</v>
       </c>
       <c r="H64" t="n">
-        <v>40.9</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a88.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a88.jpeg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.07440000027418137</v>
+        <v>0.1023999974131584</v>
       </c>
       <c r="E65" t="n">
-        <v>0.09950000047683716</v>
+        <v>0.1040000021457672</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7813000082969666</v>
+        <v>0.7547000050544739</v>
       </c>
       <c r="G65" t="n">
-        <v>0.09269999712705612</v>
+        <v>0.09570000320672989</v>
       </c>
       <c r="H65" t="n">
-        <v>35.1</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s74.png</t>
+          <t>c:\ML_Project\test\Sad\s74.png</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2523,25 +2523,25 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.03299999982118607</v>
+        <v>0.101000003516674</v>
       </c>
       <c r="E66" t="n">
-        <v>0.383899986743927</v>
+        <v>0.160400003194809</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1844999939203262</v>
+        <v>0.2851000130176544</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2055000066757202</v>
+        <v>0.4041999876499176</v>
       </c>
       <c r="H66" t="n">
-        <v>34.6</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h16.jpg</t>
+          <t>c:\ML_Project\test\Happy\h16.jpg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2555,25 +2555,25 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.917900025844574</v>
+        <v>0.8278999924659729</v>
       </c>
       <c r="E67" t="n">
-        <v>0.05550000071525574</v>
+        <v>0.1036999970674515</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03299999982118607</v>
+        <v>0.05200000107288361</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0568000003695488</v>
+        <v>0.08860000222921371</v>
       </c>
       <c r="H67" t="n">
-        <v>94.5</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h70.jpg</t>
+          <t>c:\ML_Project\test\Happy\h70.jpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2587,25 +2587,25 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.9172000288963318</v>
+        <v>0.8460999727249146</v>
       </c>
       <c r="E68" t="n">
-        <v>0.03030000068247318</v>
+        <v>0.04940000176429749</v>
       </c>
       <c r="F68" t="n">
-        <v>0.07360000163316727</v>
+        <v>0.06949999928474426</v>
       </c>
       <c r="G68" t="n">
-        <v>0.04760000109672546</v>
+        <v>0.04100000113248825</v>
       </c>
       <c r="H68" t="n">
-        <v>94.5</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h45.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h45.jpg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2619,25 +2619,25 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.6937000155448914</v>
+        <v>0.6245999932289124</v>
       </c>
       <c r="E69" t="n">
         <v>0.08190000057220459</v>
       </c>
       <c r="F69" t="n">
-        <v>0.05209999904036522</v>
+        <v>0.05689999833703041</v>
       </c>
       <c r="G69" t="n">
-        <v>0.160400003194809</v>
+        <v>0.2334000021219254</v>
       </c>
       <c r="H69" t="n">
-        <v>80.8</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h30.jpg</t>
+          <t>c:\ML_Project\test\Happy\h30.jpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2651,25 +2651,25 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.8622999787330627</v>
+        <v>0.8087000250816345</v>
       </c>
       <c r="E70" t="n">
-        <v>0.06179999932646751</v>
+        <v>0.09849999845027924</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0544000007212162</v>
+        <v>0.07320000231266022</v>
       </c>
       <c r="G70" t="n">
-        <v>0.04899999871850014</v>
+        <v>0.08900000154972076</v>
       </c>
       <c r="H70" t="n">
-        <v>91.2</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f78.jpg</t>
+          <t>c:\ML_Project\test\Fear\f78.jpg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2683,25 +2683,25 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.02080000005662441</v>
+        <v>0.04650000110268593</v>
       </c>
       <c r="E71" t="n">
-        <v>0.03999999910593033</v>
+        <v>0.0877000018954277</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8996999859809875</v>
+        <v>0.83160001039505</v>
       </c>
       <c r="G71" t="n">
-        <v>0.04650000110268593</v>
+        <v>0.07779999822378159</v>
       </c>
       <c r="H71" t="n">
-        <v>31.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a55.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a55.jpeg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2715,25 +2715,25 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.05090000107884407</v>
+        <v>0.0544000007212162</v>
       </c>
       <c r="E72" t="n">
-        <v>0.118199996650219</v>
+        <v>0.1480000019073486</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7107999920845032</v>
+        <v>0.7138000130653381</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1488000005483627</v>
+        <v>0.06780000030994415</v>
       </c>
       <c r="H72" t="n">
-        <v>33.7</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a46.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a46.jpeg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2747,25 +2747,25 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.08129999786615372</v>
+        <v>0.09759999811649323</v>
       </c>
       <c r="E73" t="n">
-        <v>0.131400004029274</v>
+        <v>0.1572999954223633</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2387000024318695</v>
+        <v>0.2047999948263168</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5564000010490417</v>
+        <v>0.5964999794960022</v>
       </c>
       <c r="H73" t="n">
-        <v>38.3</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f9.jpg</t>
+          <t>c:\ML_Project\test\Fear\f9.jpg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2779,25 +2779,25 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.05820000171661377</v>
+        <v>0.05490000173449516</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5135999917984009</v>
+        <v>0.6532999873161316</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3684000074863434</v>
+        <v>0.2383999973535538</v>
       </c>
       <c r="G74" t="n">
-        <v>0.100100003182888</v>
+        <v>0.1054999977350235</v>
       </c>
       <c r="H74" t="n">
-        <v>32</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h43.jpg</t>
+          <t>c:\ML_Project\test\Happy\h43.jpg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2811,25 +2811,25 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.8337000012397766</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="E75" t="n">
-        <v>0.06230000033974648</v>
+        <v>0.08860000222921371</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06880000233650208</v>
+        <v>0.06449999660253525</v>
       </c>
       <c r="G75" t="n">
-        <v>0.07800000160932541</v>
+        <v>0.08429999649524689</v>
       </c>
       <c r="H75" t="n">
-        <v>89.3</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s76.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s76.jpeg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0949999988079071</v>
+        <v>0.1096000000834465</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4503999948501587</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="F76" t="n">
-        <v>0.04470000043511391</v>
+        <v>0.02740000002086163</v>
       </c>
       <c r="G76" t="n">
-        <v>0.378600001335144</v>
+        <v>0.3939999938011169</v>
       </c>
       <c r="H76" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h6.jpg</t>
+          <t>c:\ML_Project\test\Happy\h6.jpg</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2875,25 +2875,25 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.6521999835968018</v>
+        <v>0.7692999839782715</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1331000030040741</v>
+        <v>0.05579999834299088</v>
       </c>
       <c r="F77" t="n">
-        <v>0.08429999649524689</v>
+        <v>0.03759999945759773</v>
       </c>
       <c r="G77" t="n">
-        <v>0.05869999900460243</v>
+        <v>0.1115999966859818</v>
       </c>
       <c r="H77" t="n">
-        <v>78.09999999999999</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s97.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s97.jpeg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2907,25 +2907,25 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.2240000069141388</v>
+        <v>0.1488000005483627</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4289000034332275</v>
+        <v>0.5906000137329102</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1044000014662743</v>
+        <v>0.160400003194809</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1070000007748604</v>
+        <v>0.06629999727010727</v>
       </c>
       <c r="H78" t="n">
-        <v>47.6</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s71.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s71.jpeg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2939,25 +2939,25 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.0153999999165535</v>
+        <v>0.06159999966621399</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8708000183105469</v>
+        <v>0.7333999872207642</v>
       </c>
       <c r="F79" t="n">
-        <v>0.03240000084042549</v>
+        <v>0.07559999823570251</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1028999984264374</v>
+        <v>0.1931000053882599</v>
       </c>
       <c r="H79" t="n">
-        <v>27.1</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f17.jpg</t>
+          <t>c:\ML_Project\test\Fear\f17.jpg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2971,25 +2971,25 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.02690000087022781</v>
+        <v>0.06549999862909317</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3169000148773193</v>
+        <v>0.3603000044822693</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1805000007152557</v>
+        <v>0.1218999996781349</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4343999922275543</v>
+        <v>0.4411999881267548</v>
       </c>
       <c r="H80" t="n">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h92.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h92.jpeg</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3003,25 +3003,25 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.9305999875068665</v>
+        <v>0.7408999800682068</v>
       </c>
       <c r="E81" t="n">
-        <v>0.04320000112056732</v>
+        <v>0.1762000024318695</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0255999993532896</v>
+        <v>0.04479999840259552</v>
       </c>
       <c r="G81" t="n">
-        <v>0.04980000108480453</v>
+        <v>0.1089999973773956</v>
       </c>
       <c r="H81" t="n">
-        <v>95.40000000000001</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f24.jpg</t>
+          <t>c:\ML_Project\test\Fear\f24.jpg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3035,25 +3035,25 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0786999985575676</v>
+        <v>0.04899999871850014</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1571000069379807</v>
+        <v>0.1994999945163727</v>
       </c>
       <c r="F82" t="n">
-        <v>0.286300003528595</v>
+        <v>0.1692000031471252</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5922999978065491</v>
+        <v>0.5539000034332275</v>
       </c>
       <c r="H82" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s36.jpg</t>
+          <t>c:\ML_Project\test\Sad\s36.jpg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3067,25 +3067,25 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.04879999905824661</v>
+        <v>0.08680000156164169</v>
       </c>
       <c r="E83" t="n">
-        <v>0.6948000192642212</v>
+        <v>0.402099996805191</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1430000066757202</v>
+        <v>0.2651000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1556999981403351</v>
+        <v>0.2211000025272369</v>
       </c>
       <c r="H83" t="n">
-        <v>30.6</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h50.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h50.jpg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3099,25 +3099,25 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.805400013923645</v>
+        <v>0.3731000125408173</v>
       </c>
       <c r="E84" t="n">
-        <v>0.07429999858140945</v>
+        <v>0.2721999883651733</v>
       </c>
       <c r="F84" t="n">
-        <v>0.09849999845027924</v>
+        <v>0.2847999930381775</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1076000034809113</v>
+        <v>0.1212000027298927</v>
       </c>
       <c r="H84" t="n">
-        <v>87.2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f92.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f92.jpeg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3131,25 +3131,25 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.04600000008940697</v>
+        <v>0.02089999988675117</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4248000085353851</v>
+        <v>0.5952000021934509</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3628000020980835</v>
+        <v>0.1118000000715256</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1507000029087067</v>
+        <v>0.1406999975442886</v>
       </c>
       <c r="H85" t="n">
-        <v>32.5</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f117.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f117.jpeg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.1394000053405762</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4812999963760376</v>
+        <v>0.6445000171661377</v>
       </c>
       <c r="F86" t="n">
-        <v>0.05860000103712082</v>
+        <v>0.08009999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2401999980211258</v>
+        <v>0.2442999929189682</v>
       </c>
       <c r="H86" t="n">
-        <v>39.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s8.jpg</t>
+          <t>c:\ML_Project\test\Sad\s8.jpg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3195,25 +3195,25 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.02089999988675117</v>
+        <v>0.02119999937713146</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7089999914169312</v>
+        <v>0.7872999906539917</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1747999936342239</v>
+        <v>0.1464000046253204</v>
       </c>
       <c r="G87" t="n">
-        <v>0.09369999915361404</v>
+        <v>0.06589999794960022</v>
       </c>
       <c r="H87" t="n">
-        <v>28.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f2.png</t>
+          <t>c:\ML_Project\test\Fear\new_f2.png</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3227,25 +3227,25 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.6845999956130981</v>
+        <v>0.6784999966621399</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2594999969005585</v>
+        <v>0.1853999942541122</v>
       </c>
       <c r="F88" t="n">
-        <v>0.06030000001192093</v>
+        <v>0.08389999717473984</v>
       </c>
       <c r="G88" t="n">
-        <v>0.05070000141859055</v>
+        <v>0.06520000100135803</v>
       </c>
       <c r="H88" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s53.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s53.jpeg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3259,25 +3259,25 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.1045999974012375</v>
+        <v>0.1102999970316887</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4049000144004822</v>
+        <v>0.4253999888896942</v>
       </c>
       <c r="F89" t="n">
-        <v>0.09229999780654907</v>
+        <v>0.05229999870061874</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4702999889850616</v>
+        <v>0.3959999978542328</v>
       </c>
       <c r="H89" t="n">
-        <v>37.5</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s46.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s46.jpeg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3291,25 +3291,25 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.0812000036239624</v>
+        <v>0.2284000068902969</v>
       </c>
       <c r="E90" t="n">
-        <v>0.07020000368356705</v>
+        <v>0.07729999721050262</v>
       </c>
       <c r="F90" t="n">
-        <v>0.351500004529953</v>
+        <v>0.3260000050067902</v>
       </c>
       <c r="G90" t="n">
-        <v>0.588699996471405</v>
+        <v>0.4108000099658966</v>
       </c>
       <c r="H90" t="n">
-        <v>37.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a84.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a84.jpeg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3323,25 +3323,25 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.08659999817609787</v>
+        <v>0.09669999778270721</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1118000000715256</v>
+        <v>0.1516000032424927</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7203999757766724</v>
+        <v>0.6665999889373779</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1284999996423721</v>
+        <v>0.1552000045776367</v>
       </c>
       <c r="H91" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f99.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f99.jpeg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3355,25 +3355,25 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.02620000019669533</v>
+        <v>0.06719999760389328</v>
       </c>
       <c r="E92" t="n">
-        <v>0.07729999721050262</v>
+        <v>0.2216999977827072</v>
       </c>
       <c r="F92" t="n">
-        <v>0.04560000076889992</v>
+        <v>0.04149999842047691</v>
       </c>
       <c r="G92" t="n">
-        <v>0.8934999704360962</v>
+        <v>0.7610999941825867</v>
       </c>
       <c r="H92" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a43.jpg</t>
+          <t>c:\ML_Project\test\Angry\a43.jpg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3387,25 +3387,25 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.04080000147223473</v>
+        <v>0.08590000122785568</v>
       </c>
       <c r="E93" t="n">
-        <v>0.06809999793767929</v>
+        <v>0.06300000101327896</v>
       </c>
       <c r="F93" t="n">
-        <v>0.678600013256073</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2269999980926514</v>
+        <v>0.1886000037193298</v>
       </c>
       <c r="H93" t="n">
-        <v>33.8</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f33.jpg</t>
+          <t>c:\ML_Project\test\Fear\f33.jpg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3419,25 +3419,25 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.01530000008642673</v>
+        <v>0.05730000138282776</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1683000028133392</v>
+        <v>0.3707999885082245</v>
       </c>
       <c r="F94" t="n">
-        <v>0.04740000143647194</v>
+        <v>0.1177000030875206</v>
       </c>
       <c r="G94" t="n">
-        <v>0.805899977684021</v>
+        <v>0.4444000124931335</v>
       </c>
       <c r="H94" t="n">
-        <v>33.8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h17.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h17.jpg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3451,25 +3451,25 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.9732000231742859</v>
+        <v>0.9617000222206116</v>
       </c>
       <c r="E95" t="n">
-        <v>0.01240000035613775</v>
+        <v>0.01119999960064888</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01640000008046627</v>
+        <v>0.01669999957084656</v>
       </c>
       <c r="G95" t="n">
-        <v>0.01219999976456165</v>
+        <v>0.01950000040233135</v>
       </c>
       <c r="H95" t="n">
-        <v>98.3</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h34.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h34.jpg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3483,25 +3483,25 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.7713000178337097</v>
+        <v>0.6223999857902527</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1307000070810318</v>
+        <v>0.2172999978065491</v>
       </c>
       <c r="F96" t="n">
-        <v>0.04769999906420708</v>
+        <v>0.1141000017523766</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1481000036001205</v>
+        <v>0.1103999987244606</v>
       </c>
       <c r="H96" t="n">
-        <v>84.8</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s11.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s11.jpg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3515,25 +3515,25 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.06859999895095825</v>
+        <v>0.07190000265836716</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1066000014543533</v>
+        <v>0.1870000064373016</v>
       </c>
       <c r="F97" t="n">
-        <v>0.06340000033378601</v>
+        <v>0.08399999886751175</v>
       </c>
       <c r="G97" t="n">
-        <v>0.7774999737739563</v>
+        <v>0.6326000094413757</v>
       </c>
       <c r="H97" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s36.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s36.jpeg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3547,25 +3547,25 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.01520000025629997</v>
+        <v>0.03999999910593033</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7626000046730042</v>
+        <v>0.4390000104904175</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01530000008642673</v>
+        <v>0.02569999918341637</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2856999933719635</v>
+        <v>0.6133999824523926</v>
       </c>
       <c r="H98" t="n">
-        <v>27.7</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s25.jpg</t>
+          <t>c:\ML_Project\test\Sad\s25.jpg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3579,25 +3579,25 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.06809999793767929</v>
+        <v>0.05730000138282776</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7074000239372253</v>
+        <v>0.8464000225067139</v>
       </c>
       <c r="F99" t="n">
-        <v>0.09520000219345093</v>
+        <v>0.07580000162124634</v>
       </c>
       <c r="G99" t="n">
-        <v>0.09960000216960907</v>
+        <v>0.05579999834299088</v>
       </c>
       <c r="H99" t="n">
-        <v>32.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a110.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a110.jpeg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3611,25 +3611,25 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.01310000009834766</v>
+        <v>0.03950000181794167</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8960999846458435</v>
+        <v>0.8260999917984009</v>
       </c>
       <c r="F100" t="n">
-        <v>0.03260000050067902</v>
+        <v>0.05559999868273735</v>
       </c>
       <c r="G100" t="n">
-        <v>0.06199999898672104</v>
+        <v>0.1331000030040741</v>
       </c>
       <c r="H100" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a56.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a56.jpeg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3643,25 +3643,25 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.05869999900460243</v>
+        <v>0.06880000233650208</v>
       </c>
       <c r="E101" t="n">
-        <v>0.08340000361204147</v>
+        <v>0.06849999725818634</v>
       </c>
       <c r="F101" t="n">
-        <v>0.781499981880188</v>
+        <v>0.8619999885559082</v>
       </c>
       <c r="G101" t="n">
-        <v>0.09520000219345093</v>
+        <v>0.05660000070929527</v>
       </c>
       <c r="H101" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h25.jpg</t>
+          <t>c:\ML_Project\test\Happy\h25.jpg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3675,25 +3675,25 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.4745000004768372</v>
+        <v>0.3707000017166138</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2178999930620193</v>
+        <v>0.2529000043869019</v>
       </c>
       <c r="F102" t="n">
-        <v>0.06030000001192093</v>
+        <v>0.1492000073194504</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1321000009775162</v>
+        <v>0.1636999994516373</v>
       </c>
       <c r="H102" t="n">
-        <v>66.40000000000001</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f64.jpg</t>
+          <t>c:\ML_Project\test\Fear\f64.jpg</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3707,25 +3707,25 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.1624000072479248</v>
+        <v>0.0885000005364418</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2822999954223633</v>
+        <v>0.5449000000953674</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1178999990224838</v>
+        <v>0.1160999983549118</v>
       </c>
       <c r="G103" t="n">
-        <v>0.4235999882221222</v>
+        <v>0.367000013589859</v>
       </c>
       <c r="H103" t="n">
-        <v>43.4</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f15.jpg</t>
+          <t>c:\ML_Project\test\Fear\f15.jpg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3739,25 +3739,25 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.01909999921917915</v>
+        <v>0.04129999876022339</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0982000008225441</v>
+        <v>0.08799999952316284</v>
       </c>
       <c r="F104" t="n">
-        <v>0.4296000003814697</v>
+        <v>0.4034999907016754</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3731000125408173</v>
+        <v>0.4126999974250793</v>
       </c>
       <c r="H104" t="n">
-        <v>34</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f17.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f17.jpeg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3771,25 +3771,25 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.02319999970495701</v>
+        <v>0.05880000069737434</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8328999876976013</v>
+        <v>0.7678999900817871</v>
       </c>
       <c r="F105" t="n">
-        <v>0.05070000141859055</v>
+        <v>0.07970000058412552</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1136000007390976</v>
+        <v>0.1112999990582466</v>
       </c>
       <c r="H105" t="n">
-        <v>28</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h53.jpg</t>
+          <t>c:\ML_Project\test\Happy\h53.jpg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3803,25 +3803,25 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.9154999852180481</v>
+        <v>0.7642999887466431</v>
       </c>
       <c r="E106" t="n">
-        <v>0.03779999911785126</v>
+        <v>0.07299999892711639</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03830000013113022</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="G106" t="n">
-        <v>0.05990000069141388</v>
+        <v>0.118199996650219</v>
       </c>
       <c r="H106" t="n">
-        <v>94.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f3.jpg</t>
+          <t>c:\ML_Project\test\Fear\f3.jpg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3835,25 +3835,25 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.0333000011742115</v>
+        <v>0.03480000048875809</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3240000009536743</v>
+        <v>0.5401999950408936</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4289999902248383</v>
+        <v>0.2547999918460846</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1650000065565109</v>
+        <v>0.1835999935865402</v>
       </c>
       <c r="H107" t="n">
-        <v>32.6</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a22.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a22.jpeg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3867,25 +3867,25 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.01600000075995922</v>
+        <v>0.02219999954104424</v>
       </c>
       <c r="E108" t="n">
-        <v>0.04500000178813934</v>
+        <v>0.05790000036358833</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9061999917030334</v>
+        <v>0.843999981880188</v>
       </c>
       <c r="G108" t="n">
-        <v>0.04500000178813934</v>
+        <v>0.04210000112652779</v>
       </c>
       <c r="H108" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h83.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h83.jpeg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3899,25 +3899,25 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.6399000287055969</v>
+        <v>0.583299994468689</v>
       </c>
       <c r="E109" t="n">
-        <v>0.2036000043153763</v>
+        <v>0.2976999878883362</v>
       </c>
       <c r="F109" t="n">
-        <v>0.02969999983906746</v>
+        <v>0.1066000014543533</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1013000011444092</v>
+        <v>0.1190000027418137</v>
       </c>
       <c r="H109" t="n">
-        <v>76.8</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h56.jpg</t>
+          <t>c:\ML_Project\test\Happy\h56.jpg</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3931,25 +3931,25 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.8345000147819519</v>
+        <v>0.7208999991416931</v>
       </c>
       <c r="E110" t="n">
-        <v>0.05649999901652336</v>
+        <v>0.1483999937772751</v>
       </c>
       <c r="F110" t="n">
-        <v>0.06620000302791595</v>
+        <v>0.05270000174641609</v>
       </c>
       <c r="G110" t="n">
-        <v>0.1389999985694885</v>
+        <v>0.1186000034213066</v>
       </c>
       <c r="H110" t="n">
-        <v>89.09999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a80.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a80.jpeg</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3963,25 +3963,25 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0494999997317791</v>
+        <v>0.05279999971389771</v>
       </c>
       <c r="E111" t="n">
-        <v>0.07050000131130219</v>
+        <v>0.09260000288486481</v>
       </c>
       <c r="F111" t="n">
-        <v>0.710099995136261</v>
+        <v>0.5806000232696533</v>
       </c>
       <c r="G111" t="n">
-        <v>0.190200001001358</v>
+        <v>0.3343999981880188</v>
       </c>
       <c r="H111" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s19.jpg</t>
+          <t>c:\ML_Project\test\Sad\s19.jpg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3995,25 +3995,25 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.07980000227689743</v>
+        <v>0.08910000324249268</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5253000259399414</v>
+        <v>0.5688999891281128</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1488000005483627</v>
+        <v>0.07989999651908875</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2831000089645386</v>
+        <v>0.2896000146865845</v>
       </c>
       <c r="H112" t="n">
-        <v>34.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s80.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s80.jpeg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4027,25 +4027,25 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.02740000002086163</v>
+        <v>0.03319999948143959</v>
       </c>
       <c r="E113" t="n">
-        <v>0.4704999923706055</v>
+        <v>0.5242000222206116</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2096000015735626</v>
+        <v>0.1005999967455864</v>
       </c>
       <c r="G113" t="n">
-        <v>0.191200003027916</v>
+        <v>0.3199000060558319</v>
       </c>
       <c r="H113" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a117.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a117.jpeg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4059,25 +4059,25 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.02820000052452087</v>
+        <v>0.04960000142455101</v>
       </c>
       <c r="E114" t="n">
-        <v>0.5475999712944031</v>
+        <v>0.2676999866962433</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1589999943971634</v>
+        <v>0.2259999960660934</v>
       </c>
       <c r="G114" t="n">
-        <v>0.2115000039339066</v>
+        <v>0.3531000018119812</v>
       </c>
       <c r="H114" t="n">
-        <v>31.4</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h17.jpg</t>
+          <t>c:\ML_Project\test\Happy\h17.jpg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4091,25 +4091,25 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.9595000147819519</v>
+        <v>0.8881999850273132</v>
       </c>
       <c r="E115" t="n">
-        <v>0.01920000091195107</v>
+        <v>0.04549999907612801</v>
       </c>
       <c r="F115" t="n">
-        <v>0.02910000085830688</v>
+        <v>0.05660000070929527</v>
       </c>
       <c r="G115" t="n">
-        <v>0.02649999968707561</v>
+        <v>0.06629999727010727</v>
       </c>
       <c r="H115" t="n">
-        <v>97.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h9.jpg</t>
+          <t>c:\ML_Project\test\Happy\h9.jpg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4123,25 +4123,25 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.9041000008583069</v>
+        <v>0.8902000188827515</v>
       </c>
       <c r="E116" t="n">
-        <v>0.04699999839067459</v>
+        <v>0.04540000110864639</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05380000174045563</v>
+        <v>0.05999999865889549</v>
       </c>
       <c r="G116" t="n">
-        <v>0.03370000049471855</v>
+        <v>0.03689999878406525</v>
       </c>
       <c r="H116" t="n">
-        <v>93.8</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f13.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f13.jpeg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4155,25 +4155,25 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.04899999871850014</v>
       </c>
       <c r="E117" t="n">
-        <v>0.4318999946117401</v>
+        <v>0.5593000054359436</v>
       </c>
       <c r="F117" t="n">
-        <v>0.08190000057220459</v>
+        <v>0.07660000026226044</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6013000011444092</v>
+        <v>0.4575000107288361</v>
       </c>
       <c r="H117" t="n">
-        <v>31.7</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f41.jpg</t>
+          <t>c:\ML_Project\test\Fear\f41.jpg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4187,25 +4187,25 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.04239999875426292</v>
+        <v>0.09809999912977219</v>
       </c>
       <c r="E118" t="n">
-        <v>0.09730000048875809</v>
+        <v>0.08340000361204147</v>
       </c>
       <c r="F118" t="n">
-        <v>0.07400000095367432</v>
+        <v>0.4307000041007996</v>
       </c>
       <c r="G118" t="n">
-        <v>0.8312000036239624</v>
+        <v>0.4257999956607819</v>
       </c>
       <c r="H118" t="n">
-        <v>36.3</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h6.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h6.jpg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.9681000113487244</v>
+        <v>0.8784999847412109</v>
       </c>
       <c r="E119" t="n">
-        <v>0.01360000018030405</v>
+        <v>0.0227000005543232</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02429999969899654</v>
+        <v>0.05950000137090683</v>
       </c>
       <c r="G119" t="n">
-        <v>0.01470000017434359</v>
+        <v>0.02859999984502792</v>
       </c>
       <c r="H119" t="n">
-        <v>97.90000000000001</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a7.jpg</t>
+          <t>c:\ML_Project\test\Angry\a7.jpg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4251,25 +4251,25 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.0681999996304512</v>
+        <v>0.04500000178813934</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1129999980330467</v>
+        <v>0.503000020980835</v>
       </c>
       <c r="F120" t="n">
-        <v>0.7384999990463257</v>
+        <v>0.2802999913692474</v>
       </c>
       <c r="G120" t="n">
-        <v>0.08489999920129776</v>
+        <v>0.1422999948263168</v>
       </c>
       <c r="H120" t="n">
-        <v>35.1</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h3.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h3.jpg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4283,25 +4283,25 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.8633999824523926</v>
+        <v>0.8416000008583069</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1182999983429909</v>
+        <v>0.08749999850988388</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0198999997228384</v>
+        <v>0.04289999976754189</v>
       </c>
       <c r="G121" t="n">
-        <v>0.02659999951720238</v>
+        <v>0.05229999870061874</v>
       </c>
       <c r="H121" t="n">
-        <v>91.09999999999999</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s38.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s38.jpeg</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4315,25 +4315,25 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.05820000171661377</v>
+        <v>0.07859999686479568</v>
       </c>
       <c r="E122" t="n">
-        <v>0.6941999793052673</v>
+        <v>0.7210000157356262</v>
       </c>
       <c r="F122" t="n">
-        <v>0.07840000092983246</v>
+        <v>0.0778999999165535</v>
       </c>
       <c r="G122" t="n">
-        <v>0.1845999956130981</v>
+        <v>0.1186000034213066</v>
       </c>
       <c r="H122" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h57.jpg</t>
+          <t>c:\ML_Project\test\Happy\h57.jpg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4347,25 +4347,25 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.9753000140190125</v>
+        <v>0.7947999835014343</v>
       </c>
       <c r="E123" t="n">
-        <v>0.01130000036209822</v>
+        <v>0.04280000180006027</v>
       </c>
       <c r="F123" t="n">
-        <v>0.01789999939501286</v>
+        <v>0.08349999785423279</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0203000009059906</v>
+        <v>0.04069999977946281</v>
       </c>
       <c r="H123" t="n">
-        <v>98.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h84.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h84.jpeg</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4379,25 +4379,25 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.7670999765396118</v>
+        <v>0.6765999794006348</v>
       </c>
       <c r="E124" t="n">
-        <v>0.06509999930858612</v>
+        <v>0.1766999959945679</v>
       </c>
       <c r="F124" t="n">
-        <v>0.01730000041425228</v>
+        <v>0.04199999943375587</v>
       </c>
       <c r="G124" t="n">
-        <v>0.08799999952316284</v>
+        <v>0.1807000041007996</v>
       </c>
       <c r="H124" t="n">
-        <v>85.90000000000001</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f34.jpg</t>
+          <t>c:\ML_Project\test\Fear\f34.jpg</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4411,25 +4411,25 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.04749999940395355</v>
+        <v>0.0544000007212162</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1406999975442886</v>
+        <v>0.1645999997854233</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1103999987244606</v>
+        <v>0.08649999648332596</v>
       </c>
       <c r="G125" t="n">
-        <v>0.7554000020027161</v>
+        <v>0.7351999878883362</v>
       </c>
       <c r="H125" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a48.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a48.jpeg</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.08659999817609787</v>
+        <v>0.09669999778270721</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1118000000715256</v>
+        <v>0.1516000032424927</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7203999757766724</v>
+        <v>0.6665999889373779</v>
       </c>
       <c r="G126" t="n">
-        <v>0.1284999996423721</v>
+        <v>0.1552000045776367</v>
       </c>
       <c r="H126" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s17.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s17.jpg</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4475,25 +4475,25 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.1234000027179718</v>
+        <v>0.1606999933719635</v>
       </c>
       <c r="E127" t="n">
-        <v>0.09399999678134918</v>
+        <v>0.1722999960184097</v>
       </c>
       <c r="F127" t="n">
-        <v>0.09939999878406525</v>
+        <v>0.2964999973773956</v>
       </c>
       <c r="G127" t="n">
-        <v>0.65829998254776</v>
+        <v>0.4778999984264374</v>
       </c>
       <c r="H127" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s5.jpg</t>
+          <t>c:\ML_Project\test\Sad\s5.jpg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4507,25 +4507,25 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.9251999855041504</v>
+        <v>0.7389000058174133</v>
       </c>
       <c r="E128" t="n">
-        <v>0.05460000038146973</v>
+        <v>0.1233000010251999</v>
       </c>
       <c r="F128" t="n">
-        <v>0.04149999842047691</v>
+        <v>0.1080000028014183</v>
       </c>
       <c r="G128" t="n">
-        <v>0.04839999973773956</v>
+        <v>0.05260000005364418</v>
       </c>
       <c r="H128" t="n">
-        <v>94.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f45.jpg</t>
+          <t>c:\ML_Project\test\Fear\f45.jpg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4539,25 +4539,25 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.05979999899864197</v>
+        <v>0.07680000364780426</v>
       </c>
       <c r="E129" t="n">
-        <v>0.07840000092983246</v>
+        <v>0.3616000115871429</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1442999988794327</v>
+        <v>0.07479999959468842</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6873999834060669</v>
+        <v>0.5564000010490417</v>
       </c>
       <c r="H129" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a83.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a83.jpeg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4571,25 +4571,25 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.04879999905824661</v>
+        <v>0.03739999979734421</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2958000004291534</v>
+        <v>0.3700000047683716</v>
       </c>
       <c r="F130" t="n">
-        <v>0.135900005698204</v>
+        <v>0.07760000228881836</v>
       </c>
       <c r="G130" t="n">
-        <v>0.446399986743927</v>
+        <v>0.4643000066280365</v>
       </c>
       <c r="H130" t="n">
-        <v>35.6</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f40.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f40.jpeg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4603,25 +4603,25 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.06260000169277191</v>
+        <v>0.05999999865889549</v>
       </c>
       <c r="E131" t="n">
-        <v>0.2375999987125397</v>
+        <v>0.4435999989509583</v>
       </c>
       <c r="F131" t="n">
-        <v>0.05460000038146973</v>
+        <v>0.09470000118017197</v>
       </c>
       <c r="G131" t="n">
-        <v>0.7337999939918518</v>
+        <v>0.5253999829292297</v>
       </c>
       <c r="H131" t="n">
-        <v>36</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s15.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s15.jpg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4635,25 +4635,25 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.01799999922513962</v>
+        <v>0.03660000115633011</v>
       </c>
       <c r="E132" t="n">
-        <v>0.6761999726295471</v>
+        <v>0.5841000080108643</v>
       </c>
       <c r="F132" t="n">
-        <v>0.08320000022649765</v>
+        <v>0.07410000264644623</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2293999940156937</v>
+        <v>0.3815000057220459</v>
       </c>
       <c r="H132" t="n">
-        <v>29.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f88.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f88.jpeg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.02749999985098839</v>
+        <v>0.05480000004172325</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7954999804496765</v>
+        <v>0.5254999995231628</v>
       </c>
       <c r="F133" t="n">
-        <v>0.05339999869465828</v>
+        <v>0.0786999985575676</v>
       </c>
       <c r="G133" t="n">
-        <v>0.1404000073671341</v>
+        <v>0.4137000143527985</v>
       </c>
       <c r="H133" t="n">
-        <v>28.7</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f58.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f58.jpeg</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4699,25 +4699,25 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.07400000095367432</v>
+        <v>0.05480000004172325</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2107000052928925</v>
+        <v>0.3856000006198883</v>
       </c>
       <c r="F134" t="n">
-        <v>0.048700001090765</v>
+        <v>0.05950000137090683</v>
       </c>
       <c r="G134" t="n">
-        <v>0.7045999765396118</v>
+        <v>0.5812000036239624</v>
       </c>
       <c r="H134" t="n">
-        <v>37.6</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f105.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f105.jpeg</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4731,25 +4731,25 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.05229999870061874</v>
+        <v>0.04170000180602074</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1818999946117401</v>
+        <v>0.1497000008821487</v>
       </c>
       <c r="F135" t="n">
-        <v>0.4061999917030334</v>
+        <v>0.2696999907493591</v>
       </c>
       <c r="G135" t="n">
-        <v>0.2495999932289124</v>
+        <v>0.3621000051498413</v>
       </c>
       <c r="H135" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a111.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a111.jpeg</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4763,25 +4763,25 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.05209999904036522</v>
+        <v>0.03869999945163727</v>
       </c>
       <c r="E136" t="n">
-        <v>0.6159999966621399</v>
+        <v>0.595300018787384</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2159000039100647</v>
+        <v>0.1642999947071075</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1072999984025955</v>
+        <v>0.09269999712705612</v>
       </c>
       <c r="H136" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f14.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f14.jpeg</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4795,25 +4795,25 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.04230000078678131</v>
+        <v>0.05750000104308128</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3253999948501587</v>
+        <v>0.3980999886989594</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2037000060081482</v>
+        <v>0.1687999963760376</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3937000036239624</v>
+        <v>0.4205999970436096</v>
       </c>
       <c r="H137" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a69.jpg</t>
+          <t>c:\ML_Project\test\Angry\a69.jpg</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4827,25 +4827,25 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.03909999877214432</v>
+        <v>0.04010000079870224</v>
       </c>
       <c r="E138" t="n">
-        <v>0.07079999893903732</v>
+        <v>0.08990000188350677</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4864999949932098</v>
+        <v>0.198400005698204</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4032000005245209</v>
+        <v>0.6617000102996826</v>
       </c>
       <c r="H138" t="n">
-        <v>34.7</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h5.jpg</t>
+          <t>c:\ML_Project\test\Happy\h5.jpg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4859,25 +4859,25 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.9125999808311462</v>
+        <v>0.8237000107765198</v>
       </c>
       <c r="E139" t="n">
-        <v>0.06129999831318855</v>
+        <v>0.08749999850988388</v>
       </c>
       <c r="F139" t="n">
-        <v>0.05260000005364418</v>
+        <v>0.06689999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>0.04190000146627426</v>
+        <v>0.06459999829530716</v>
       </c>
       <c r="H139" t="n">
-        <v>94.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h20.jpg</t>
+          <t>c:\ML_Project\test\Happy\h20.jpg</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4891,25 +4891,25 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.9746999740600586</v>
+        <v>0.9524000287055969</v>
       </c>
       <c r="E140" t="n">
-        <v>0.01209999993443489</v>
+        <v>0.02219999954104424</v>
       </c>
       <c r="F140" t="n">
-        <v>0.01290000043809414</v>
+        <v>0.02480000071227551</v>
       </c>
       <c r="G140" t="n">
-        <v>0.01889999955892563</v>
+        <v>0.03810000047087669</v>
       </c>
       <c r="H140" t="n">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s34.webp</t>
+          <t>c:\ML_Project\test\Sad\s34.webp</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4926,22 +4926,22 @@
         <v>0.06629999727010727</v>
       </c>
       <c r="E141" t="n">
-        <v>0.660099983215332</v>
+        <v>0.7685999870300293</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1694000065326691</v>
+        <v>0.1221999973058701</v>
       </c>
       <c r="G141" t="n">
-        <v>0.09210000187158585</v>
+        <v>0.09279999881982803</v>
       </c>
       <c r="H141" t="n">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h39.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h39.jpg</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4955,25 +4955,25 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.9354000091552734</v>
+        <v>0.8615000247955322</v>
       </c>
       <c r="E142" t="n">
-        <v>0.03799999877810478</v>
+        <v>0.08619999885559082</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0463000014424324</v>
+        <v>0.04980000108480453</v>
       </c>
       <c r="G142" t="n">
-        <v>0.05629999935626984</v>
+        <v>0.06970000267028809</v>
       </c>
       <c r="H142" t="n">
-        <v>95.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f50.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f50.jpeg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4987,25 +4987,25 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.5465999841690063</v>
+        <v>0.3494000136852264</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2039999961853027</v>
+        <v>0.2944000065326691</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1165999993681908</v>
+        <v>0.1870999932289124</v>
       </c>
       <c r="G143" t="n">
-        <v>0.1485999971628189</v>
+        <v>0.07670000195503235</v>
       </c>
       <c r="H143" t="n">
-        <v>70.09999999999999</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f101.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f101.jpeg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5019,25 +5019,25 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.05099999904632568</v>
+        <v>0.03819999843835831</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2931999862194061</v>
+        <v>0.5080999732017517</v>
       </c>
       <c r="F144" t="n">
-        <v>0.4169999957084656</v>
+        <v>0.2187000066041946</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1879000067710876</v>
+        <v>0.1756000071763992</v>
       </c>
       <c r="H144" t="n">
-        <v>34.2</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f77.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f77.jpeg</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5051,25 +5051,25 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.05550000071525574</v>
+        <v>0.07900000363588333</v>
       </c>
       <c r="E145" t="n">
-        <v>0.332399994134903</v>
+        <v>0.5236999988555908</v>
       </c>
       <c r="F145" t="n">
-        <v>0.3648999929428101</v>
+        <v>0.3833999931812286</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2140000015497208</v>
+        <v>0.07760000228881836</v>
       </c>
       <c r="H145" t="n">
-        <v>34.3</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h49.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h49.jpg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5083,25 +5083,25 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.9685999751091003</v>
+        <v>0.8288000226020813</v>
       </c>
       <c r="E146" t="n">
-        <v>0.01360000018030405</v>
+        <v>0.07530000060796738</v>
       </c>
       <c r="F146" t="n">
-        <v>0.02470000088214874</v>
+        <v>0.1071999967098236</v>
       </c>
       <c r="G146" t="n">
-        <v>0.02390000037848949</v>
+        <v>0.08049999922513962</v>
       </c>
       <c r="H146" t="n">
-        <v>97.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a6.jpg</t>
+          <t>c:\ML_Project\test\Angry\a6.jpg</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5115,25 +5115,25 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.04690000042319298</v>
+        <v>0.04349999874830246</v>
       </c>
       <c r="E147" t="n">
-        <v>0.07500000298023224</v>
+        <v>0.1703000068664551</v>
       </c>
       <c r="F147" t="n">
-        <v>0.704800009727478</v>
+        <v>0.2316000014543533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.208299994468689</v>
+        <v>0.5802000164985657</v>
       </c>
       <c r="H147" t="n">
-        <v>33.8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s55.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s55.jpeg</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5147,25 +5147,25 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.066600002348423</v>
       </c>
       <c r="E148" t="n">
-        <v>0.7300000190734863</v>
+        <v>0.558899998664856</v>
       </c>
       <c r="F148" t="n">
-        <v>0.066600002348423</v>
+        <v>0.1211000010371208</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2398000061511993</v>
+        <v>0.2861000001430511</v>
       </c>
       <c r="H148" t="n">
-        <v>29.6</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f45.jpg</t>
+          <t>c:\ML_Project\test\Fear\f45.jpg</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5179,25 +5179,25 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.03920000046491623</v>
+        <v>0.07680000364780426</v>
       </c>
       <c r="E149" t="n">
-        <v>0.2966000139713287</v>
+        <v>0.3616000115871429</v>
       </c>
       <c r="F149" t="n">
-        <v>0.05169999971985817</v>
+        <v>0.07479999959468842</v>
       </c>
       <c r="G149" t="n">
-        <v>0.6960999965667725</v>
+        <v>0.5564000010490417</v>
       </c>
       <c r="H149" t="n">
-        <v>33.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f53.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f53.jpeg</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5211,25 +5211,25 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.1836999952793121</v>
+        <v>0.2876999974250793</v>
       </c>
       <c r="E150" t="n">
-        <v>0.2441000044345856</v>
+        <v>0.1420000046491623</v>
       </c>
       <c r="F150" t="n">
-        <v>0.08079999685287476</v>
+        <v>0.2815999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4129999876022339</v>
+        <v>0.2122000008821487</v>
       </c>
       <c r="H150" t="n">
-        <v>46</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f118.webp</t>
+          <t>c:\ML_Project\test\Fear\f118.webp</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5243,25 +5243,25 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.1238999962806702</v>
+        <v>0.1072999984025955</v>
       </c>
       <c r="E151" t="n">
-        <v>0.1058999970555305</v>
+        <v>0.153099998831749</v>
       </c>
       <c r="F151" t="n">
-        <v>0.1439999938011169</v>
+        <v>0.1182999983429909</v>
       </c>
       <c r="G151" t="n">
-        <v>0.5713000297546387</v>
+        <v>0.5745999813079834</v>
       </c>
       <c r="H151" t="n">
-        <v>42.6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f47.jpg</t>
+          <t>c:\ML_Project\test\Fear\f47.jpg</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5275,25 +5275,25 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.03139999881386757</v>
+        <v>0.04280000180006027</v>
       </c>
       <c r="E152" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.4891999959945679</v>
       </c>
       <c r="F152" t="n">
-        <v>0.07999999821186066</v>
+        <v>0.1400000005960464</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4375999867916107</v>
+        <v>0.3433000147342682</v>
       </c>
       <c r="H152" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_download (6).jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_download (6).jpeg</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5307,25 +5307,25 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.03640000149607658</v>
+        <v>0.06750000268220901</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5989000201225281</v>
+        <v>0.6470999717712402</v>
       </c>
       <c r="F153" t="n">
-        <v>0.1269000023603439</v>
+        <v>0.09529999643564224</v>
       </c>
       <c r="G153" t="n">
-        <v>0.2590000033378601</v>
+        <v>0.2458000034093857</v>
       </c>
       <c r="H153" t="n">
-        <v>30.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a99.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a99.jpeg</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5339,25 +5339,25 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.04549999907612801</v>
+        <v>0.08240000158548355</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1215000003576279</v>
+        <v>0.1410000026226044</v>
       </c>
       <c r="F154" t="n">
-        <v>0.7656000256538391</v>
+        <v>0.707099974155426</v>
       </c>
       <c r="G154" t="n">
-        <v>0.1430000066757202</v>
+        <v>0.1397999972105026</v>
       </c>
       <c r="H154" t="n">
-        <v>32.6</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a98.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a98.jpeg</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5371,25 +5371,25 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.1309999972581863</v>
+        <v>0.1101000010967255</v>
       </c>
       <c r="E155" t="n">
-        <v>0.08479999750852585</v>
+        <v>0.2058999985456467</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6973000168800354</v>
+        <v>0.5346999764442444</v>
       </c>
       <c r="G155" t="n">
-        <v>0.149399995803833</v>
+        <v>0.1829999983310699</v>
       </c>
       <c r="H155" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h2.jpg</t>
+          <t>c:\ML_Project\test\Happy\h2.jpg</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5403,25 +5403,25 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.8942999839782715</v>
+        <v>0.852400004863739</v>
       </c>
       <c r="E156" t="n">
-        <v>0.03359999880194664</v>
+        <v>0.05059999972581863</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0357000008225441</v>
+        <v>0.06239999830722809</v>
       </c>
       <c r="G156" t="n">
-        <v>0.07859999686479568</v>
+        <v>0.05959999933838844</v>
       </c>
       <c r="H156" t="n">
-        <v>93.3</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a70.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a70.jpeg</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5435,25 +5435,25 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.04069999977946281</v>
+        <v>0.04509999975562096</v>
       </c>
       <c r="E157" t="n">
-        <v>0.504800021648407</v>
+        <v>0.4532000124454498</v>
       </c>
       <c r="F157" t="n">
-        <v>0.219200000166893</v>
+        <v>0.3436000049114227</v>
       </c>
       <c r="G157" t="n">
-        <v>0.2070000022649765</v>
+        <v>0.1629000008106232</v>
       </c>
       <c r="H157" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h24.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h24.jpg</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5467,25 +5467,25 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.9258000254631042</v>
+        <v>0.7696999907493591</v>
       </c>
       <c r="E158" t="n">
-        <v>0.03130000084638596</v>
+        <v>0.133200004696846</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0153999999165535</v>
+        <v>0.02730000019073486</v>
       </c>
       <c r="G158" t="n">
-        <v>0.04509999975562096</v>
+        <v>0.1064999997615814</v>
       </c>
       <c r="H158" t="n">
-        <v>95.3</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s9.jpg</t>
+          <t>c:\ML_Project\test\Sad\s9.jpg</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5499,25 +5499,25 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.03620000183582306</v>
+        <v>0.1048000007867813</v>
       </c>
       <c r="E159" t="n">
-        <v>0.7918999791145325</v>
+        <v>0.4476000070571899</v>
       </c>
       <c r="F159" t="n">
-        <v>0.09809999912977219</v>
+        <v>0.1262000054121017</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1085999980568886</v>
+        <v>0.3310999870300293</v>
       </c>
       <c r="H159" t="n">
-        <v>29</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a118.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a118.jpeg</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5531,16 +5531,16 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.03700000047683716</v>
+        <v>0.03810000047087669</v>
       </c>
       <c r="E160" t="n">
-        <v>0.04280000180006027</v>
+        <v>0.06210000067949295</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8551999926567078</v>
+        <v>0.8525999784469604</v>
       </c>
       <c r="G160" t="n">
-        <v>0.08879999816417694</v>
+        <v>0.06480000168085098</v>
       </c>
       <c r="H160" t="n">
         <v>32.8</v>
@@ -5549,7 +5549,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a47.jpg</t>
+          <t>c:\ML_Project\test\Angry\a47.jpg</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5563,25 +5563,25 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.05260000005364418</v>
+        <v>0.0544000007212162</v>
       </c>
       <c r="E161" t="n">
-        <v>0.18019999563694</v>
+        <v>0.09189999848604202</v>
       </c>
       <c r="F161" t="n">
-        <v>0.664900004863739</v>
+        <v>0.7942000031471252</v>
       </c>
       <c r="G161" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1186999976634979</v>
       </c>
       <c r="H161" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f57.jpg</t>
+          <t>c:\ML_Project\test\Fear\f57.jpg</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5595,25 +5595,25 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.05869999900460243</v>
+        <v>0.05889999866485596</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1037999987602234</v>
+        <v>0.1195999979972839</v>
       </c>
       <c r="F162" t="n">
-        <v>0.620199978351593</v>
+        <v>0.6365000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>0.211899995803833</v>
+        <v>0.2090000063180923</v>
       </c>
       <c r="H162" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f2.jpg</t>
+          <t>c:\ML_Project\test\Fear\f2.jpg</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5627,25 +5627,25 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.04910000041127205</v>
+        <v>0.05180000141263008</v>
       </c>
       <c r="E163" t="n">
-        <v>0.2268999963998795</v>
+        <v>0.4185999929904938</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5867999792098999</v>
+        <v>0.266400009393692</v>
       </c>
       <c r="G163" t="n">
-        <v>0.09120000153779984</v>
+        <v>0.1413999944925308</v>
       </c>
       <c r="H163" t="n">
-        <v>33.9</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f15.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f15.jpeg</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5659,25 +5659,25 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.03420000150799751</v>
+        <v>0.03770000115036964</v>
       </c>
       <c r="E164" t="n">
-        <v>0.7979999780654907</v>
+        <v>0.7146000266075134</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1821999996900558</v>
+        <v>0.1324999928474426</v>
       </c>
       <c r="G164" t="n">
-        <v>0.09839999675750732</v>
+        <v>0.1333999931812286</v>
       </c>
       <c r="H164" t="n">
-        <v>27.6</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h14.jpg</t>
+          <t>c:\ML_Project\test\Happy\h14.jpg</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5691,25 +5691,25 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.5134999752044678</v>
+        <v>0.2806999981403351</v>
       </c>
       <c r="E165" t="n">
-        <v>0.301499992609024</v>
+        <v>0.4797999858856201</v>
       </c>
       <c r="F165" t="n">
-        <v>0.07150000333786011</v>
+        <v>0.07639999687671661</v>
       </c>
       <c r="G165" t="n">
-        <v>0.08389999717473984</v>
+        <v>0.1456999927759171</v>
       </c>
       <c r="H165" t="n">
-        <v>67.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a10.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a10.jpeg</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5723,25 +5723,25 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.05490000173449516</v>
+        <v>0.08489999920129776</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1992000043392181</v>
+        <v>0.2610999941825867</v>
       </c>
       <c r="F166" t="n">
-        <v>0.2298000007867813</v>
+        <v>0.1435000002384186</v>
       </c>
       <c r="G166" t="n">
-        <v>0.5723999738693237</v>
+        <v>0.6086000204086304</v>
       </c>
       <c r="H166" t="n">
-        <v>35.3</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h84.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h84.jpeg</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5755,25 +5755,25 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.7670999765396118</v>
+        <v>0.6765999794006348</v>
       </c>
       <c r="E167" t="n">
-        <v>0.06509999930858612</v>
+        <v>0.1766999959945679</v>
       </c>
       <c r="F167" t="n">
-        <v>0.01730000041425228</v>
+        <v>0.04199999943375587</v>
       </c>
       <c r="G167" t="n">
-        <v>0.08799999952316284</v>
+        <v>0.1807000041007996</v>
       </c>
       <c r="H167" t="n">
-        <v>85.90000000000001</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s46.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s46.jpeg</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5787,25 +5787,25 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.02889999933540821</v>
+        <v>0.0771000012755394</v>
       </c>
       <c r="E168" t="n">
-        <v>0.8343999981880188</v>
+        <v>0.7297000288963318</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0471000000834465</v>
+        <v>0.1005999967455864</v>
       </c>
       <c r="G168" t="n">
-        <v>0.1054999977350235</v>
+        <v>0.1357000023126602</v>
       </c>
       <c r="H168" t="n">
-        <v>28.5</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h98.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h98.jpeg</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5819,25 +5819,25 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.7928000092506409</v>
+        <v>0.2635999917984009</v>
       </c>
       <c r="E169" t="n">
-        <v>0.05249999836087227</v>
+        <v>0.2232999950647354</v>
       </c>
       <c r="F169" t="n">
-        <v>0.06599999964237213</v>
+        <v>0.3030999898910522</v>
       </c>
       <c r="G169" t="n">
-        <v>0.1931000053882599</v>
+        <v>0.213699996471405</v>
       </c>
       <c r="H169" t="n">
-        <v>86.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h14.jpg</t>
+          <t>c:\ML_Project\test\Happy\h14.jpg</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.5134999752044678</v>
+        <v>0.2806999981403351</v>
       </c>
       <c r="E170" t="n">
-        <v>0.301499992609024</v>
+        <v>0.4797999858856201</v>
       </c>
       <c r="F170" t="n">
-        <v>0.07150000333786011</v>
+        <v>0.07639999687671661</v>
       </c>
       <c r="G170" t="n">
-        <v>0.08389999717473984</v>
+        <v>0.1456999927759171</v>
       </c>
       <c r="H170" t="n">
-        <v>67.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h99.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h99.jpeg</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5883,25 +5883,25 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.8510000109672546</v>
+        <v>0.7896000146865845</v>
       </c>
       <c r="E171" t="n">
-        <v>0.06360000371932983</v>
+        <v>0.1351000070571899</v>
       </c>
       <c r="F171" t="n">
-        <v>0.04490000009536743</v>
+        <v>0.01460000034421682</v>
       </c>
       <c r="G171" t="n">
-        <v>0.09340000152587891</v>
+        <v>0.07590000331401825</v>
       </c>
       <c r="H171" t="n">
-        <v>90.40000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s89.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s89.jpeg</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5915,25 +5915,25 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.01480000000447035</v>
+        <v>0.04010000079870224</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8716999888420105</v>
+        <v>0.7511000037193298</v>
       </c>
       <c r="F172" t="n">
-        <v>0.03159999847412109</v>
+        <v>0.03660000115633011</v>
       </c>
       <c r="G172" t="n">
-        <v>0.1089999973773956</v>
+        <v>0.2971999943256378</v>
       </c>
       <c r="H172" t="n">
-        <v>27</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s55.jpg</t>
+          <t>c:\ML_Project\test\Sad\s55.jpg</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5947,25 +5947,25 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.04250000044703484</v>
+        <v>0.05629999935626984</v>
       </c>
       <c r="E173" t="n">
-        <v>0.5881000161170959</v>
+        <v>0.3935999870300293</v>
       </c>
       <c r="F173" t="n">
-        <v>0.2107000052928925</v>
+        <v>0.296099990606308</v>
       </c>
       <c r="G173" t="n">
-        <v>0.1378999948501587</v>
+        <v>0.1790000051259995</v>
       </c>
       <c r="H173" t="n">
-        <v>31.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f1.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f1.jpeg</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5979,25 +5979,25 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.09669999778270721</v>
+        <v>0.1386999934911728</v>
       </c>
       <c r="E174" t="n">
-        <v>0.214699998497963</v>
+        <v>0.347900003194809</v>
       </c>
       <c r="F174" t="n">
-        <v>0.05229999870061874</v>
+        <v>0.2342000007629395</v>
       </c>
       <c r="G174" t="n">
-        <v>0.6402999758720398</v>
+        <v>0.3280999958515167</v>
       </c>
       <c r="H174" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a42.jpg</t>
+          <t>c:\ML_Project\test\Angry\a42.jpg</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6011,25 +6011,25 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.03750000149011612</v>
+        <v>0.06270000338554382</v>
       </c>
       <c r="E175" t="n">
-        <v>0.09279999881982803</v>
+        <v>0.150299996137619</v>
       </c>
       <c r="F175" t="n">
-        <v>0.7073000073432922</v>
+        <v>0.5315999984741211</v>
       </c>
       <c r="G175" t="n">
-        <v>0.1264999955892563</v>
+        <v>0.2313999980688095</v>
       </c>
       <c r="H175" t="n">
-        <v>33.6</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f5.jpg</t>
+          <t>c:\ML_Project\test\Fear\f5.jpg</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6043,25 +6043,25 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.08139999955892563</v>
+        <v>0.09549999982118607</v>
       </c>
       <c r="E176" t="n">
-        <v>0.1483999937772751</v>
+        <v>0.1291999965906143</v>
       </c>
       <c r="F176" t="n">
-        <v>0.5442000031471252</v>
+        <v>0.7196999788284302</v>
       </c>
       <c r="G176" t="n">
-        <v>0.1228000000119209</v>
+        <v>0.1127000004053116</v>
       </c>
       <c r="H176" t="n">
-        <v>37.7</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a78.jpg</t>
+          <t>c:\ML_Project\test\Angry\a78.jpg</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6075,25 +6075,25 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.07440000027418137</v>
+        <v>0.0820000022649765</v>
       </c>
       <c r="E177" t="n">
-        <v>0.2849000096321106</v>
+        <v>0.1260000020265579</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5526999831199646</v>
+        <v>0.7580999732017517</v>
       </c>
       <c r="G177" t="n">
-        <v>0.1755000054836273</v>
+        <v>0.1133999973535538</v>
       </c>
       <c r="H177" t="n">
-        <v>34</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f36.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f36.jpeg</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6107,25 +6107,25 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.0478999987244606</v>
+        <v>0.08389999717473984</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1688999980688095</v>
+        <v>0.1676999926567078</v>
       </c>
       <c r="F178" t="n">
-        <v>0.1410000026226044</v>
+        <v>0.1257999986410141</v>
       </c>
       <c r="G178" t="n">
-        <v>0.6955000162124634</v>
+        <v>0.7566999793052673</v>
       </c>
       <c r="H178" t="n">
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f51.jpg</t>
+          <t>c:\ML_Project\test\Fear\f51.jpg</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6139,25 +6139,25 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.02940000034868717</v>
+        <v>0.03220000118017197</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1728000044822693</v>
+        <v>0.3059999942779541</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1017000004649162</v>
+        <v>0.04010000079870224</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6951000094413757</v>
+        <v>0.6960999965667725</v>
       </c>
       <c r="H179" t="n">
-        <v>34.9</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h68.jpg</t>
+          <t>c:\ML_Project\test\Happy\h68.jpg</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6171,25 +6171,25 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.9029999971389771</v>
+        <v>0.8896999955177307</v>
       </c>
       <c r="E180" t="n">
-        <v>0.04610000178217888</v>
+        <v>0.04500000178813934</v>
       </c>
       <c r="F180" t="n">
-        <v>0.05719999969005585</v>
+        <v>0.06319999694824219</v>
       </c>
       <c r="G180" t="n">
-        <v>0.02730000019073486</v>
+        <v>0.03889999911189079</v>
       </c>
       <c r="H180" t="n">
-        <v>93.7</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s79.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s79.jpeg</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6203,25 +6203,25 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.01600000075995922</v>
+        <v>0.04149999842047691</v>
       </c>
       <c r="E181" t="n">
-        <v>0.2518999874591827</v>
+        <v>0.1750999987125397</v>
       </c>
       <c r="F181" t="n">
-        <v>0.05539999902248383</v>
+        <v>0.0535999983549118</v>
       </c>
       <c r="G181" t="n">
-        <v>0.7332000136375427</v>
+        <v>0.7768999934196472</v>
       </c>
       <c r="H181" t="n">
-        <v>32.8</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_images (54).jpg</t>
+          <t>c:\ML_Project\test\Happy\new_images (54).jpg</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6235,25 +6235,25 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.9351999759674072</v>
+        <v>0.8454999923706055</v>
       </c>
       <c r="E182" t="n">
-        <v>0.03070000000298023</v>
+        <v>0.09520000219345093</v>
       </c>
       <c r="F182" t="n">
-        <v>0.02749999985098839</v>
+        <v>0.05240000039339066</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0364999994635582</v>
+        <v>0.05070000141859055</v>
       </c>
       <c r="H182" t="n">
-        <v>95.8</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f36.jpg</t>
+          <t>c:\ML_Project\test\Fear\f36.jpg</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6267,25 +6267,25 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.01439999975264072</v>
+        <v>0.03559999912977219</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1880999952554703</v>
+        <v>0.1782000064849854</v>
       </c>
       <c r="F183" t="n">
-        <v>0.03429999947547913</v>
+        <v>0.04340000078082085</v>
       </c>
       <c r="G183" t="n">
-        <v>0.843500018119812</v>
+        <v>0.8396000266075134</v>
       </c>
       <c r="H183" t="n">
-        <v>33.2</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a51.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a51.jpeg</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6299,25 +6299,25 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.03449999913573265</v>
+        <v>0.05490000173449516</v>
       </c>
       <c r="E184" t="n">
-        <v>0.1301999986171722</v>
+        <v>0.324999988079071</v>
       </c>
       <c r="F184" t="n">
-        <v>0.2474000006914139</v>
+        <v>0.2158000022172928</v>
       </c>
       <c r="G184" t="n">
-        <v>0.5975000262260437</v>
+        <v>0.4320000112056732</v>
       </c>
       <c r="H184" t="n">
-        <v>34.9</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_klk.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_klk.jpeg</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6331,25 +6331,25 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.01779999956488609</v>
+        <v>0.04439999908208847</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1468999981880188</v>
+        <v>0.2838000059127808</v>
       </c>
       <c r="F185" t="n">
-        <v>0.06539999693632126</v>
+        <v>0.06960000097751617</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8159999847412109</v>
+        <v>0.7164000272750854</v>
       </c>
       <c r="H185" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_images (47).jpg</t>
+          <t>c:\ML_Project\test\Happy\new_images (47).jpg</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6363,25 +6363,25 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.09640000015497208</v>
+        <v>0.158500000834465</v>
       </c>
       <c r="E186" t="n">
-        <v>0.6696000099182129</v>
+        <v>0.5375999808311462</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1102000027894974</v>
+        <v>0.1946000009775162</v>
       </c>
       <c r="G186" t="n">
-        <v>0.06369999796152115</v>
+        <v>0.09610000252723694</v>
       </c>
       <c r="H186" t="n">
-        <v>35.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s32.jpg</t>
+          <t>c:\ML_Project\test\Sad\s32.jpg</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6395,25 +6395,25 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.01810000091791153</v>
+        <v>0.04010000079870224</v>
       </c>
       <c r="E187" t="n">
-        <v>0.7250000238418579</v>
+        <v>0.6718000173568726</v>
       </c>
       <c r="F187" t="n">
-        <v>0.03220000118017197</v>
+        <v>0.06390000134706497</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2576000094413757</v>
+        <v>0.2685999870300293</v>
       </c>
       <c r="H187" t="n">
-        <v>28.6</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Fear\f46.jpg</t>
+          <t>c:\ML_Project\test\Fear\f46.jpg</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6427,25 +6427,25 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.048700001090765</v>
+        <v>0.06539999693632126</v>
       </c>
       <c r="E188" t="n">
-        <v>0.03400000184774399</v>
+        <v>0.08720000088214874</v>
       </c>
       <c r="F188" t="n">
-        <v>0.3472000062465668</v>
+        <v>0.2545999884605408</v>
       </c>
       <c r="G188" t="n">
-        <v>0.59579998254776</v>
+        <v>0.7627999782562256</v>
       </c>
       <c r="H188" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a87.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a87.jpeg</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6459,25 +6459,25 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.06069999933242798</v>
+        <v>0.04820000007748604</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2754000127315521</v>
+        <v>0.2583000063896179</v>
       </c>
       <c r="F189" t="n">
-        <v>0.515500009059906</v>
+        <v>0.4663999974727631</v>
       </c>
       <c r="G189" t="n">
-        <v>0.1046999990940094</v>
+        <v>0.1630000025033951</v>
       </c>
       <c r="H189" t="n">
-        <v>34.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a7.jpg</t>
+          <t>c:\ML_Project\test\Angry\a7.jpg</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6491,25 +6491,25 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.01439999975264072</v>
+        <v>0.04500000178813934</v>
       </c>
       <c r="E190" t="n">
-        <v>0.5996999740600586</v>
+        <v>0.503000020980835</v>
       </c>
       <c r="F190" t="n">
-        <v>0.09830000251531601</v>
+        <v>0.2802999913692474</v>
       </c>
       <c r="G190" t="n">
-        <v>0.2026000022888184</v>
+        <v>0.1422999948263168</v>
       </c>
       <c r="H190" t="n">
-        <v>30.4</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s110.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s110.jpeg</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6523,25 +6523,25 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.03739999979734421</v>
+        <v>0.05869999900460243</v>
       </c>
       <c r="E191" t="n">
-        <v>0.359499990940094</v>
+        <v>0.3795000016689301</v>
       </c>
       <c r="F191" t="n">
-        <v>0.2741000056266785</v>
+        <v>0.3346999883651733</v>
       </c>
       <c r="G191" t="n">
-        <v>0.1692000031471252</v>
+        <v>0.1333999931812286</v>
       </c>
       <c r="H191" t="n">
-        <v>34.4</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h47.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h47.jpg</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6555,25 +6555,25 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.9684000015258789</v>
+        <v>0.9316999912261963</v>
       </c>
       <c r="E192" t="n">
-        <v>0.01940000057220459</v>
+        <v>0.0421999990940094</v>
       </c>
       <c r="F192" t="n">
-        <v>0.022299999371171</v>
+        <v>0.03099999949336052</v>
       </c>
       <c r="G192" t="n">
-        <v>0.02510000020265579</v>
+        <v>0.03759999945759773</v>
       </c>
       <c r="H192" t="n">
-        <v>97.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s48.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s48.jpeg</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6587,25 +6587,25 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.04080000147223473</v>
+        <v>0.06650000065565109</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4630999863147736</v>
+        <v>0.3420000076293945</v>
       </c>
       <c r="F193" t="n">
-        <v>0.2540000081062317</v>
+        <v>0.3251999914646149</v>
       </c>
       <c r="G193" t="n">
-        <v>0.1611000001430511</v>
+        <v>0.1829999983310699</v>
       </c>
       <c r="H193" t="n">
-        <v>32.9</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_images (1).jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_images (1).jpeg</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6619,25 +6619,25 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.04199999943375587</v>
+        <v>0.05229999870061874</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1793999969959259</v>
+        <v>0.4336999952793121</v>
       </c>
       <c r="F194" t="n">
-        <v>0.2879999876022339</v>
+        <v>0.185699999332428</v>
       </c>
       <c r="G194" t="n">
-        <v>0.4113999903202057</v>
+        <v>0.3138999938964844</v>
       </c>
       <c r="H194" t="n">
-        <v>35.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a22.jpg</t>
+          <t>c:\ML_Project\test\Angry\a22.jpg</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6651,25 +6651,25 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.03030000068247318</v>
+        <v>0.03350000083446503</v>
       </c>
       <c r="E195" t="n">
-        <v>0.07980000227689743</v>
+        <v>0.1255999952554703</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7123000025749207</v>
+        <v>0.59170001745224</v>
       </c>
       <c r="G195" t="n">
-        <v>0.1448000073432922</v>
+        <v>0.2076999992132187</v>
       </c>
       <c r="H195" t="n">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s103.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s103.jpeg</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6683,25 +6683,25 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.06729999929666519</v>
+        <v>0.06669999659061432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3833000063896179</v>
+        <v>0.4984999895095825</v>
       </c>
       <c r="F196" t="n">
-        <v>0.03700000047683716</v>
+        <v>0.03299999982118607</v>
       </c>
       <c r="G196" t="n">
-        <v>0.5221999883651733</v>
+        <v>0.5533999800682068</v>
       </c>
       <c r="H196" t="n">
-        <v>35.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\h83.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h83.jpeg</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6715,25 +6715,25 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.6399000287055969</v>
+        <v>0.583299994468689</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2036000043153763</v>
+        <v>0.2976999878883362</v>
       </c>
       <c r="F197" t="n">
-        <v>0.02969999983906746</v>
+        <v>0.1066000014543533</v>
       </c>
       <c r="G197" t="n">
-        <v>0.1013000011444092</v>
+        <v>0.1190000027418137</v>
       </c>
       <c r="H197" t="n">
-        <v>76.8</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s84.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s84.jpeg</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6747,25 +6747,25 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.03079999983310699</v>
+        <v>0.048700001090765</v>
       </c>
       <c r="E198" t="n">
-        <v>0.7839999794960022</v>
+        <v>0.6980999708175659</v>
       </c>
       <c r="F198" t="n">
-        <v>0.06669999659061432</v>
+        <v>0.08370000123977661</v>
       </c>
       <c r="G198" t="n">
-        <v>0.19480000436306</v>
+        <v>0.2124000042676926</v>
       </c>
       <c r="H198" t="n">
-        <v>28.4</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s81.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s81.jpeg</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6779,25 +6779,25 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.01810000091791153</v>
+        <v>0.02769999951124191</v>
       </c>
       <c r="E199" t="n">
-        <v>0.7788000106811523</v>
+        <v>0.7662000060081482</v>
       </c>
       <c r="F199" t="n">
-        <v>0.03130000084638596</v>
+        <v>0.03460000082850456</v>
       </c>
       <c r="G199" t="n">
-        <v>0.1955000013113022</v>
+        <v>0.1483000069856644</v>
       </c>
       <c r="H199" t="n">
-        <v>28.2</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s77.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s77.jpeg</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6811,25 +6811,25 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.1508000046014786</v>
+        <v>0.1344999969005585</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3206000030040741</v>
+        <v>0.2759999930858612</v>
       </c>
       <c r="F200" t="n">
-        <v>0.2263000011444092</v>
+        <v>0.3327000141143799</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2334000021219254</v>
+        <v>0.1492000073194504</v>
       </c>
       <c r="H200" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a26.jpg</t>
+          <t>c:\ML_Project\test\Angry\a26.jpg</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6843,25 +6843,25 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.09880000352859497</v>
+        <v>0.0786999985575676</v>
       </c>
       <c r="E201" t="n">
-        <v>0.1720999926328659</v>
+        <v>0.1076999977231026</v>
       </c>
       <c r="F201" t="n">
-        <v>0.6657999753952026</v>
+        <v>0.7603999972343445</v>
       </c>
       <c r="G201" t="n">
-        <v>0.1272000074386597</v>
+        <v>0.09830000251531601</v>
       </c>
       <c r="H201" t="n">
-        <v>36.6</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s50.jpg</t>
+          <t>c:\ML_Project\test\Sad\s50.jpg</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6875,25 +6875,25 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.0333000011742115</v>
+        <v>0.03480000048875809</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3240000009536743</v>
+        <v>0.5401999950408936</v>
       </c>
       <c r="F202" t="n">
-        <v>0.4289999902248383</v>
+        <v>0.2547999918460846</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1650000065565109</v>
+        <v>0.1835999935865402</v>
       </c>
       <c r="H202" t="n">
-        <v>32.6</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s50.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s50.jpeg</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6907,25 +6907,25 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.2522999942302704</v>
+        <v>0.1309999972581863</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3258999884128571</v>
+        <v>0.4417000114917755</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1490000039339066</v>
+        <v>0.1946000009775162</v>
       </c>
       <c r="G203" t="n">
-        <v>0.1074000000953674</v>
+        <v>0.2345999926328659</v>
       </c>
       <c r="H203" t="n">
-        <v>50.5</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a23.jpg</t>
+          <t>c:\ML_Project\test\Angry\a23.jpg</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6939,25 +6939,25 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.04540000110864639</v>
+        <v>0.04470000043511391</v>
       </c>
       <c r="E204" t="n">
-        <v>0.09860000014305115</v>
+        <v>0.2397000044584274</v>
       </c>
       <c r="F204" t="n">
-        <v>0.4555000066757202</v>
+        <v>0.3055999875068665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.3398999869823456</v>
+        <v>0.4524999856948853</v>
       </c>
       <c r="H204" t="n">
-        <v>35.6</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Happy\new_h29.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h29.jpg</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6971,25 +6971,25 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.6097999811172485</v>
+        <v>0.5297999978065491</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1211000010371208</v>
+        <v>0.1164999976754189</v>
       </c>
       <c r="F205" t="n">
-        <v>0.1561000049114227</v>
+        <v>0.1459999978542328</v>
       </c>
       <c r="G205" t="n">
-        <v>0.1546999961137772</v>
+        <v>0.1685000061988831</v>
       </c>
       <c r="H205" t="n">
-        <v>74.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\new_a38.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a38.jpeg</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7003,25 +7003,25 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.3352000117301941</v>
+        <v>0.124600000679493</v>
       </c>
       <c r="E206" t="n">
-        <v>0.02190000005066395</v>
+        <v>0.06469999998807907</v>
       </c>
       <c r="F206" t="n">
-        <v>0.6363000273704529</v>
+        <v>0.7020000219345093</v>
       </c>
       <c r="G206" t="n">
-        <v>0.09560000151395798</v>
+        <v>0.1523000001907349</v>
       </c>
       <c r="H206" t="n">
-        <v>54.7</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s83.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s83.jpeg</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7035,25 +7035,25 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.1781000047922134</v>
+        <v>0.1437000036239624</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3240000009536743</v>
+        <v>0.5530999898910522</v>
       </c>
       <c r="F207" t="n">
-        <v>0.02319999970495701</v>
+        <v>0.03229999914765358</v>
       </c>
       <c r="G207" t="n">
-        <v>0.3393999934196472</v>
+        <v>0.258899986743927</v>
       </c>
       <c r="H207" t="n">
-        <v>45.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s10.jpg</t>
+          <t>c:\ML_Project\test\Sad\s10.jpg</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7067,25 +7067,25 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.124099999666214</v>
+        <v>0.07429999858140945</v>
       </c>
       <c r="E208" t="n">
-        <v>0.5084999799728394</v>
+        <v>0.7310000061988831</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1023999974131584</v>
+        <v>0.1825000047683716</v>
       </c>
       <c r="G208" t="n">
-        <v>0.160300001502037</v>
+        <v>0.08070000261068344</v>
       </c>
       <c r="H208" t="n">
-        <v>39.5</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a79.jpg</t>
+          <t>c:\ML_Project\test\Angry\a79.jpg</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7099,25 +7099,25 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.04080000147223473</v>
+        <v>0.08590000122785568</v>
       </c>
       <c r="E209" t="n">
-        <v>0.06809999793767929</v>
+        <v>0.06300000101327896</v>
       </c>
       <c r="F209" t="n">
-        <v>0.6784999966621399</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="G209" t="n">
-        <v>0.2269999980926514</v>
+        <v>0.1887000054121017</v>
       </c>
       <c r="H209" t="n">
-        <v>33.8</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s115.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s115.jpeg</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7131,25 +7131,25 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.04850000143051147</v>
+        <v>0.06289999932050705</v>
       </c>
       <c r="E210" t="n">
-        <v>0.8429999947547913</v>
+        <v>0.8294000029563904</v>
       </c>
       <c r="F210" t="n">
-        <v>0.06549999862909317</v>
+        <v>0.06759999692440033</v>
       </c>
       <c r="G210" t="n">
-        <v>0.09489999711513519</v>
+        <v>0.1059999987483025</v>
       </c>
       <c r="H210" t="n">
-        <v>29.4</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Sad\s33.jpg</t>
+          <t>c:\ML_Project\test\Sad\s33.jpg</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7163,25 +7163,25 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.03290000185370445</v>
+        <v>0.0601000003516674</v>
       </c>
       <c r="E211" t="n">
-        <v>0.8587999939918518</v>
+        <v>0.7102000117301941</v>
       </c>
       <c r="F211" t="n">
-        <v>0.04820000007748604</v>
+        <v>0.1508000046014786</v>
       </c>
       <c r="G211" t="n">
-        <v>0.07199999690055847</v>
+        <v>0.1172000020742416</v>
       </c>
       <c r="H211" t="n">
-        <v>28.6</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h26.jpg</t>
+          <t>c:\ML_Project\test\Happy\h26.jpg</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7195,25 +7195,25 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.6901000142097473</v>
+        <v>0.8125</v>
       </c>
       <c r="E212" t="n">
-        <v>0.1184000000357628</v>
+        <v>0.1050999984145164</v>
       </c>
       <c r="F212" t="n">
-        <v>0.03779999911785126</v>
+        <v>0.02889999933540821</v>
       </c>
       <c r="G212" t="n">
-        <v>0.1433999985456467</v>
+        <v>0.05570000037550926</v>
       </c>
       <c r="H212" t="n">
-        <v>80.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\new_f30.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f30.jpeg</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7227,25 +7227,25 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.06669999659061432</v>
+        <v>0.05370000004768372</v>
       </c>
       <c r="E213" t="n">
-        <v>0.2354000061750412</v>
+        <v>0.2845999896526337</v>
       </c>
       <c r="F213" t="n">
-        <v>0.1696999967098236</v>
+        <v>0.1049000024795532</v>
       </c>
       <c r="G213" t="n">
-        <v>0.5164999961853027</v>
+        <v>0.5453000068664551</v>
       </c>
       <c r="H213" t="n">
-        <v>36.7</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Fear\f31.jpg</t>
+          <t>c:\ML_Project\test\Fear\f31.jpg</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7259,25 +7259,25 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.06449999660253525</v>
+        <v>0.1011999994516373</v>
       </c>
       <c r="E214" t="n">
-        <v>0.1749999970197678</v>
+        <v>0.3190999925136566</v>
       </c>
       <c r="F214" t="n">
-        <v>0.1976999938488007</v>
+        <v>0.1156999990344048</v>
       </c>
       <c r="G214" t="n">
-        <v>0.5672000050544739</v>
+        <v>0.497299998998642</v>
       </c>
       <c r="H214" t="n">
-        <v>36.9</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\new_s6.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s6.jpg</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7291,25 +7291,25 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.05810000002384186</v>
+        <v>0.1438000053167343</v>
       </c>
       <c r="E215" t="n">
-        <v>0.603600025177002</v>
+        <v>0.2922999858856201</v>
       </c>
       <c r="F215" t="n">
-        <v>0.1840000003576279</v>
+        <v>0.4512999951839447</v>
       </c>
       <c r="G215" t="n">
-        <v>0.1186000034213066</v>
+        <v>0.09669999778270721</v>
       </c>
       <c r="H215" t="n">
-        <v>32.7</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a37.jpg</t>
+          <t>c:\ML_Project\test\Angry\a37.jpg</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7323,25 +7323,25 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.2651999890804291</v>
+        <v>0.05270000174641609</v>
       </c>
       <c r="E216" t="n">
-        <v>0.245399996638298</v>
+        <v>0.7075999975204468</v>
       </c>
       <c r="F216" t="n">
-        <v>0.2001000046730042</v>
+        <v>0.151199996471405</v>
       </c>
       <c r="G216" t="n">
-        <v>0.1743000000715256</v>
+        <v>0.1028999984264374</v>
       </c>
       <c r="H216" t="n">
-        <v>51.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Happy\h91.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h91.jpeg</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7355,25 +7355,25 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.8709999918937683</v>
+        <v>0.7836999893188477</v>
       </c>
       <c r="E217" t="n">
-        <v>0.02669999934732914</v>
+        <v>0.05649999901652336</v>
       </c>
       <c r="F217" t="n">
-        <v>0.03599999845027924</v>
+        <v>0.08299999684095383</v>
       </c>
       <c r="G217" t="n">
-        <v>0.1272999942302704</v>
+        <v>0.08039999753236771</v>
       </c>
       <c r="H217" t="n">
-        <v>91.8</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Angry\a71.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a71.jpeg</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7387,25 +7387,25 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.02969999983906746</v>
+        <v>0.06120000034570694</v>
       </c>
       <c r="E218" t="n">
-        <v>0.7423999905586243</v>
+        <v>0.4119000136852264</v>
       </c>
       <c r="F218" t="n">
-        <v>0.1456000059843063</v>
+        <v>0.2233999967575073</v>
       </c>
       <c r="G218" t="n">
-        <v>0.08959999680519104</v>
+        <v>0.2072000056505203</v>
       </c>
       <c r="H218" t="n">
-        <v>29</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a50.jpg</t>
+          <t>c:\ML_Project\test\Angry\a50.jpg</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7419,25 +7419,25 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.04170000180602074</v>
+        <v>0.07599999755620956</v>
       </c>
       <c r="E219" t="n">
-        <v>0.240899994969368</v>
+        <v>0.1481000036001205</v>
       </c>
       <c r="F219" t="n">
-        <v>0.5618000030517578</v>
+        <v>0.6151999831199646</v>
       </c>
       <c r="G219" t="n">
-        <v>0.125900000333786</v>
+        <v>0.1495999991893768</v>
       </c>
       <c r="H219" t="n">
-        <v>33.2</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a51.jpg</t>
+          <t>c:\ML_Project\test\Angry\a51.jpg</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7451,25 +7451,25 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.1490000039339066</v>
+        <v>0.178399994969368</v>
       </c>
       <c r="E220" t="n">
-        <v>0.1630000025033951</v>
+        <v>0.2205000072717667</v>
       </c>
       <c r="F220" t="n">
-        <v>0.373199999332428</v>
+        <v>0.3337000012397766</v>
       </c>
       <c r="G220" t="n">
-        <v>0.121799997985363</v>
+        <v>0.1030000001192093</v>
       </c>
       <c r="H220" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a100.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a100.jpeg</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7483,25 +7483,25 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.2273000031709671</v>
+        <v>0.3890999853610992</v>
       </c>
       <c r="E221" t="n">
-        <v>0.1435000002384186</v>
+        <v>0.1710000038146973</v>
       </c>
       <c r="F221" t="n">
-        <v>0.4140999913215637</v>
+        <v>0.2795999944210052</v>
       </c>
       <c r="G221" t="n">
-        <v>0.2081000059843063</v>
+        <v>0.1221000030636787</v>
       </c>
       <c r="H221" t="n">
-        <v>47.9</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\NewArts2\NewArts2\Angry\a94.webp</t>
+          <t>c:\ML_Project\test\Angry\a94.webp</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7515,25 +7515,25 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.04650000110268593</v>
+        <v>0.07150000333786011</v>
       </c>
       <c r="E222" t="n">
-        <v>0.1568000018596649</v>
+        <v>0.1978999972343445</v>
       </c>
       <c r="F222" t="n">
-        <v>0.6190999746322632</v>
+        <v>0.7408999800682068</v>
       </c>
       <c r="G222" t="n">
-        <v>0.2587000131607056</v>
+        <v>0.09319999814033508</v>
       </c>
       <c r="H222" t="n">
-        <v>33</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C:\Users\borad\.cache\kagglehub\datasets\vishmiperera\children-drawings\versions\1\data\Sad\s45.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s45.jpeg</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7547,19 +7547,19 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.2240000069141388</v>
+        <v>0.1488000005483627</v>
       </c>
       <c r="E223" t="n">
-        <v>0.4289000034332275</v>
+        <v>0.5906999707221985</v>
       </c>
       <c r="F223" t="n">
-        <v>0.1044000014662743</v>
+        <v>0.160400003194809</v>
       </c>
       <c r="G223" t="n">
-        <v>0.1070000007748604</v>
+        <v>0.06629999727010727</v>
       </c>
       <c r="H223" t="n">
-        <v>47.6</v>
+        <v>39.6</v>
       </c>
     </row>
   </sheetData>

--- a/test_predictions.xlsx
+++ b/test_predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05389999970793724</v>
+        <v>0.06340000033378601</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2470999956130981</v>
+        <v>0.2307000011205673</v>
       </c>
       <c r="F2" t="n">
-        <v>0.453000009059906</v>
+        <v>0.3458000123500824</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1978999972343445</v>
+        <v>0.2928999960422516</v>
       </c>
       <c r="H2" t="n">
-        <v>34.7</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="3">
@@ -507,19 +507,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.08940000087022781</v>
+        <v>0.08209999650716782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1588000059127808</v>
+        <v>0.244499996304512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4891999959945679</v>
+        <v>0.2302999943494797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2337999939918518</v>
+        <v>0.4695000052452087</v>
       </c>
       <c r="H3" t="n">
-        <v>37.8</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="4">
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3149999976158142</v>
+        <v>0.382999986410141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2234999984502792</v>
+        <v>0.1533000022172928</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1524000018835068</v>
+        <v>0.1616999953985214</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3621000051498413</v>
+        <v>0.3359000086784363</v>
       </c>
       <c r="H4" t="n">
-        <v>53.9</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="5">
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.04919999837875366</v>
+        <v>0.07029999792575836</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2676999866962433</v>
+        <v>0.4366999864578247</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2648000121116638</v>
+        <v>0.2849000096321106</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3143999874591827</v>
+        <v>0.2511000037193298</v>
       </c>
       <c r="H5" t="n">
-        <v>35.6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.03209999948740005</v>
+        <v>0.04509999975562096</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04780000075697899</v>
+        <v>0.1416999995708466</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9054999947547913</v>
+        <v>0.5702999830245972</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0333000011742115</v>
+        <v>0.1779000014066696</v>
       </c>
       <c r="H6" t="n">
-        <v>32.2</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3707000017166138</v>
+        <v>0.4968000054359436</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2529000043869019</v>
+        <v>0.2427999973297119</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1492000073194504</v>
+        <v>0.1800000071525574</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1636999994516373</v>
+        <v>0.2089000046253204</v>
       </c>
       <c r="H7" t="n">
-        <v>58.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3361000120639801</v>
+        <v>0.5329999923706055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.130500003695488</v>
+        <v>0.2099000066518784</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2016000002622604</v>
+        <v>0.152199998497963</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2496999949216843</v>
+        <v>0.2904999852180481</v>
       </c>
       <c r="H8" t="n">
-        <v>57</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -699,19 +699,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.03400000184774399</v>
+        <v>0.1506000012159348</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3059000074863434</v>
+        <v>0.2949999868869781</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1105000004172325</v>
+        <v>0.1180000007152557</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5080000162124634</v>
+        <v>0.4806999862194061</v>
       </c>
       <c r="H9" t="n">
-        <v>34.3</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="10">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8421000242233276</v>
+        <v>0.8183000087738037</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07940000295639038</v>
+        <v>0.06639999896287918</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1121999993920326</v>
+        <v>0.07859999686479568</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08579999953508377</v>
+        <v>0.08789999783039093</v>
       </c>
       <c r="H10" t="n">
-        <v>89.3</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="11">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05579999834299088</v>
+        <v>0.0255999993532896</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1678999960422516</v>
+        <v>0.1136000007390976</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6574000120162964</v>
+        <v>0.7113999724388123</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09040000289678574</v>
+        <v>0.0697999969124794</v>
       </c>
       <c r="H11" t="n">
-        <v>34.4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7445999979972839</v>
+        <v>0.9211000204086304</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1596000045537949</v>
+        <v>0.01370000001043081</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02539999969303608</v>
+        <v>0.01620000042021275</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1429000049829483</v>
+        <v>0.03180000185966492</v>
       </c>
       <c r="H12" t="n">
-        <v>83.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="13">
@@ -827,19 +827,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01970000006258488</v>
+        <v>0.0234999991953373</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7943999767303467</v>
+        <v>0.6407999992370605</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06580000370740891</v>
+        <v>0.1225999966263771</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1993000060319901</v>
+        <v>0.1766999959945679</v>
       </c>
       <c r="H13" t="n">
-        <v>27.4</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="14">
@@ -859,19 +859,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07490000128746033</v>
+        <v>0.07180000096559525</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1414999961853027</v>
+        <v>0.2001000046730042</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2454999983310699</v>
+        <v>0.3671000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6360999941825867</v>
+        <v>0.4079999923706055</v>
       </c>
       <c r="H14" t="n">
-        <v>36.8</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="15">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04899999871850014</v>
+        <v>0.1055999994277954</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1994999945163727</v>
+        <v>0.3792999982833862</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1692000031471252</v>
+        <v>0.2759000062942505</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5539000034332275</v>
+        <v>0.3267000019550323</v>
       </c>
       <c r="H15" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="16">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1023999974131584</v>
+        <v>0.08709999918937683</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1040000021457672</v>
+        <v>0.1456999927759171</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7547000050544739</v>
+        <v>0.619700014591217</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09570000320672989</v>
+        <v>0.1088000014424324</v>
       </c>
       <c r="H16" t="n">
         <v>37.2</v>
@@ -955,19 +955,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1220000013709068</v>
+        <v>0.1097000017762184</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2971999943256378</v>
+        <v>0.4478000104427338</v>
       </c>
       <c r="F17" t="n">
-        <v>0.35589998960495</v>
+        <v>0.1419000029563904</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2948000133037567</v>
+        <v>0.4187999963760376</v>
       </c>
       <c r="H17" t="n">
-        <v>38.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="18">
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02690000087022781</v>
+        <v>0.06419999897480011</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6812000274658203</v>
+        <v>0.5864999890327454</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01640000008046627</v>
+        <v>0.07490000128746033</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4954000115394592</v>
+        <v>0.3084000051021576</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="19">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9318000078201294</v>
+        <v>0.788100004196167</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02459999918937683</v>
+        <v>0.07360000163316727</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0414000004529953</v>
+        <v>0.07079999893903732</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02449999935925007</v>
+        <v>0.07230000197887421</v>
       </c>
       <c r="H19" t="n">
-        <v>95.7</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.7537000179290771</v>
+        <v>0.8151999711990356</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1099999994039536</v>
+        <v>0.0575999990105629</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08429999649524689</v>
+        <v>0.07249999791383743</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07819999754428864</v>
+        <v>0.08079999685287476</v>
       </c>
       <c r="H20" t="n">
-        <v>84.09999999999999</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="21">
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.02859999984502792</v>
+        <v>0.06310000270605087</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2224999964237213</v>
+        <v>0.1881999969482422</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2928000092506409</v>
+        <v>0.2870000004768372</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3452000021934509</v>
+        <v>0.4526999890804291</v>
       </c>
       <c r="H21" t="n">
-        <v>34.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="22">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9276999831199646</v>
+        <v>0.9120000004768372</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04980000108480453</v>
+        <v>0.02160000056028366</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02180000022053719</v>
+        <v>0.03269999846816063</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.03220000118017197</v>
       </c>
       <c r="H22" t="n">
-        <v>95.3</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.03970000147819519</v>
+        <v>0.06300000101327896</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4086999893188477</v>
+        <v>0.2894999980926514</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1923000067472458</v>
+        <v>0.4456000030040741</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3170000016689301</v>
+        <v>0.2240000069141388</v>
       </c>
       <c r="H23" t="n">
-        <v>33.3</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="24">
@@ -1179,19 +1179,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1518000066280365</v>
+        <v>0.1494999974966049</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4496999979019165</v>
+        <v>0.2671000063419342</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3145999908447266</v>
+        <v>0.3684000074863434</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1105000004172325</v>
+        <v>0.411300003528595</v>
       </c>
       <c r="H24" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="25">
@@ -1211,19 +1211,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1437000036239624</v>
+        <v>0.1229000017046928</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5530999898910522</v>
+        <v>0.3420000076293945</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03229999914765358</v>
+        <v>0.03750000149011612</v>
       </c>
       <c r="G25" t="n">
-        <v>0.258899986743927</v>
+        <v>0.3355000019073486</v>
       </c>
       <c r="H25" t="n">
-        <v>40</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="26">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.445499986410141</v>
+        <v>0.7696999907493591</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1200999990105629</v>
+        <v>0.08370000123977661</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1659999936819077</v>
+        <v>0.1357000023126602</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2703999876976013</v>
+        <v>0.09719999879598618</v>
       </c>
       <c r="H26" t="n">
-        <v>63.9</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="27">
@@ -1275,19 +1275,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1868000030517578</v>
+        <v>0.1497000008821487</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1703999936580658</v>
+        <v>0.1858000010251999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5694000124931335</v>
+        <v>0.5472999811172485</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08470000326633453</v>
+        <v>0.1855999976396561</v>
       </c>
       <c r="H27" t="n">
-        <v>43.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="28">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.4172999858856201</v>
+        <v>0.7601000070571899</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1541000008583069</v>
+        <v>0.0560000017285347</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3998999893665314</v>
+        <v>0.08150000125169754</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07639999687671661</v>
+        <v>0.1154000014066696</v>
       </c>
       <c r="H28" t="n">
-        <v>60.6</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.06350000202655792</v>
+        <v>0.03970000147819519</v>
       </c>
       <c r="E29" t="n">
-        <v>0.760699987411499</v>
+        <v>0.7560999989509583</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1230000033974648</v>
+        <v>0.08590000122785568</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0966000035405159</v>
+        <v>0.1301999986171722</v>
       </c>
       <c r="H29" t="n">
-        <v>31.2</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="30">
@@ -1371,19 +1371,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9575999975204468</v>
+        <v>0.8655999898910522</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01439999975264072</v>
+        <v>0.03720000013709068</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01720000058412552</v>
+        <v>0.04969999939203262</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01970000006258488</v>
+        <v>0.05299999937415123</v>
       </c>
       <c r="H30" t="n">
-        <v>97.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.04399999976158142</v>
+        <v>0.05770000070333481</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.6330000162124634</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07199999690055847</v>
+        <v>0.1999000012874603</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2047999948263168</v>
+        <v>0.1412999927997589</v>
       </c>
       <c r="H31" t="n">
-        <v>28.2</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="32">
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.07150000333786011</v>
+        <v>0.06310000270605087</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06459999829530716</v>
+        <v>0.08730000257492065</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8319000005722046</v>
+        <v>0.6159999966621399</v>
       </c>
       <c r="G32" t="n">
-        <v>0.101000003516674</v>
+        <v>0.198400005698204</v>
       </c>
       <c r="H32" t="n">
-        <v>34.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.02969999983906746</v>
+        <v>0.02740000002086163</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06639999896287918</v>
+        <v>0.1904000043869019</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05719999969005585</v>
+        <v>0.1835999935865402</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8554999828338623</v>
+        <v>0.4672000110149384</v>
       </c>
       <c r="H33" t="n">
-        <v>36.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="34">
@@ -1499,19 +1499,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.04250000044703484</v>
+        <v>0.08810000121593475</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3901999890804291</v>
+        <v>0.2883999943733215</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04690000042319298</v>
+        <v>0.1572999954223633</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6891999840736389</v>
+        <v>0.4914999902248383</v>
       </c>
       <c r="H34" t="n">
-        <v>32.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="35">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.04679999873042107</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6718000173568726</v>
+        <v>0.7074000239372253</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06390000134706497</v>
+        <v>0.1128000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2685999870300293</v>
+        <v>0.1869000047445297</v>
       </c>
       <c r="H35" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="36">
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.02969999983906746</v>
+        <v>0.02060000039637089</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6711999773979187</v>
+        <v>0.6963000297546387</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1027999967336655</v>
+        <v>0.0786999985575676</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1614000052213669</v>
+        <v>0.1705999970436096</v>
       </c>
       <c r="H36" t="n">
-        <v>30.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="37">
@@ -1595,19 +1595,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.09309999644756317</v>
+        <v>0.03959999978542328</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4560999870300293</v>
+        <v>0.241799995303154</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1494999974966049</v>
+        <v>0.2903000116348267</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4077000021934509</v>
+        <v>0.3151000142097473</v>
       </c>
       <c r="H37" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="38">
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.03739999979734421</v>
+        <v>0.1002999991178513</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3700000047683716</v>
+        <v>0.4061999917030334</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07760000228881836</v>
+        <v>0.2352000027894974</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4643000066280365</v>
+        <v>0.3248000144958496</v>
       </c>
       <c r="H38" t="n">
-        <v>34.1</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="39">
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.8736000061035156</v>
+        <v>0.9272000193595886</v>
       </c>
       <c r="E39" t="n">
-        <v>0.05290000140666962</v>
+        <v>0.01310000009834766</v>
       </c>
       <c r="F39" t="n">
-        <v>0.03810000047087669</v>
+        <v>0.01569999940693378</v>
       </c>
       <c r="G39" t="n">
-        <v>0.09030000120401382</v>
+        <v>0.0296000000089407</v>
       </c>
       <c r="H39" t="n">
-        <v>91.8</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.07289999723434448</v>
+        <v>0.6055999994277954</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4241000115871429</v>
+        <v>0.1022000014781952</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2267999947071075</v>
+        <v>0.1395000070333481</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2310999929904938</v>
+        <v>0.1317999958992004</v>
       </c>
       <c r="H40" t="n">
-        <v>35.4</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="41">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.07599999755620956</v>
+        <v>0.07180000096559525</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1481000036001205</v>
+        <v>0.3339999914169312</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6151999831199646</v>
+        <v>0.4618000090122223</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1495999991893768</v>
+        <v>0.2087000012397766</v>
       </c>
       <c r="H41" t="n">
-        <v>36.1</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="42">
@@ -1755,19 +1755,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.7777000069618225</v>
+        <v>0.8341000080108643</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1145000010728836</v>
+        <v>0.05900000035762787</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04769999906420708</v>
+        <v>0.0632999986410141</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0632999986410141</v>
+        <v>0.09269999712705612</v>
       </c>
       <c r="H42" t="n">
-        <v>85.8</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="43">
@@ -1787,19 +1787,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.07119999825954437</v>
+        <v>0.09749999642372131</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3310999870300293</v>
+        <v>0.3420000076293945</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4056999981403351</v>
+        <v>0.2138999998569489</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2308000028133392</v>
+        <v>0.4577000141143799</v>
       </c>
       <c r="H43" t="n">
-        <v>34.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="44">
@@ -1819,19 +1819,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.04019999876618385</v>
+        <v>0.06080000102519989</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6987000107765198</v>
+        <v>0.6463000178337097</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08550000190734863</v>
+        <v>0.09870000183582306</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1833000034093857</v>
+        <v>0.1608999967575073</v>
       </c>
       <c r="H44" t="n">
-        <v>30.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="45">
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.04509999975562096</v>
+        <v>0.1204999983310699</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4451999962329865</v>
+        <v>0.2375999987125397</v>
       </c>
       <c r="F45" t="n">
-        <v>0.07810000330209732</v>
+        <v>0.2698000073432922</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5329999923706055</v>
+        <v>0.5663999915122986</v>
       </c>
       <c r="H45" t="n">
-        <v>32.5</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="46">
@@ -1883,19 +1883,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.05319999903440475</v>
+        <v>0.0778999999165535</v>
       </c>
       <c r="E46" t="n">
-        <v>0.07129999995231628</v>
+        <v>0.1583999991416931</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4474999904632568</v>
+        <v>0.5324000120162964</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3325000107288361</v>
+        <v>0.3122000098228455</v>
       </c>
       <c r="H46" t="n">
-        <v>36.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="47">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0502999983727932</v>
+        <v>0.01530000008642673</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2549999952316284</v>
+        <v>0.2696999907493591</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5608999729156494</v>
+        <v>0.332399994134903</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1606999933719635</v>
+        <v>0.2120999991893768</v>
       </c>
       <c r="H47" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="48">
@@ -1947,19 +1947,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.05370000004768372</v>
+        <v>0.03799999877810478</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1124999970197678</v>
+        <v>0.09160000085830688</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8471000194549561</v>
+        <v>0.7576000094413757</v>
       </c>
       <c r="G48" t="n">
-        <v>0.05579999834299088</v>
+        <v>0.09510000050067902</v>
       </c>
       <c r="H48" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="49">
@@ -1979,19 +1979,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.1327999979257584</v>
+        <v>0.1326999962329865</v>
       </c>
       <c r="E49" t="n">
-        <v>0.06989999860525131</v>
+        <v>0.1155999973416328</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7075999975204468</v>
+        <v>0.5885999798774719</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1278000026941299</v>
+        <v>0.2250999957323074</v>
       </c>
       <c r="H49" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -2011,19 +2011,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.8740000128746033</v>
+        <v>0.7712000012397766</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03700000047683716</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06939999759197235</v>
+        <v>0.1017000004649162</v>
       </c>
       <c r="G50" t="n">
-        <v>0.04879999905824661</v>
+        <v>0.1225000023841858</v>
       </c>
       <c r="H50" t="n">
-        <v>92</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.05229999870061874</v>
+        <v>0.02370000071823597</v>
       </c>
       <c r="E51" t="n">
-        <v>0.07410000264644623</v>
+        <v>0.1040999963879585</v>
       </c>
       <c r="F51" t="n">
-        <v>0.262800008058548</v>
+        <v>0.05950000137090683</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6079999804496765</v>
+        <v>0.6553999781608582</v>
       </c>
       <c r="H51" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="52">
@@ -2075,19 +2075,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.07769999653100967</v>
+        <v>0.1014999970793724</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5552999973297119</v>
+        <v>0.488999992609024</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3397000133991241</v>
+        <v>0.3890999853610992</v>
       </c>
       <c r="G52" t="n">
-        <v>0.09109999984502792</v>
+        <v>0.1559000015258789</v>
       </c>
       <c r="H52" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="53">
@@ -2107,19 +2107,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.04839999973773956</v>
+        <v>0.03790000081062317</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3379000127315521</v>
+        <v>0.3032999932765961</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06440000236034393</v>
+        <v>0.1978999972343445</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5710999965667725</v>
+        <v>0.3846000134944916</v>
       </c>
       <c r="H53" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="54">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.04019999876618385</v>
+        <v>0.1014999970793724</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1163000017404556</v>
+        <v>0.2093999981880188</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2102999985218048</v>
+        <v>0.5060999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6442999839782715</v>
+        <v>0.2714999914169312</v>
       </c>
       <c r="H54" t="n">
-        <v>35.6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55">
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.05180000141263008</v>
+        <v>0.1138999983668327</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4185999929904938</v>
+        <v>0.258899986743927</v>
       </c>
       <c r="F55" t="n">
-        <v>0.266400009393692</v>
+        <v>0.432200014591217</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1413999944925308</v>
+        <v>0.2782999873161316</v>
       </c>
       <c r="H55" t="n">
-        <v>34.5</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="56">
@@ -2203,19 +2203,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.8216000199317932</v>
+        <v>0.8269000053405762</v>
       </c>
       <c r="E56" t="n">
-        <v>0.06459999829530716</v>
+        <v>0.07270000129938126</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06679999828338623</v>
+        <v>0.09070000052452087</v>
       </c>
       <c r="G56" t="n">
-        <v>0.08410000056028366</v>
+        <v>0.07890000194311142</v>
       </c>
       <c r="H56" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="57">
@@ -2235,19 +2235,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.04259999841451645</v>
+        <v>0.03940000012516975</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4395999908447266</v>
+        <v>0.5472000241279602</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2277999967336655</v>
+        <v>0.1764000058174133</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3203000128269196</v>
+        <v>0.2581999897956848</v>
       </c>
       <c r="H57" t="n">
-        <v>32.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="58">
@@ -2267,19 +2267,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1553000062704086</v>
+        <v>0.1174999997019768</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3305999934673309</v>
+        <v>0.322299987077713</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2460999935865402</v>
+        <v>0.335999995470047</v>
       </c>
       <c r="G58" t="n">
-        <v>0.324400007724762</v>
+        <v>0.301800012588501</v>
       </c>
       <c r="H58" t="n">
-        <v>41.3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.824999988079071</v>
+        <v>0.7875000238418579</v>
       </c>
       <c r="E59" t="n">
-        <v>0.08860000222921371</v>
+        <v>0.1068999990820885</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06449999660253525</v>
+        <v>0.06379999965429306</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08429999649524689</v>
+        <v>0.1089000031352043</v>
       </c>
       <c r="H59" t="n">
-        <v>88.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2331,19 +2331,19 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0357000008225441</v>
+        <v>0.1033999994397163</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5144000053405762</v>
+        <v>0.2397000044584274</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1330000013113022</v>
+        <v>0.3057000041007996</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2858999967575073</v>
+        <v>0.4772000014781952</v>
       </c>
       <c r="H60" t="n">
-        <v>32.1</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="61">
@@ -2363,19 +2363,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.647599995136261</v>
+        <v>0.7021999955177307</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2236000001430511</v>
+        <v>0.1203000023961067</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1036999970674515</v>
+        <v>0.09589999914169312</v>
       </c>
       <c r="G61" t="n">
-        <v>0.09200000017881393</v>
+        <v>0.09480000287294388</v>
       </c>
       <c r="H61" t="n">
-        <v>76.40000000000001</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="62">
@@ -2395,19 +2395,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.05499999970197678</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1361999958753586</v>
+        <v>0.1351000070571899</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2148000001907349</v>
+        <v>0.2370000034570694</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5978999733924866</v>
+        <v>0.5315999984741211</v>
       </c>
       <c r="H62" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="63">
@@ -2427,19 +2427,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1062999963760376</v>
+        <v>0.1914000064134598</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2736000120639801</v>
+        <v>0.1964000016450882</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5974000096321106</v>
+        <v>0.3743000030517578</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1149000003933907</v>
+        <v>0.2272000014781952</v>
       </c>
       <c r="H63" t="n">
-        <v>36.3</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="64">
@@ -2459,94 +2459,94 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.07900000363588333</v>
+        <v>0.1885000020265579</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5236999988555908</v>
+        <v>0.3188000023365021</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3833999931812286</v>
+        <v>0.3646000027656555</v>
       </c>
       <c r="G64" t="n">
-        <v>0.07760000228881836</v>
+        <v>0.2883000075817108</v>
       </c>
       <c r="H64" t="n">
-        <v>33.1</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a88.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s74.png</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>a88.jpeg</t>
+          <t>s74.png</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1023999974131584</v>
+        <v>0.07249999791383743</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1040000021457672</v>
+        <v>0.2919999957084656</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7547000050544739</v>
+        <v>0.4704999923706055</v>
       </c>
       <c r="G65" t="n">
-        <v>0.09570000320672989</v>
+        <v>0.2119999974966049</v>
       </c>
       <c r="H65" t="n">
-        <v>37.2</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s74.png</t>
+          <t>c:\ML_Project\test\Happy\h16.jpg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>s74.png</t>
+          <t>h16.jpg</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.101000003516674</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="E66" t="n">
-        <v>0.160400003194809</v>
+        <v>0.05270000174641609</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2851000130176544</v>
+        <v>0.05380000174045563</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4041999876499176</v>
+        <v>0.06260000169277191</v>
       </c>
       <c r="H66" t="n">
-        <v>39.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h16.jpg</t>
+          <t>c:\ML_Project\test\Happy\h70.jpg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>h16.jpg</t>
+          <t>h70.jpg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2558,27 +2558,27 @@
         <v>0.8278999924659729</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1036999970674515</v>
+        <v>0.06880000233650208</v>
       </c>
       <c r="F67" t="n">
-        <v>0.05200000107288361</v>
+        <v>0.06539999693632126</v>
       </c>
       <c r="G67" t="n">
-        <v>0.08860000222921371</v>
+        <v>0.09759999811649323</v>
       </c>
       <c r="H67" t="n">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h70.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h45.jpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>h70.jpg</t>
+          <t>new_h45.jpg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2587,30 +2587,30 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.8460999727249146</v>
+        <v>0.4402999877929688</v>
       </c>
       <c r="E68" t="n">
-        <v>0.04940000176429749</v>
+        <v>0.07859999686479568</v>
       </c>
       <c r="F68" t="n">
-        <v>0.06949999928474426</v>
+        <v>0.05040000006556511</v>
       </c>
       <c r="G68" t="n">
-        <v>0.04100000113248825</v>
+        <v>0.2831999957561493</v>
       </c>
       <c r="H68" t="n">
-        <v>90.3</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h45.jpg</t>
+          <t>c:\ML_Project\test\Happy\h30.jpg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>new_h45.jpg</t>
+          <t>h30.jpg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2619,94 +2619,94 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.6245999932289124</v>
+        <v>0.7396000027656555</v>
       </c>
       <c r="E69" t="n">
-        <v>0.08190000057220459</v>
+        <v>0.1142999976873398</v>
       </c>
       <c r="F69" t="n">
-        <v>0.05689999833703041</v>
+        <v>0.09730000048875809</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2334000021219254</v>
+        <v>0.1307000070810318</v>
       </c>
       <c r="H69" t="n">
-        <v>76.3</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h30.jpg</t>
+          <t>c:\ML_Project\test\Fear\f78.jpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>h30.jpg</t>
+          <t>f78.jpg</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.8087000250816345</v>
+        <v>0.02610000036656857</v>
       </c>
       <c r="E70" t="n">
-        <v>0.09849999845027924</v>
+        <v>0.05959999933838844</v>
       </c>
       <c r="F70" t="n">
-        <v>0.07320000231266022</v>
+        <v>0.6992999911308289</v>
       </c>
       <c r="G70" t="n">
-        <v>0.08900000154972076</v>
+        <v>0.1348000019788742</v>
       </c>
       <c r="H70" t="n">
-        <v>87.40000000000001</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f78.jpg</t>
+          <t>c:\ML_Project\test\Angry\a55.jpeg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>f78.jpg</t>
+          <t>a55.jpeg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.04650000110268593</v>
+        <v>0.0494999997317791</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0877000018954277</v>
+        <v>0.3230000138282776</v>
       </c>
       <c r="F71" t="n">
-        <v>0.83160001039505</v>
+        <v>0.4690000116825104</v>
       </c>
       <c r="G71" t="n">
-        <v>0.07779999822378159</v>
+        <v>0.1826000064611435</v>
       </c>
       <c r="H71" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a55.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a46.jpeg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>a55.jpeg</t>
+          <t>new_a46.jpeg</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2715,94 +2715,94 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0544000007212162</v>
+        <v>0.06310000270605087</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1480000019073486</v>
+        <v>0.1407999992370605</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7138000130653381</v>
+        <v>0.2549999952316284</v>
       </c>
       <c r="G72" t="n">
-        <v>0.06780000030994415</v>
+        <v>0.5279999971389771</v>
       </c>
       <c r="H72" t="n">
-        <v>34.1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\new_a46.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f9.jpg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>new_a46.jpeg</t>
+          <t>f9.jpg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.09759999811649323</v>
+        <v>0.04210000112652779</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1572999954223633</v>
+        <v>0.6804999709129333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2047999948263168</v>
+        <v>0.1800000071525574</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5964999794960022</v>
+        <v>0.1476999968290329</v>
       </c>
       <c r="H73" t="n">
-        <v>38.9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f9.jpg</t>
+          <t>c:\ML_Project\test\Sad\s76.jpeg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>f9.jpg</t>
+          <t>s76.jpeg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.05490000173449516</v>
+        <v>0.06260000169277191</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6532999873161316</v>
+        <v>0.5604000091552734</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2383999973535538</v>
+        <v>0.05909999832510948</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1054999977350235</v>
+        <v>0.3334999978542328</v>
       </c>
       <c r="H74" t="n">
-        <v>30.9</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h43.jpg</t>
+          <t>c:\ML_Project\test\Happy\h6.jpg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>h43.jpg</t>
+          <t>h6.jpg</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2811,30 +2811,30 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.824999988079071</v>
+        <v>0.7296000123023987</v>
       </c>
       <c r="E75" t="n">
-        <v>0.08860000222921371</v>
+        <v>0.08479999750852585</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06449999660253525</v>
+        <v>0.1308999955654144</v>
       </c>
       <c r="G75" t="n">
-        <v>0.08429999649524689</v>
+        <v>0.1242000013589859</v>
       </c>
       <c r="H75" t="n">
-        <v>88.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s76.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s97.jpeg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>s76.jpeg</t>
+          <t>s97.jpeg</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2843,126 +2843,126 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.1096000000834465</v>
+        <v>0.1158000007271767</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.6007999777793884</v>
       </c>
       <c r="F76" t="n">
-        <v>0.02740000002086163</v>
+        <v>0.1074000000953674</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3939999938011169</v>
+        <v>0.122299998998642</v>
       </c>
       <c r="H76" t="n">
-        <v>38</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h6.jpg</t>
+          <t>c:\ML_Project\test\Sad\s71.jpeg</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>h6.jpg</t>
+          <t>s71.jpeg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.7692999839782715</v>
+        <v>0.1076000034809113</v>
       </c>
       <c r="E77" t="n">
-        <v>0.05579999834299088</v>
+        <v>0.6126000285148621</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03759999945759773</v>
+        <v>0.1756999939680099</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1115999966859818</v>
+        <v>0.2917999923229218</v>
       </c>
       <c r="H77" t="n">
-        <v>85.8</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s97.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f17.jpg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>s97.jpeg</t>
+          <t>f17.jpg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.1488000005483627</v>
+        <v>0.03950000181794167</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5906000137329102</v>
+        <v>0.4532999992370605</v>
       </c>
       <c r="F78" t="n">
-        <v>0.160400003194809</v>
+        <v>0.0828000009059906</v>
       </c>
       <c r="G78" t="n">
-        <v>0.06629999727010727</v>
+        <v>0.3580000102519989</v>
       </c>
       <c r="H78" t="n">
-        <v>39.6</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s71.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h92.jpeg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>s71.jpeg</t>
+          <t>h92.jpeg</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.06159999966621399</v>
+        <v>0.7124000191688538</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7333999872207642</v>
+        <v>0.1094999983906746</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07559999823570251</v>
+        <v>0.1042999997735023</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1931000053882599</v>
+        <v>0.1237000003457069</v>
       </c>
       <c r="H79" t="n">
-        <v>31.3</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f17.jpg</t>
+          <t>c:\ML_Project\test\Fear\f24.jpg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>f17.jpg</t>
+          <t>f24.jpg</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2971,190 +2971,190 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.06549999862909317</v>
+        <v>0.1055999994277954</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3603000044822693</v>
+        <v>0.3792999982833862</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1218999996781349</v>
+        <v>0.2759000062942505</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4411999881267548</v>
+        <v>0.3267000019550323</v>
       </c>
       <c r="H80" t="n">
-        <v>35.7</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h92.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s36.jpg</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>h92.jpeg</t>
+          <t>s36.jpg</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.7408999800682068</v>
+        <v>0.09830000251531601</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1762000024318695</v>
+        <v>0.3898999989032745</v>
       </c>
       <c r="F81" t="n">
-        <v>0.04479999840259552</v>
+        <v>0.3298999965190887</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1089999973773956</v>
+        <v>0.3088000118732452</v>
       </c>
       <c r="H81" t="n">
-        <v>82.8</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f24.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h50.jpg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f24.jpg</t>
+          <t>new_h50.jpg</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.04899999871850014</v>
+        <v>0.4079000055789948</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1994999945163727</v>
+        <v>0.2919000089168549</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1692000031471252</v>
+        <v>0.1421999931335449</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5539000034332275</v>
+        <v>0.1763000041246414</v>
       </c>
       <c r="H82" t="n">
-        <v>36</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s36.jpg</t>
+          <t>c:\ML_Project\test\Fear\f92.jpeg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>s36.jpg</t>
+          <t>f92.jpeg</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.08680000156164169</v>
+        <v>0.04600000008940697</v>
       </c>
       <c r="E83" t="n">
-        <v>0.402099996805191</v>
+        <v>0.5698999762535095</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2651000022888184</v>
+        <v>0.2777999937534332</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2211000025272369</v>
+        <v>0.1465999931097031</v>
       </c>
       <c r="H83" t="n">
-        <v>36.3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h50.jpg</t>
+          <t>c:\ML_Project\test\Fear\f117.jpeg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>new_h50.jpg</t>
+          <t>f117.jpeg</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.3731000125408173</v>
+        <v>0.3610999882221222</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2721999883651733</v>
+        <v>0.385699987411499</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2847999930381775</v>
+        <v>0.08889999985694885</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1212000027298927</v>
+        <v>0.1915999948978424</v>
       </c>
       <c r="H84" t="n">
-        <v>57</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f92.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s8.jpg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>f92.jpeg</t>
+          <t>s8.jpg</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.02089999988675117</v>
+        <v>0.01700000092387199</v>
       </c>
       <c r="E85" t="n">
-        <v>0.5952000021934509</v>
+        <v>0.7630000114440918</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1118000000715256</v>
+        <v>0.07100000232458115</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1406999975442886</v>
+        <v>0.1263000071048737</v>
       </c>
       <c r="H85" t="n">
-        <v>31.4</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f117.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f2.png</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>f117.jpeg</t>
+          <t>new_f2.png</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3163,30 +3163,30 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.1394000053405762</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6445000171661377</v>
+        <v>0.159400001168251</v>
       </c>
       <c r="F86" t="n">
-        <v>0.08009999990463257</v>
+        <v>0.1647000014781952</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2442999929189682</v>
+        <v>0.1085999980568886</v>
       </c>
       <c r="H86" t="n">
-        <v>37.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s8.jpg</t>
+          <t>c:\ML_Project\test\Sad\s53.jpeg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>s8.jpg</t>
+          <t>s53.jpeg</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3195,126 +3195,126 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.02119999937713146</v>
+        <v>0.03929999843239784</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7872999906539917</v>
+        <v>0.4894999861717224</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1464000046253204</v>
+        <v>0.0348999984562397</v>
       </c>
       <c r="G87" t="n">
-        <v>0.06589999794960022</v>
+        <v>0.3919000029563904</v>
       </c>
       <c r="H87" t="n">
-        <v>27.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f2.png</t>
+          <t>c:\ML_Project\test\Sad\new_s46.jpeg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>new_f2.png</t>
+          <t>new_s46.jpeg</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.6784999966621399</v>
+        <v>0.1570000052452087</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1853999942541122</v>
+        <v>0.299699991941452</v>
       </c>
       <c r="F88" t="n">
-        <v>0.08389999717473984</v>
+        <v>0.2626999914646149</v>
       </c>
       <c r="G88" t="n">
-        <v>0.06520000100135803</v>
+        <v>0.3779999911785126</v>
       </c>
       <c r="H88" t="n">
-        <v>79</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s53.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a84.jpeg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>s53.jpeg</t>
+          <t>a84.jpeg</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.1102999970316887</v>
+        <v>0.07429999858140945</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4253999888896942</v>
+        <v>0.1738000065088272</v>
       </c>
       <c r="F89" t="n">
-        <v>0.05229999870061874</v>
+        <v>0.5055999755859375</v>
       </c>
       <c r="G89" t="n">
-        <v>0.3959999978542328</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="H89" t="n">
-        <v>38.7</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_s46.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f99.jpeg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>new_s46.jpeg</t>
+          <t>f99.jpeg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.2284000068902969</v>
+        <v>0.05539999902248383</v>
       </c>
       <c r="E90" t="n">
-        <v>0.07729999721050262</v>
+        <v>0.1372999995946884</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3260000050067902</v>
+        <v>0.08139999955892563</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4108000099658966</v>
+        <v>0.59579998254776</v>
       </c>
       <c r="H90" t="n">
-        <v>48.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a84.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a43.jpg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>a84.jpeg</t>
+          <t>a43.jpg</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3323,30 +3323,30 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.09669999778270721</v>
+        <v>0.03840000182390213</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1516000032424927</v>
+        <v>0.09910000115633011</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6665999889373779</v>
+        <v>0.7045000195503235</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1552000045776367</v>
+        <v>0.1465999931097031</v>
       </c>
       <c r="H91" t="n">
-        <v>36.6</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f99.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f33.jpg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>f99.jpeg</t>
+          <t>f33.jpg</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3355,158 +3355,158 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.06719999760389328</v>
+        <v>0.03109999932348728</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2216999977827072</v>
+        <v>0.1968999952077866</v>
       </c>
       <c r="F92" t="n">
-        <v>0.04149999842047691</v>
+        <v>0.2773999869823456</v>
       </c>
       <c r="G92" t="n">
-        <v>0.7610999941825867</v>
+        <v>0.3698000013828278</v>
       </c>
       <c r="H92" t="n">
-        <v>36.5</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a43.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h17.jpg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>a43.jpg</t>
+          <t>new_h17.jpg</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.08590000122785568</v>
+        <v>0.8633999824523926</v>
       </c>
       <c r="E93" t="n">
-        <v>0.06300000101327896</v>
+        <v>0.04699999839067459</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6700000166893005</v>
+        <v>0.04729999974370003</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1886000037193298</v>
+        <v>0.05840000137686729</v>
       </c>
       <c r="H93" t="n">
-        <v>37.2</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f33.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h34.jpg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>f33.jpg</t>
+          <t>new_h34.jpg</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.05730000138282776</v>
+        <v>0.6359000205993652</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3707999885082245</v>
+        <v>0.1395000070333481</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1177000030875206</v>
+        <v>0.09640000015497208</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4444000124931335</v>
+        <v>0.158500000834465</v>
       </c>
       <c r="H94" t="n">
-        <v>35</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h17.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s11.jpg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>new_h17.jpg</t>
+          <t>new_s11.jpg</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.9617000222206116</v>
+        <v>0.02910000085830688</v>
       </c>
       <c r="E95" t="n">
-        <v>0.01119999960064888</v>
+        <v>0.1088000014424324</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01669999957084656</v>
+        <v>0.0348999984562397</v>
       </c>
       <c r="G95" t="n">
-        <v>0.01950000040233135</v>
+        <v>0.6455000042915344</v>
       </c>
       <c r="H95" t="n">
-        <v>97.59999999999999</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h34.jpg</t>
+          <t>c:\ML_Project\test\Sad\s36.jpeg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>new_h34.jpg</t>
+          <t>s36.jpeg</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.6223999857902527</v>
+        <v>0.1385000050067902</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2172999978065491</v>
+        <v>0.3770000040531158</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1141000017523766</v>
+        <v>0.1643999963998795</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1103999987244606</v>
+        <v>0.4070000052452087</v>
       </c>
       <c r="H96" t="n">
-        <v>74.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_s11.jpg</t>
+          <t>c:\ML_Project\test\Sad\s25.jpg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>new_s11.jpg</t>
+          <t>s25.jpg</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3515,222 +3515,222 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.07190000265836716</v>
+        <v>0.0632999986410141</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1870000064373016</v>
+        <v>0.7063000202178955</v>
       </c>
       <c r="F97" t="n">
-        <v>0.08399999886751175</v>
+        <v>0.09099999815225601</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6326000094413757</v>
+        <v>0.1763000041246414</v>
       </c>
       <c r="H97" t="n">
-        <v>38.1</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s36.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a110.jpeg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>s36.jpeg</t>
+          <t>a110.jpeg</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.03999999910593033</v>
+        <v>0.0255999993532896</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4390000104904175</v>
+        <v>0.7817000150680542</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02569999918341637</v>
+        <v>0.05009999871253967</v>
       </c>
       <c r="G98" t="n">
-        <v>0.6133999824523926</v>
+        <v>0.1119000017642975</v>
       </c>
       <c r="H98" t="n">
-        <v>32.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s25.jpg</t>
+          <t>c:\ML_Project\test\Angry\a56.jpeg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>s25.jpg</t>
+          <t>a56.jpeg</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.05730000138282776</v>
+        <v>0.0892999991774559</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8464000225067139</v>
+        <v>0.07940000295639038</v>
       </c>
       <c r="F99" t="n">
-        <v>0.07580000162124634</v>
+        <v>0.6671000123023987</v>
       </c>
       <c r="G99" t="n">
-        <v>0.05579999834299088</v>
+        <v>0.1186999976634979</v>
       </c>
       <c r="H99" t="n">
-        <v>30.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a110.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f64.jpg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>a110.jpeg</t>
+          <t>f64.jpg</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.03950000181794167</v>
+        <v>0.05530000105500221</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8260999917984009</v>
+        <v>0.5842000246047974</v>
       </c>
       <c r="F100" t="n">
-        <v>0.05559999868273735</v>
+        <v>0.06809999793767929</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1331000030040741</v>
+        <v>0.2904999852180481</v>
       </c>
       <c r="H100" t="n">
-        <v>28.9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a56.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f15.jpg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>a56.jpeg</t>
+          <t>f15.jpg</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.06880000233650208</v>
+        <v>0.08219999819993973</v>
       </c>
       <c r="E101" t="n">
-        <v>0.06849999725818634</v>
+        <v>0.1888999938964844</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8619999885559082</v>
+        <v>0.4160000085830688</v>
       </c>
       <c r="G101" t="n">
-        <v>0.05660000070929527</v>
+        <v>0.4187999963760376</v>
       </c>
       <c r="H101" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h25.jpg</t>
+          <t>c:\ML_Project\test\Fear\f17.jpeg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>h25.jpg</t>
+          <t>f17.jpeg</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.3707000017166138</v>
+        <v>0.03130000084638596</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2529000043869019</v>
+        <v>0.7813000082969666</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1492000073194504</v>
+        <v>0.06219999864697456</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1636999994516373</v>
+        <v>0.1339000016450882</v>
       </c>
       <c r="H102" t="n">
-        <v>58.4</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f64.jpg</t>
+          <t>c:\ML_Project\test\Happy\h53.jpg</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>f64.jpg</t>
+          <t>h53.jpg</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.0885000005364418</v>
+        <v>0.7786999940872192</v>
       </c>
       <c r="E103" t="n">
-        <v>0.5449000000953674</v>
+        <v>0.08139999955892563</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1160999983549118</v>
+        <v>0.06729999929666519</v>
       </c>
       <c r="G103" t="n">
-        <v>0.367000013589859</v>
+        <v>0.133200004696846</v>
       </c>
       <c r="H103" t="n">
-        <v>34.4</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f15.jpg</t>
+          <t>c:\ML_Project\test\Fear\f3.jpg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>f15.jpg</t>
+          <t>f3.jpg</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3739,62 +3739,62 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.04129999876022339</v>
+        <v>0.07999999821186066</v>
       </c>
       <c r="E104" t="n">
-        <v>0.08799999952316284</v>
+        <v>0.3127000033855438</v>
       </c>
       <c r="F104" t="n">
-        <v>0.4034999907016754</v>
+        <v>0.3402000069618225</v>
       </c>
       <c r="G104" t="n">
-        <v>0.4126999974250793</v>
+        <v>0.2387000024318695</v>
       </c>
       <c r="H104" t="n">
-        <v>35.6</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f17.jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a22.jpeg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>f17.jpeg</t>
+          <t>new_a22.jpeg</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.05880000069737434</v>
+        <v>0.02439999952912331</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7678999900817871</v>
+        <v>0.1097000017762184</v>
       </c>
       <c r="F105" t="n">
-        <v>0.07970000058412552</v>
+        <v>0.6315000057220459</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1112999990582466</v>
+        <v>0.1406999975442886</v>
       </c>
       <c r="H105" t="n">
-        <v>31.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h53.jpg</t>
+          <t>c:\ML_Project\test\Happy\h83.jpeg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>h53.jpg</t>
+          <t>h83.jpeg</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3803,62 +3803,62 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.7642999887466431</v>
+        <v>0.6251999735832214</v>
       </c>
       <c r="E106" t="n">
-        <v>0.07299999892711639</v>
+        <v>0.1544000059366226</v>
       </c>
       <c r="F106" t="n">
-        <v>0.07599999755620956</v>
+        <v>0.04399999976158142</v>
       </c>
       <c r="G106" t="n">
-        <v>0.118199996650219</v>
+        <v>0.08829999715089798</v>
       </c>
       <c r="H106" t="n">
-        <v>85</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f3.jpg</t>
+          <t>c:\ML_Project\test\Happy\h56.jpg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>f3.jpg</t>
+          <t>h56.jpg</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.03480000048875809</v>
+        <v>0.4803999960422516</v>
       </c>
       <c r="E107" t="n">
-        <v>0.5401999950408936</v>
+        <v>0.2295999974012375</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2547999918460846</v>
+        <v>0.0608999989926815</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1835999935865402</v>
+        <v>0.2071000039577484</v>
       </c>
       <c r="H107" t="n">
-        <v>30.8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\new_a22.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a80.jpeg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>new_a22.jpeg</t>
+          <t>a80.jpeg</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3867,94 +3867,94 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.02219999954104424</v>
+        <v>0.06570000201463699</v>
       </c>
       <c r="E108" t="n">
-        <v>0.05790000036358833</v>
+        <v>0.162200003862381</v>
       </c>
       <c r="F108" t="n">
-        <v>0.843999981880188</v>
+        <v>0.4435000121593475</v>
       </c>
       <c r="G108" t="n">
-        <v>0.04210000112652779</v>
+        <v>0.2960000038146973</v>
       </c>
       <c r="H108" t="n">
-        <v>32.2</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h83.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s19.jpg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>h83.jpeg</t>
+          <t>s19.jpg</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.583299994468689</v>
+        <v>0.1200999990105629</v>
       </c>
       <c r="E109" t="n">
-        <v>0.2976999878883362</v>
+        <v>0.5609999895095825</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1066000014543533</v>
+        <v>0.129600003361702</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1190000027418137</v>
+        <v>0.3736999928951263</v>
       </c>
       <c r="H109" t="n">
-        <v>71.40000000000001</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h56.jpg</t>
+          <t>c:\ML_Project\test\Sad\s80.jpeg</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>h56.jpg</t>
+          <t>s80.jpeg</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.7208999991416931</v>
+        <v>0.06219999864697456</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1483999937772751</v>
+        <v>0.5404999852180481</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05270000174641609</v>
+        <v>0.1290999948978424</v>
       </c>
       <c r="G110" t="n">
-        <v>0.1186000034213066</v>
+        <v>0.2845999896526337</v>
       </c>
       <c r="H110" t="n">
-        <v>81.8</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a80.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a117.jpeg</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>a80.jpeg</t>
+          <t>a117.jpeg</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3963,158 +3963,158 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.05279999971389771</v>
+        <v>0.0234999991953373</v>
       </c>
       <c r="E111" t="n">
-        <v>0.09260000288486481</v>
+        <v>0.3064000010490417</v>
       </c>
       <c r="F111" t="n">
-        <v>0.5806000232696533</v>
+        <v>0.3339999914169312</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3343999981880188</v>
+        <v>0.1958999931812286</v>
       </c>
       <c r="H111" t="n">
-        <v>34.4</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s19.jpg</t>
+          <t>c:\ML_Project\test\Happy\h17.jpg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>s19.jpg</t>
+          <t>h17.jpg</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.08910000324249268</v>
+        <v>0.906000018119812</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5688999891281128</v>
+        <v>0.02429999969899654</v>
       </c>
       <c r="F112" t="n">
-        <v>0.07989999651908875</v>
+        <v>0.03130000084638596</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2896000146865845</v>
+        <v>0.04390000179409981</v>
       </c>
       <c r="H112" t="n">
-        <v>35.3</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s80.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h9.jpg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>s80.jpeg</t>
+          <t>h9.jpg</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.03319999948143959</v>
+        <v>0.8754000067710876</v>
       </c>
       <c r="E113" t="n">
-        <v>0.5242000222206116</v>
+        <v>0.04580000042915344</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1005999967455864</v>
+        <v>0.05860000103712082</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3199000060558319</v>
+        <v>0.05889999866485596</v>
       </c>
       <c r="H113" t="n">
-        <v>31.9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a117.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f13.jpeg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>a117.jpeg</t>
+          <t>new_f13.jpeg</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.04960000142455101</v>
+        <v>0.1185000017285347</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2676999866962433</v>
+        <v>0.3946999907493591</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2259999960660934</v>
+        <v>0.1538999974727631</v>
       </c>
       <c r="G114" t="n">
-        <v>0.3531000018119812</v>
+        <v>0.4040000140666962</v>
       </c>
       <c r="H114" t="n">
-        <v>35.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h17.jpg</t>
+          <t>c:\ML_Project\test\Fear\f41.jpg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>h17.jpg</t>
+          <t>f41.jpg</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.8881999850273132</v>
+        <v>0.1732999980449677</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04549999907612801</v>
+        <v>0.2813999950885773</v>
       </c>
       <c r="F115" t="n">
-        <v>0.05660000070929527</v>
+        <v>0.1854999959468842</v>
       </c>
       <c r="G115" t="n">
-        <v>0.06629999727010727</v>
+        <v>0.474700003862381</v>
       </c>
       <c r="H115" t="n">
-        <v>92.7</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h9.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h6.jpg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>h9.jpg</t>
+          <t>new_h6.jpg</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4123,158 +4123,158 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.8902000188827515</v>
+        <v>0.8702999949455261</v>
       </c>
       <c r="E116" t="n">
-        <v>0.04540000110864639</v>
+        <v>0.02370000071823597</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05999999865889549</v>
+        <v>0.04690000042319298</v>
       </c>
       <c r="G116" t="n">
-        <v>0.03689999878406525</v>
+        <v>0.04080000147223473</v>
       </c>
       <c r="H116" t="n">
-        <v>92.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f13.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a7.jpg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>new_f13.jpeg</t>
+          <t>a7.jpg</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.04899999871850014</v>
+        <v>0.03720000013709068</v>
       </c>
       <c r="E117" t="n">
-        <v>0.5593000054359436</v>
+        <v>0.6366999745368958</v>
       </c>
       <c r="F117" t="n">
-        <v>0.07660000026226044</v>
+        <v>0.147599995136261</v>
       </c>
       <c r="G117" t="n">
-        <v>0.4575000107288361</v>
+        <v>0.1946000009775162</v>
       </c>
       <c r="H117" t="n">
-        <v>31.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f41.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h3.jpg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>f41.jpg</t>
+          <t>new_h3.jpg</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.09809999912977219</v>
+        <v>0.9399999976158142</v>
       </c>
       <c r="E118" t="n">
-        <v>0.08340000361204147</v>
+        <v>0.01169999968260527</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4307000041007996</v>
+        <v>0.01799999922513962</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4257999956607819</v>
+        <v>0.02050000056624413</v>
       </c>
       <c r="H118" t="n">
-        <v>38.7</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h6.jpg</t>
+          <t>c:\ML_Project\test\Sad\s38.jpeg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>new_h6.jpg</t>
+          <t>s38.jpeg</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.8784999847412109</v>
+        <v>0.2476000040769577</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0227000005543232</v>
+        <v>0.4848000109195709</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05950000137090683</v>
+        <v>0.07739999890327454</v>
       </c>
       <c r="G119" t="n">
-        <v>0.02859999984502792</v>
+        <v>0.1827999949455261</v>
       </c>
       <c r="H119" t="n">
-        <v>92.5</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a7.jpg</t>
+          <t>c:\ML_Project\test\Happy\h57.jpg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>a7.jpg</t>
+          <t>h57.jpg</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.04500000178813934</v>
+        <v>0.8263999819755554</v>
       </c>
       <c r="E120" t="n">
-        <v>0.503000020980835</v>
+        <v>0.05999999865889549</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2802999913692474</v>
+        <v>0.08179999887943268</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1422999948263168</v>
+        <v>0.07379999756813049</v>
       </c>
       <c r="H120" t="n">
-        <v>32.2</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h3.jpg</t>
+          <t>c:\ML_Project\test\Happy\h84.jpeg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>new_h3.jpg</t>
+          <t>h84.jpeg</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4283,222 +4283,222 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.8416000008583069</v>
+        <v>0.8130999803543091</v>
       </c>
       <c r="E121" t="n">
-        <v>0.08749999850988388</v>
+        <v>0.06239999830722809</v>
       </c>
       <c r="F121" t="n">
-        <v>0.04289999976754189</v>
+        <v>0.06319999694824219</v>
       </c>
       <c r="G121" t="n">
-        <v>0.05229999870061874</v>
+        <v>0.09229999780654907</v>
       </c>
       <c r="H121" t="n">
-        <v>89.8</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s38.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f34.jpg</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>s38.jpeg</t>
+          <t>f34.jpg</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.07859999686479568</v>
+        <v>0.1063999980688095</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7210000157356262</v>
+        <v>0.295199990272522</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0778999999165535</v>
+        <v>0.301800012588501</v>
       </c>
       <c r="G122" t="n">
-        <v>0.1186000034213066</v>
+        <v>0.3334999978542328</v>
       </c>
       <c r="H122" t="n">
-        <v>33.3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h57.jpg</t>
+          <t>c:\ML_Project\test\Angry\a48.jpeg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>h57.jpg</t>
+          <t>a48.jpeg</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.7947999835014343</v>
+        <v>0.07429999858140945</v>
       </c>
       <c r="E123" t="n">
-        <v>0.04280000180006027</v>
+        <v>0.1738000065088272</v>
       </c>
       <c r="F123" t="n">
-        <v>0.08349999785423279</v>
+        <v>0.5055999755859375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.04069999977946281</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="H123" t="n">
-        <v>87.40000000000001</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h84.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s17.jpg</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>h84.jpeg</t>
+          <t>new_s17.jpg</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.6765999794006348</v>
+        <v>0.1977999955415726</v>
       </c>
       <c r="E124" t="n">
-        <v>0.1766999959945679</v>
+        <v>0.2151000052690506</v>
       </c>
       <c r="F124" t="n">
-        <v>0.04199999943375587</v>
+        <v>0.3357999920845032</v>
       </c>
       <c r="G124" t="n">
-        <v>0.1807000041007996</v>
+        <v>0.3609000146389008</v>
       </c>
       <c r="H124" t="n">
-        <v>78.7</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f34.jpg</t>
+          <t>c:\ML_Project\test\Sad\s5.jpg</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>f34.jpg</t>
+          <t>s5.jpg</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0544000007212162</v>
+        <v>0.8626999855041504</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1645999997854233</v>
+        <v>0.03030000068247318</v>
       </c>
       <c r="F125" t="n">
-        <v>0.08649999648332596</v>
+        <v>0.04470000043511391</v>
       </c>
       <c r="G125" t="n">
-        <v>0.7351999878883362</v>
+        <v>0.05330000072717667</v>
       </c>
       <c r="H125" t="n">
-        <v>36.4</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a48.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f45.jpg</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>a48.jpeg</t>
+          <t>f45.jpg</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.09669999778270721</v>
+        <v>0.07729999721050262</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1516000032424927</v>
+        <v>0.4490000009536743</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6665999889373779</v>
+        <v>0.1753000020980835</v>
       </c>
       <c r="G126" t="n">
-        <v>0.1552000045776367</v>
+        <v>0.3111999928951263</v>
       </c>
       <c r="H126" t="n">
-        <v>36.6</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_s17.jpg</t>
+          <t>c:\ML_Project\test\Fear\new_f40.jpeg</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>new_s17.jpg</t>
+          <t>new_f40.jpeg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.1606999933719635</v>
+        <v>0.06179999932646751</v>
       </c>
       <c r="E127" t="n">
-        <v>0.1722999960184097</v>
+        <v>0.2529000043869019</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2964999973773956</v>
+        <v>0.1379999965429306</v>
       </c>
       <c r="G127" t="n">
-        <v>0.4778999984264374</v>
+        <v>0.4990000128746033</v>
       </c>
       <c r="H127" t="n">
-        <v>42.4</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s5.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s15.jpg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>s5.jpg</t>
+          <t>new_s15.jpg</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4507,30 +4507,30 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.7389000058174133</v>
+        <v>0.06190000101923943</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1233000010251999</v>
+        <v>0.4916999936103821</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1080000028014183</v>
+        <v>0.2180999964475632</v>
       </c>
       <c r="G128" t="n">
-        <v>0.05260000005364418</v>
+        <v>0.2788000106811523</v>
       </c>
       <c r="H128" t="n">
-        <v>83.09999999999999</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f45.jpg</t>
+          <t>c:\ML_Project\test\Fear\f88.jpeg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>f45.jpg</t>
+          <t>f88.jpeg</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.07680000364780426</v>
+        <v>0.0438000001013279</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3616000115871429</v>
+        <v>0.7002000212669373</v>
       </c>
       <c r="F129" t="n">
-        <v>0.07479999959468842</v>
+        <v>0.05829999968409538</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5564000010490417</v>
+        <v>0.2348999977111816</v>
       </c>
       <c r="H129" t="n">
-        <v>36</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a83.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f58.jpeg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>a83.jpeg</t>
+          <t>f58.jpeg</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.03739999979734421</v>
+        <v>0.09740000218153</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3700000047683716</v>
+        <v>0.2520999908447266</v>
       </c>
       <c r="F130" t="n">
-        <v>0.07760000228881836</v>
+        <v>0.0714000016450882</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4643000066280365</v>
+        <v>0.5340999960899353</v>
       </c>
       <c r="H130" t="n">
-        <v>34.1</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f40.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f105.jpeg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>new_f40.jpeg</t>
+          <t>f105.jpeg</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4603,62 +4603,62 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.05999999865889549</v>
+        <v>0.2148000001907349</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4435999989509583</v>
+        <v>0.3411000072956085</v>
       </c>
       <c r="F131" t="n">
-        <v>0.09470000118017197</v>
+        <v>0.3461999893188477</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5253999829292297</v>
+        <v>0.4040000140666962</v>
       </c>
       <c r="H131" t="n">
-        <v>33.3</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_s15.jpg</t>
+          <t>c:\ML_Project\test\Angry\a111.jpeg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>new_s15.jpg</t>
+          <t>a111.jpeg</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.03660000115633011</v>
+        <v>0.04210000112652779</v>
       </c>
       <c r="E132" t="n">
-        <v>0.5841000080108643</v>
+        <v>0.652400016784668</v>
       </c>
       <c r="F132" t="n">
-        <v>0.07410000264644623</v>
+        <v>0.1999000012874603</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3815000057220459</v>
+        <v>0.1387999951839447</v>
       </c>
       <c r="H132" t="n">
-        <v>30.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f88.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f14.jpeg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>f88.jpeg</t>
+          <t>f14.jpeg</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4667,350 +4667,350 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.05480000004172325</v>
+        <v>0.09290000051259995</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5254999995231628</v>
+        <v>0.3614999949932098</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0786999985575676</v>
+        <v>0.1944999992847443</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4137000143527985</v>
+        <v>0.4560000002384186</v>
       </c>
       <c r="H133" t="n">
-        <v>32.7</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f58.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a69.jpg</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>f58.jpeg</t>
+          <t>a69.jpg</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.05480000004172325</v>
+        <v>0.05939999967813492</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3856000006198883</v>
+        <v>0.2578000128269196</v>
       </c>
       <c r="F134" t="n">
-        <v>0.05950000137090683</v>
+        <v>0.441100001335144</v>
       </c>
       <c r="G134" t="n">
-        <v>0.5812000036239624</v>
+        <v>0.2849000096321106</v>
       </c>
       <c r="H134" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f105.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h5.jpg</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>f105.jpeg</t>
+          <t>h5.jpg</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.04170000180602074</v>
+        <v>0.8597000241279602</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1497000008821487</v>
+        <v>0.05299999937415123</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2696999907493591</v>
+        <v>0.05420000106096268</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3621000051498413</v>
+        <v>0.06880000233650208</v>
       </c>
       <c r="H135" t="n">
-        <v>36.9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a111.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h20.jpg</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>a111.jpeg</t>
+          <t>h20.jpg</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.03869999945163727</v>
+        <v>0.8580999970436096</v>
       </c>
       <c r="E136" t="n">
-        <v>0.595300018787384</v>
+        <v>0.04650000110268593</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1642999947071075</v>
+        <v>0.05240000039339066</v>
       </c>
       <c r="G136" t="n">
-        <v>0.09269999712705612</v>
+        <v>0.06129999831318855</v>
       </c>
       <c r="H136" t="n">
-        <v>32.2</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f14.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s34.webp</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>f14.jpeg</t>
+          <t>s34.webp</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.05750000104308128</v>
+        <v>0.08760000020265579</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3980999886989594</v>
+        <v>0.6557999849319458</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1687999963760376</v>
+        <v>0.1612000018358231</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4205999970436096</v>
+        <v>0.1815000027418137</v>
       </c>
       <c r="H137" t="n">
-        <v>34</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a69.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h39.jpg</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>a69.jpg</t>
+          <t>new_h39.jpg</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.7325999736785889</v>
       </c>
       <c r="E138" t="n">
-        <v>0.08990000188350677</v>
+        <v>0.09440000355243683</v>
       </c>
       <c r="F138" t="n">
-        <v>0.198400005698204</v>
+        <v>0.1326999962329865</v>
       </c>
       <c r="G138" t="n">
-        <v>0.6617000102996826</v>
+        <v>0.1036000028252602</v>
       </c>
       <c r="H138" t="n">
-        <v>36.1</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h5.jpg</t>
+          <t>c:\ML_Project\test\Fear\new_f50.jpeg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>h5.jpg</t>
+          <t>new_f50.jpeg</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.8237000107765198</v>
+        <v>0.1517000049352646</v>
       </c>
       <c r="E139" t="n">
-        <v>0.08749999850988388</v>
+        <v>0.548799991607666</v>
       </c>
       <c r="F139" t="n">
-        <v>0.06689999997615814</v>
+        <v>0.1537999957799911</v>
       </c>
       <c r="G139" t="n">
-        <v>0.06459999829530716</v>
+        <v>0.2098000049591064</v>
       </c>
       <c r="H139" t="n">
-        <v>88.59999999999999</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h20.jpg</t>
+          <t>c:\ML_Project\test\Fear\f101.jpeg</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>h20.jpg</t>
+          <t>f101.jpeg</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.9524000287055969</v>
+        <v>0.1145000010728836</v>
       </c>
       <c r="E140" t="n">
-        <v>0.02219999954104424</v>
+        <v>0.3495999872684479</v>
       </c>
       <c r="F140" t="n">
-        <v>0.02480000071227551</v>
+        <v>0.4496000111103058</v>
       </c>
       <c r="G140" t="n">
-        <v>0.03810000047087669</v>
+        <v>0.2678000032901764</v>
       </c>
       <c r="H140" t="n">
-        <v>96.90000000000001</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s34.webp</t>
+          <t>c:\ML_Project\test\Happy\new_h49.jpg</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>s34.webp</t>
+          <t>new_h49.jpg</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.06629999727010727</v>
+        <v>0.8903999924659729</v>
       </c>
       <c r="E141" t="n">
-        <v>0.7685999870300293</v>
+        <v>0.02380000054836273</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1221999973058701</v>
+        <v>0.03220000118017197</v>
       </c>
       <c r="G141" t="n">
-        <v>0.09279999881982803</v>
+        <v>0.0430000014603138</v>
       </c>
       <c r="H141" t="n">
-        <v>31.2</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h39.jpg</t>
+          <t>c:\ML_Project\test\Angry\a6.jpg</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>new_h39.jpg</t>
+          <t>a6.jpg</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.8615000247955322</v>
+        <v>0.04610000178217888</v>
       </c>
       <c r="E142" t="n">
-        <v>0.08619999885559082</v>
+        <v>0.08529999852180481</v>
       </c>
       <c r="F142" t="n">
-        <v>0.04980000108480453</v>
+        <v>0.3610999882221222</v>
       </c>
       <c r="G142" t="n">
-        <v>0.06970000267028809</v>
+        <v>0.3982000052928925</v>
       </c>
       <c r="H142" t="n">
-        <v>90.90000000000001</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f50.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s55.jpeg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>new_f50.jpeg</t>
+          <t>s55.jpeg</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.3494000136852264</v>
+        <v>0.04369999840855598</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2944000065326691</v>
+        <v>0.7265999913215637</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1870999932289124</v>
+        <v>0.05590000003576279</v>
       </c>
       <c r="G143" t="n">
-        <v>0.07670000195503235</v>
+        <v>0.2017000019550323</v>
       </c>
       <c r="H143" t="n">
-        <v>56.7</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f101.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f53.jpeg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>f101.jpeg</t>
+          <t>new_f53.jpeg</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5019,30 +5019,30 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.03819999843835831</v>
+        <v>0.2590000033378601</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5080999732017517</v>
+        <v>0.1816000044345856</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2187000066041946</v>
+        <v>0.2786000072956085</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1756000071763992</v>
+        <v>0.3325000107288361</v>
       </c>
       <c r="H144" t="n">
-        <v>32.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f77.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f118.webp</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>f77.jpeg</t>
+          <t>f118.webp</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5051,254 +5051,254 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.07900000363588333</v>
+        <v>0.5299000144004822</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5236999988555908</v>
+        <v>0.1946000009775162</v>
       </c>
       <c r="F145" t="n">
-        <v>0.3833999931812286</v>
+        <v>0.2527999877929688</v>
       </c>
       <c r="G145" t="n">
-        <v>0.07760000228881836</v>
+        <v>0.2305999994277954</v>
       </c>
       <c r="H145" t="n">
-        <v>33.1</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h49.jpg</t>
+          <t>c:\ML_Project\test\Fear\f47.jpg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>new_h49.jpg</t>
+          <t>f47.jpg</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.8288000226020813</v>
+        <v>0.07660000026226044</v>
       </c>
       <c r="E146" t="n">
-        <v>0.07530000060796738</v>
+        <v>0.3506999909877777</v>
       </c>
       <c r="F146" t="n">
-        <v>0.1071999967098236</v>
+        <v>0.225600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>0.08049999922513962</v>
+        <v>0.417600005865097</v>
       </c>
       <c r="H146" t="n">
-        <v>88.59999999999999</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a6.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_download (6).jpeg</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>a6.jpg</t>
+          <t>new_download (6).jpeg</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.04349999874830246</v>
+        <v>0.02449999935925007</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1703000068664551</v>
+        <v>0.6972000002861023</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2316000014543533</v>
+        <v>0.03970000147819519</v>
       </c>
       <c r="G147" t="n">
-        <v>0.5802000164985657</v>
+        <v>0.2303999960422516</v>
       </c>
       <c r="H147" t="n">
-        <v>35</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s55.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a99.jpeg</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>s55.jpeg</t>
+          <t>a99.jpeg</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.066600002348423</v>
+        <v>0.1571999937295914</v>
       </c>
       <c r="E148" t="n">
-        <v>0.558899998664856</v>
+        <v>0.1542000025510788</v>
       </c>
       <c r="F148" t="n">
-        <v>0.1211000010371208</v>
+        <v>0.4738999903202057</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2861000001430511</v>
+        <v>0.3185999989509583</v>
       </c>
       <c r="H148" t="n">
-        <v>33.4</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f45.jpg</t>
+          <t>c:\ML_Project\test\Angry\a98.jpeg</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>f45.jpg</t>
+          <t>a98.jpeg</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.07680000364780426</v>
+        <v>0.08550000190734863</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3616000115871429</v>
+        <v>0.1642999947071075</v>
       </c>
       <c r="F149" t="n">
-        <v>0.07479999959468842</v>
+        <v>0.5044000148773193</v>
       </c>
       <c r="G149" t="n">
-        <v>0.5564000010490417</v>
+        <v>0.2596000134944916</v>
       </c>
       <c r="H149" t="n">
-        <v>36</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f53.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h2.jpg</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>new_f53.jpeg</t>
+          <t>h2.jpg</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.2876999974250793</v>
+        <v>0.8852999806404114</v>
       </c>
       <c r="E150" t="n">
-        <v>0.1420000046491623</v>
+        <v>0.02740000002086163</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2815999984741211</v>
+        <v>0.03469999879598618</v>
       </c>
       <c r="G150" t="n">
-        <v>0.2122000008821487</v>
+        <v>0.04270000010728836</v>
       </c>
       <c r="H150" t="n">
-        <v>53.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f118.webp</t>
+          <t>c:\ML_Project\test\Angry\a70.jpeg</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>f118.webp</t>
+          <t>a70.jpeg</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.1072999984025955</v>
+        <v>0.04360000044107437</v>
       </c>
       <c r="E151" t="n">
-        <v>0.153099998831749</v>
+        <v>0.2644000053405762</v>
       </c>
       <c r="F151" t="n">
-        <v>0.1182999983429909</v>
+        <v>0.5174999833106995</v>
       </c>
       <c r="G151" t="n">
-        <v>0.5745999813079834</v>
+        <v>0.1818999946117401</v>
       </c>
       <c r="H151" t="n">
-        <v>41</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f47.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_h24.jpg</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>f47.jpg</t>
+          <t>new_h24.jpg</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.04280000180006027</v>
+        <v>0.8443999886512756</v>
       </c>
       <c r="E152" t="n">
-        <v>0.4891999959945679</v>
+        <v>0.04589999839663506</v>
       </c>
       <c r="F152" t="n">
-        <v>0.1400000005960464</v>
+        <v>0.02300000004470348</v>
       </c>
       <c r="G152" t="n">
-        <v>0.3433000147342682</v>
+        <v>0.06230000033974648</v>
       </c>
       <c r="H152" t="n">
-        <v>32.4</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_download (6).jpeg</t>
+          <t>c:\ML_Project\test\Sad\s9.jpg</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>new_download (6).jpeg</t>
+          <t>s9.jpg</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5307,30 +5307,30 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.06750000268220901</v>
+        <v>0.05290000140666962</v>
       </c>
       <c r="E153" t="n">
-        <v>0.6470999717712402</v>
+        <v>0.6040999889373779</v>
       </c>
       <c r="F153" t="n">
-        <v>0.09529999643564224</v>
+        <v>0.1270000040531158</v>
       </c>
       <c r="G153" t="n">
-        <v>0.2458000034093857</v>
+        <v>0.2117999941110611</v>
       </c>
       <c r="H153" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a99.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a118.jpeg</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>a99.jpeg</t>
+          <t>a118.jpeg</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5339,30 +5339,30 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.08240000158548355</v>
+        <v>0.03359999880194664</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1410000026226044</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="F154" t="n">
-        <v>0.707099974155426</v>
+        <v>0.4528999924659729</v>
       </c>
       <c r="G154" t="n">
-        <v>0.1397999972105026</v>
+        <v>0.3240000009536743</v>
       </c>
       <c r="H154" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a98.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a47.jpg</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>a98.jpeg</t>
+          <t>a47.jpg</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5371,94 +5371,94 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.1101000010967255</v>
+        <v>0.08139999955892563</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2058999985456467</v>
+        <v>0.1185000017285347</v>
       </c>
       <c r="F155" t="n">
-        <v>0.5346999764442444</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="G155" t="n">
-        <v>0.1829999983310699</v>
+        <v>0.192100003361702</v>
       </c>
       <c r="H155" t="n">
-        <v>38</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h2.jpg</t>
+          <t>c:\ML_Project\test\Fear\f57.jpg</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>h2.jpg</t>
+          <t>f57.jpg</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.852400004863739</v>
+        <v>0.1066000014543533</v>
       </c>
       <c r="E156" t="n">
-        <v>0.05059999972581863</v>
+        <v>0.148499995470047</v>
       </c>
       <c r="F156" t="n">
-        <v>0.06239999830722809</v>
+        <v>0.4787000119686127</v>
       </c>
       <c r="G156" t="n">
-        <v>0.05959999933838844</v>
+        <v>0.2628999948501587</v>
       </c>
       <c r="H156" t="n">
-        <v>90.59999999999999</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a70.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f15.jpeg</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>a70.jpeg</t>
+          <t>f15.jpeg</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.04509999975562096</v>
+        <v>0.0414000004529953</v>
       </c>
       <c r="E157" t="n">
-        <v>0.4532000124454498</v>
+        <v>0.6305999755859375</v>
       </c>
       <c r="F157" t="n">
-        <v>0.3436000049114227</v>
+        <v>0.07940000295639038</v>
       </c>
       <c r="G157" t="n">
-        <v>0.1629000008106232</v>
+        <v>0.250900000333786</v>
       </c>
       <c r="H157" t="n">
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h24.jpg</t>
+          <t>c:\ML_Project\test\Happy\h14.jpg</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>new_h24.jpg</t>
+          <t>h14.jpg</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5467,254 +5467,254 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.7696999907493591</v>
+        <v>0.5616999864578247</v>
       </c>
       <c r="E158" t="n">
-        <v>0.133200004696846</v>
+        <v>0.227400004863739</v>
       </c>
       <c r="F158" t="n">
-        <v>0.02730000019073486</v>
+        <v>0.1512999981641769</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1064999997615814</v>
+        <v>0.1525000035762787</v>
       </c>
       <c r="H158" t="n">
-        <v>85.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s9.jpg</t>
+          <t>c:\ML_Project\test\Angry\new_a10.jpeg</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>s9.jpg</t>
+          <t>new_a10.jpeg</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.1048000007867813</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="E159" t="n">
-        <v>0.4476000070571899</v>
+        <v>0.1824000030755997</v>
       </c>
       <c r="F159" t="n">
-        <v>0.1262000054121017</v>
+        <v>0.4593000113964081</v>
       </c>
       <c r="G159" t="n">
-        <v>0.3310999870300293</v>
+        <v>0.3883999884128571</v>
       </c>
       <c r="H159" t="n">
-        <v>37.5</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a118.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s46.jpeg</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>a118.jpeg</t>
+          <t>s46.jpeg</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.03810000047087669</v>
+        <v>0.03680000081658363</v>
       </c>
       <c r="E160" t="n">
-        <v>0.06210000067949295</v>
+        <v>0.8091999888420105</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8525999784469604</v>
+        <v>0.066600002348423</v>
       </c>
       <c r="G160" t="n">
-        <v>0.06480000168085098</v>
+        <v>0.1462000012397766</v>
       </c>
       <c r="H160" t="n">
-        <v>32.8</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a47.jpg</t>
+          <t>c:\ML_Project\test\Happy\h98.jpeg</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>a47.jpg</t>
+          <t>h98.jpeg</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.0544000007212162</v>
+        <v>0.6434000134468079</v>
       </c>
       <c r="E161" t="n">
-        <v>0.09189999848604202</v>
+        <v>0.123199999332428</v>
       </c>
       <c r="F161" t="n">
-        <v>0.7942000031471252</v>
+        <v>0.08169999718666077</v>
       </c>
       <c r="G161" t="n">
-        <v>0.1186999976634979</v>
+        <v>0.1128000020980835</v>
       </c>
       <c r="H161" t="n">
-        <v>33.5</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f57.jpg</t>
+          <t>c:\ML_Project\test\Happy\h99.jpeg</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>f57.jpg</t>
+          <t>h99.jpeg</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.05889999866485596</v>
+        <v>0.7603999972343445</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1195999979972839</v>
+        <v>0.06750000268220901</v>
       </c>
       <c r="F162" t="n">
-        <v>0.6365000009536743</v>
+        <v>0.03599999845027924</v>
       </c>
       <c r="G162" t="n">
-        <v>0.2090000063180923</v>
+        <v>0.1027999967336655</v>
       </c>
       <c r="H162" t="n">
-        <v>34.7</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f2.jpg</t>
+          <t>c:\ML_Project\test\Sad\s89.jpeg</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>f2.jpg</t>
+          <t>s89.jpeg</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.05180000141263008</v>
+        <v>0.0127999996766448</v>
       </c>
       <c r="E163" t="n">
-        <v>0.4185999929904938</v>
+        <v>0.8043000102043152</v>
       </c>
       <c r="F163" t="n">
-        <v>0.266400009393692</v>
+        <v>0.0421999990940094</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1413999944925308</v>
+        <v>0.117299996316433</v>
       </c>
       <c r="H163" t="n">
-        <v>34.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f15.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s55.jpg</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>f15.jpeg</t>
+          <t>s55.jpg</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.03770000115036964</v>
+        <v>0.07940000295639038</v>
       </c>
       <c r="E164" t="n">
-        <v>0.7146000266075134</v>
+        <v>0.6089000105857849</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1324999928474426</v>
+        <v>0.2008000016212463</v>
       </c>
       <c r="G164" t="n">
-        <v>0.1333999931812286</v>
+        <v>0.2504000067710876</v>
       </c>
       <c r="H164" t="n">
-        <v>29.9</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h14.jpg</t>
+          <t>c:\ML_Project\test\Fear\new_f1.jpeg</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>h14.jpg</t>
+          <t>new_f1.jpeg</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.2806999981403351</v>
+        <v>0.1412000060081482</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4797999858856201</v>
+        <v>0.3061999976634979</v>
       </c>
       <c r="F165" t="n">
-        <v>0.07639999687671661</v>
+        <v>0.2125000059604645</v>
       </c>
       <c r="G165" t="n">
-        <v>0.1456999927759171</v>
+        <v>0.4415000081062317</v>
       </c>
       <c r="H165" t="n">
-        <v>50.3</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\new_a10.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a42.jpg</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>new_a10.jpeg</t>
+          <t>a42.jpg</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5723,158 +5723,158 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.08489999920129776</v>
+        <v>0.05319999903440475</v>
       </c>
       <c r="E166" t="n">
-        <v>0.2610999941825867</v>
+        <v>0.1552000045776367</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1435000002384186</v>
+        <v>0.4621999859809875</v>
       </c>
       <c r="G166" t="n">
-        <v>0.6086000204086304</v>
+        <v>0.2966000139713287</v>
       </c>
       <c r="H166" t="n">
-        <v>36.9</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h84.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f5.jpg</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>h84.jpeg</t>
+          <t>f5.jpg</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.6765999794006348</v>
+        <v>0.1429000049829483</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1766999959945679</v>
+        <v>0.2915000021457672</v>
       </c>
       <c r="F167" t="n">
-        <v>0.04199999943375587</v>
+        <v>0.4124000072479248</v>
       </c>
       <c r="G167" t="n">
-        <v>0.1807000041007996</v>
+        <v>0.3147000074386597</v>
       </c>
       <c r="H167" t="n">
-        <v>78.7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s46.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a78.jpg</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>s46.jpeg</t>
+          <t>a78.jpg</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.0771000012755394</v>
+        <v>0.08550000190734863</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7297000288963318</v>
+        <v>0.1449999958276749</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1005999967455864</v>
+        <v>0.5626999735832214</v>
       </c>
       <c r="G168" t="n">
-        <v>0.1357000023126602</v>
+        <v>0.2168000042438507</v>
       </c>
       <c r="H168" t="n">
-        <v>32.6</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h98.jpeg</t>
+          <t>c:\ML_Project\test\Fear\new_f36.jpeg</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>h98.jpeg</t>
+          <t>new_f36.jpeg</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.2635999917984009</v>
+        <v>0.07660000026226044</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2232999950647354</v>
+        <v>0.2750999927520752</v>
       </c>
       <c r="F169" t="n">
-        <v>0.3030999898910522</v>
+        <v>0.1615999937057495</v>
       </c>
       <c r="G169" t="n">
-        <v>0.213699996471405</v>
+        <v>0.5422999858856201</v>
       </c>
       <c r="H169" t="n">
-        <v>50.1</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h14.jpg</t>
+          <t>c:\ML_Project\test\Fear\f51.jpg</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>h14.jpg</t>
+          <t>f51.jpg</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.2806999981403351</v>
+        <v>0.07109999656677246</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4797999858856201</v>
+        <v>0.1739999949932098</v>
       </c>
       <c r="F170" t="n">
-        <v>0.07639999687671661</v>
+        <v>0.1439000070095062</v>
       </c>
       <c r="G170" t="n">
-        <v>0.1456999927759171</v>
+        <v>0.6017000079154968</v>
       </c>
       <c r="H170" t="n">
-        <v>50.3</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h99.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h68.jpg</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>h99.jpeg</t>
+          <t>h68.jpg</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5883,30 +5883,30 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.7896000146865845</v>
+        <v>0.8823999762535095</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1351000070571899</v>
+        <v>0.0390000008046627</v>
       </c>
       <c r="F171" t="n">
-        <v>0.01460000034421682</v>
+        <v>0.05319999903440475</v>
       </c>
       <c r="G171" t="n">
-        <v>0.07590000331401825</v>
+        <v>0.0511000007390976</v>
       </c>
       <c r="H171" t="n">
-        <v>86.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s89.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s79.jpeg</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>s89.jpeg</t>
+          <t>s79.jpeg</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5915,62 +5915,62 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.03950000181794167</v>
       </c>
       <c r="E172" t="n">
-        <v>0.7511000037193298</v>
+        <v>0.1026000007987022</v>
       </c>
       <c r="F172" t="n">
-        <v>0.03660000115633011</v>
+        <v>0.07779999822378159</v>
       </c>
       <c r="G172" t="n">
-        <v>0.2971999943256378</v>
+        <v>0.6310999989509583</v>
       </c>
       <c r="H172" t="n">
-        <v>29.1</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s55.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_images (54).jpg</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>s55.jpg</t>
+          <t>new_images (54).jpg</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.05629999935626984</v>
+        <v>0.854200005531311</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3935999870300293</v>
+        <v>0.0535999983549118</v>
       </c>
       <c r="F173" t="n">
-        <v>0.296099990606308</v>
+        <v>0.04890000075101852</v>
       </c>
       <c r="G173" t="n">
-        <v>0.1790000051259995</v>
+        <v>0.0771000012755394</v>
       </c>
       <c r="H173" t="n">
-        <v>34.5</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f1.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f36.jpg</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>new_f1.jpeg</t>
+          <t>f36.jpg</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5979,30 +5979,30 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.1386999934911728</v>
+        <v>0.03510000184178352</v>
       </c>
       <c r="E174" t="n">
-        <v>0.347900003194809</v>
+        <v>0.2353000044822693</v>
       </c>
       <c r="F174" t="n">
-        <v>0.2342000007629395</v>
+        <v>0.05640000104904175</v>
       </c>
       <c r="G174" t="n">
-        <v>0.3280999958515167</v>
+        <v>0.5449000000953674</v>
       </c>
       <c r="H174" t="n">
-        <v>40</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a42.jpg</t>
+          <t>c:\ML_Project\test\Angry\new_a51.jpeg</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>a42.jpg</t>
+          <t>new_a51.jpeg</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6011,94 +6011,94 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.06270000338554382</v>
+        <v>0.09340000152587891</v>
       </c>
       <c r="E175" t="n">
-        <v>0.150299996137619</v>
+        <v>0.1677999943494797</v>
       </c>
       <c r="F175" t="n">
-        <v>0.5315999984741211</v>
+        <v>0.2879999876022339</v>
       </c>
       <c r="G175" t="n">
-        <v>0.2313999980688095</v>
+        <v>0.4494999945163727</v>
       </c>
       <c r="H175" t="n">
-        <v>35.7</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f5.jpg</t>
+          <t>c:\ML_Project\test\Sad\new_klk.jpeg</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>f5.jpg</t>
+          <t>new_klk.jpeg</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.09549999982118607</v>
+        <v>0.0982000008225441</v>
       </c>
       <c r="E176" t="n">
-        <v>0.1291999965906143</v>
+        <v>0.3878999948501587</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7196999788284302</v>
+        <v>0.1169999986886978</v>
       </c>
       <c r="G176" t="n">
-        <v>0.1127000004053116</v>
+        <v>0.3312999904155731</v>
       </c>
       <c r="H176" t="n">
-        <v>36.6</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a78.jpg</t>
+          <t>c:\ML_Project\test\Happy\new_images (47).jpg</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>a78.jpg</t>
+          <t>new_images (47).jpg</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.0820000022649765</v>
+        <v>0.2784999907016754</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1260000020265579</v>
+        <v>0.3555999994277954</v>
       </c>
       <c r="F177" t="n">
-        <v>0.7580999732017517</v>
+        <v>0.1343999952077866</v>
       </c>
       <c r="G177" t="n">
-        <v>0.1133999973535538</v>
+        <v>0.1494999974966049</v>
       </c>
       <c r="H177" t="n">
-        <v>35.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_f36.jpeg</t>
+          <t>c:\ML_Project\test\Fear\f46.jpg</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>new_f36.jpeg</t>
+          <t>f46.jpg</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6107,158 +6107,158 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.08389999717473984</v>
+        <v>0.04569999873638153</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1676999926567078</v>
+        <v>0.1123000010848045</v>
       </c>
       <c r="F178" t="n">
-        <v>0.1257999986410141</v>
+        <v>0.2348999977111816</v>
       </c>
       <c r="G178" t="n">
-        <v>0.7566999793052673</v>
+        <v>0.5311999917030334</v>
       </c>
       <c r="H178" t="n">
-        <v>37.5</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f51.jpg</t>
+          <t>c:\ML_Project\test\Angry\a87.jpeg</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>f51.jpg</t>
+          <t>a87.jpeg</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.03220000118017197</v>
+        <v>0.0771000012755394</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3059999942779541</v>
+        <v>0.4828000068664551</v>
       </c>
       <c r="F179" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.328000009059906</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6960999965667725</v>
+        <v>0.1844999939203262</v>
       </c>
       <c r="H179" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h68.jpg</t>
+          <t>c:\ML_Project\test\Sad\s110.jpeg</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>h68.jpg</t>
+          <t>s110.jpeg</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.8896999955177307</v>
+        <v>0.09920000284910202</v>
       </c>
       <c r="E180" t="n">
-        <v>0.04500000178813934</v>
+        <v>0.3235999941825867</v>
       </c>
       <c r="F180" t="n">
-        <v>0.06319999694824219</v>
+        <v>0.3210000097751617</v>
       </c>
       <c r="G180" t="n">
-        <v>0.03889999911189079</v>
+        <v>0.3210000097751617</v>
       </c>
       <c r="H180" t="n">
-        <v>92.90000000000001</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s79.jpeg</t>
+          <t>c:\ML_Project\test\Happy\new_h47.jpg</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>s79.jpeg</t>
+          <t>new_h47.jpg</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.04149999842047691</v>
+        <v>0.8144999742507935</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1750999987125397</v>
+        <v>0.0640999972820282</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0535999983549118</v>
+        <v>0.06700000166893005</v>
       </c>
       <c r="G181" t="n">
-        <v>0.7768999934196472</v>
+        <v>0.1036999970674515</v>
       </c>
       <c r="H181" t="n">
-        <v>35.5</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_images (54).jpg</t>
+          <t>c:\ML_Project\test\Sad\new_s48.jpeg</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>new_images (54).jpg</t>
+          <t>new_s48.jpeg</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.8454999923706055</v>
+        <v>0.04349999874830246</v>
       </c>
       <c r="E182" t="n">
-        <v>0.09520000219345093</v>
+        <v>0.5501999855041504</v>
       </c>
       <c r="F182" t="n">
-        <v>0.05240000039339066</v>
+        <v>0.2694999873638153</v>
       </c>
       <c r="G182" t="n">
-        <v>0.05070000141859055</v>
+        <v>0.159400001168251</v>
       </c>
       <c r="H182" t="n">
-        <v>89.90000000000001</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f36.jpg</t>
+          <t>c:\ML_Project\test\Fear\new_images (1).jpeg</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>f36.jpg</t>
+          <t>new_images (1).jpeg</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6267,30 +6267,30 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.03559999912977219</v>
+        <v>0.1289999932050705</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1782000064849854</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="F183" t="n">
-        <v>0.04340000078082085</v>
+        <v>0.3201999962329865</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8396000266075134</v>
+        <v>0.4079000055789948</v>
       </c>
       <c r="H183" t="n">
-        <v>34.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\new_a51.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a22.jpg</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>new_a51.jpeg</t>
+          <t>a22.jpg</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6299,30 +6299,30 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.05490000173449516</v>
+        <v>0.1128999963402748</v>
       </c>
       <c r="E184" t="n">
-        <v>0.324999988079071</v>
+        <v>0.2506999969482422</v>
       </c>
       <c r="F184" t="n">
-        <v>0.2158000022172928</v>
+        <v>0.2585999965667725</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4320000112056732</v>
+        <v>0.4571999907493591</v>
       </c>
       <c r="H184" t="n">
-        <v>34.4</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_klk.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s103.jpeg</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>new_klk.jpeg</t>
+          <t>s103.jpeg</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6331,62 +6331,62 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.04439999908208847</v>
+        <v>0.07580000162124634</v>
       </c>
       <c r="E185" t="n">
-        <v>0.2838000059127808</v>
+        <v>0.3867000043392181</v>
       </c>
       <c r="F185" t="n">
-        <v>0.06960000097751617</v>
+        <v>0.1212000027298927</v>
       </c>
       <c r="G185" t="n">
-        <v>0.7164000272750854</v>
+        <v>0.4535999894142151</v>
       </c>
       <c r="H185" t="n">
-        <v>33.9</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_images (47).jpg</t>
+          <t>c:\ML_Project\test\Sad\s84.jpeg</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>new_images (47).jpg</t>
+          <t>s84.jpeg</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.158500000834465</v>
+        <v>0.2101999968290329</v>
       </c>
       <c r="E186" t="n">
-        <v>0.5375999808311462</v>
+        <v>0.4814999997615814</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1946000009775162</v>
+        <v>0.1200999990105629</v>
       </c>
       <c r="G186" t="n">
-        <v>0.09610000252723694</v>
+        <v>0.1982000023126602</v>
       </c>
       <c r="H186" t="n">
-        <v>40.5</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s32.jpg</t>
+          <t>c:\ML_Project\test\Sad\s81.jpeg</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>s32.jpg</t>
+          <t>s81.jpeg</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6395,62 +6395,62 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.04010000079870224</v>
+        <v>0.03119999915361404</v>
       </c>
       <c r="E187" t="n">
-        <v>0.6718000173568726</v>
+        <v>0.7085999846458435</v>
       </c>
       <c r="F187" t="n">
-        <v>0.06390000134706497</v>
+        <v>0.1076999977231026</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2685999870300293</v>
+        <v>0.1439000070095062</v>
       </c>
       <c r="H187" t="n">
-        <v>30.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\f46.jpg</t>
+          <t>c:\ML_Project\test\Sad\s77.jpeg</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>f46.jpg</t>
+          <t>s77.jpeg</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.06539999693632126</v>
+        <v>0.2180999964475632</v>
       </c>
       <c r="E188" t="n">
-        <v>0.08720000088214874</v>
+        <v>0.4595000147819519</v>
       </c>
       <c r="F188" t="n">
-        <v>0.2545999884605408</v>
+        <v>0.2500999867916107</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7627999782562256</v>
+        <v>0.2551999986171722</v>
       </c>
       <c r="H188" t="n">
-        <v>35.9</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a87.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a26.jpg</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>a87.jpeg</t>
+          <t>a26.jpg</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6459,62 +6459,62 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.04820000007748604</v>
+        <v>0.08479999750852585</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2583000063896179</v>
+        <v>0.1430000066757202</v>
       </c>
       <c r="F189" t="n">
-        <v>0.4663999974727631</v>
+        <v>0.58160001039505</v>
       </c>
       <c r="G189" t="n">
-        <v>0.1630000025033951</v>
+        <v>0.1855999976396561</v>
       </c>
       <c r="H189" t="n">
-        <v>34.3</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a7.jpg</t>
+          <t>c:\ML_Project\test\Sad\s50.jpg</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>a7.jpg</t>
+          <t>s50.jpg</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.04500000178813934</v>
+        <v>0.07999999821186066</v>
       </c>
       <c r="E190" t="n">
-        <v>0.503000020980835</v>
+        <v>0.3127000033855438</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2802999913692474</v>
+        <v>0.3402000069618225</v>
       </c>
       <c r="G190" t="n">
-        <v>0.1422999948263168</v>
+        <v>0.2387000024318695</v>
       </c>
       <c r="H190" t="n">
-        <v>32.2</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s110.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s50.jpeg</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>s110.jpeg</t>
+          <t>new_s50.jpeg</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6523,158 +6523,158 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.05869999900460243</v>
+        <v>0.3373000025749207</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3795000016689301</v>
+        <v>0.380299985408783</v>
       </c>
       <c r="F191" t="n">
-        <v>0.3346999883651733</v>
+        <v>0.1773000061511993</v>
       </c>
       <c r="G191" t="n">
-        <v>0.1333999931812286</v>
+        <v>0.1814000010490417</v>
       </c>
       <c r="H191" t="n">
-        <v>34.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h47.jpg</t>
+          <t>c:\ML_Project\test\Angry\a23.jpg</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>new_h47.jpg</t>
+          <t>a23.jpg</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.9316999912261963</v>
+        <v>0.123199999332428</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0421999990940094</v>
+        <v>0.2368000000715256</v>
       </c>
       <c r="F192" t="n">
-        <v>0.03099999949336052</v>
+        <v>0.4783999919891357</v>
       </c>
       <c r="G192" t="n">
-        <v>0.03759999945759773</v>
+        <v>0.3382999897003174</v>
       </c>
       <c r="H192" t="n">
-        <v>95.5</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_s48.jpeg</t>
+          <t>c:\ML_Project\test\Happy\new_h29.jpg</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>new_s48.jpeg</t>
+          <t>new_h29.jpg</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.06650000065565109</v>
+        <v>0.4627000093460083</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3420000076293945</v>
+        <v>0.3125999867916107</v>
       </c>
       <c r="F193" t="n">
-        <v>0.3251999914646149</v>
+        <v>0.181999996304512</v>
       </c>
       <c r="G193" t="n">
-        <v>0.1829999983310699</v>
+        <v>0.1924999952316284</v>
       </c>
       <c r="H193" t="n">
-        <v>35.6</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Fear\new_images (1).jpeg</t>
+          <t>c:\ML_Project\test\Angry\new_a38.jpeg</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>new_images (1).jpeg</t>
+          <t>new_a38.jpeg</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.05229999870061874</v>
+        <v>0.1449999958276749</v>
       </c>
       <c r="E194" t="n">
-        <v>0.4336999952793121</v>
+        <v>0.0333000011742115</v>
       </c>
       <c r="F194" t="n">
-        <v>0.185699999332428</v>
+        <v>0.5228999853134155</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3138999938964844</v>
+        <v>0.1111000031232834</v>
       </c>
       <c r="H194" t="n">
-        <v>33.7</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a22.jpg</t>
+          <t>c:\ML_Project\test\Sad\s83.jpeg</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>a22.jpg</t>
+          <t>s83.jpeg</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Sad</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.03350000083446503</v>
+        <v>0.1229000017046928</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1255999952554703</v>
+        <v>0.3420000076293945</v>
       </c>
       <c r="F195" t="n">
-        <v>0.59170001745224</v>
+        <v>0.03750000149011612</v>
       </c>
       <c r="G195" t="n">
-        <v>0.2076999992132187</v>
+        <v>0.3355000019073486</v>
       </c>
       <c r="H195" t="n">
-        <v>33.6</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s103.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s10.jpg</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>s103.jpeg</t>
+          <t>s10.jpg</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6683,62 +6683,62 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.06669999659061432</v>
+        <v>0.1685000061988831</v>
       </c>
       <c r="E196" t="n">
-        <v>0.4984999895095825</v>
+        <v>0.571399986743927</v>
       </c>
       <c r="F196" t="n">
-        <v>0.03299999982118607</v>
+        <v>0.1738000065088272</v>
       </c>
       <c r="G196" t="n">
-        <v>0.5533999800682068</v>
+        <v>0.1917999982833862</v>
       </c>
       <c r="H196" t="n">
-        <v>33.3</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\h83.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a79.jpg</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>h83.jpeg</t>
+          <t>a79.jpg</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.583299994468689</v>
+        <v>0.03830000013113022</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2976999878883362</v>
+        <v>0.0989999994635582</v>
       </c>
       <c r="F197" t="n">
-        <v>0.1066000014543533</v>
+        <v>0.7045999765396118</v>
       </c>
       <c r="G197" t="n">
-        <v>0.1190000027418137</v>
+        <v>0.1465999931097031</v>
       </c>
       <c r="H197" t="n">
-        <v>71.40000000000001</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s84.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s115.jpeg</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>s84.jpeg</t>
+          <t>s115.jpeg</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6747,30 +6747,30 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.048700001090765</v>
+        <v>0.04080000147223473</v>
       </c>
       <c r="E198" t="n">
-        <v>0.6980999708175659</v>
+        <v>0.7538999915122986</v>
       </c>
       <c r="F198" t="n">
-        <v>0.08370000123977661</v>
+        <v>0.09520000219345093</v>
       </c>
       <c r="G198" t="n">
-        <v>0.2124000042676926</v>
+        <v>0.150299996137619</v>
       </c>
       <c r="H198" t="n">
-        <v>30.8</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s81.jpeg</t>
+          <t>c:\ML_Project\test\Sad\s33.jpg</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>s81.jpeg</t>
+          <t>s33.jpg</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6779,126 +6779,126 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.02769999951124191</v>
+        <v>0.1752000004053116</v>
       </c>
       <c r="E199" t="n">
-        <v>0.7662000060081482</v>
+        <v>0.4230000078678131</v>
       </c>
       <c r="F199" t="n">
-        <v>0.03460000082850456</v>
+        <v>0.1832000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>0.1483000069856644</v>
+        <v>0.2477999925613403</v>
       </c>
       <c r="H199" t="n">
-        <v>29.5</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s77.jpeg</t>
+          <t>c:\ML_Project\test\Happy\h26.jpg</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>s77.jpeg</t>
+          <t>h26.jpg</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.1344999969005585</v>
+        <v>0.7736999988555908</v>
       </c>
       <c r="E200" t="n">
-        <v>0.2759999930858612</v>
+        <v>0.1015999987721443</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3327000141143799</v>
+        <v>0.05370000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>0.1492000073194504</v>
+        <v>0.08820000290870667</v>
       </c>
       <c r="H200" t="n">
-        <v>41.4</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a26.jpg</t>
+          <t>c:\ML_Project\test\Fear\new_f30.jpeg</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>a26.jpg</t>
+          <t>new_f30.jpeg</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.0786999985575676</v>
+        <v>0.09769999980926514</v>
       </c>
       <c r="E201" t="n">
-        <v>0.1076999977231026</v>
+        <v>0.2653000056743622</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7603999972343445</v>
+        <v>0.177499994635582</v>
       </c>
       <c r="G201" t="n">
-        <v>0.09830000251531601</v>
+        <v>0.5152000188827515</v>
       </c>
       <c r="H201" t="n">
-        <v>35.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s50.jpg</t>
+          <t>c:\ML_Project\test\Fear\f31.jpg</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>s50.jpg</t>
+          <t>f31.jpg</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.03480000048875809</v>
+        <v>0.07760000228881836</v>
       </c>
       <c r="E202" t="n">
-        <v>0.5401999950408936</v>
+        <v>0.3754999935626984</v>
       </c>
       <c r="F202" t="n">
-        <v>0.2547999918460846</v>
+        <v>0.4178999960422516</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1835999935865402</v>
+        <v>0.2508000135421753</v>
       </c>
       <c r="H202" t="n">
-        <v>30.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\new_s50.jpeg</t>
+          <t>c:\ML_Project\test\Sad\new_s6.jpg</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>new_s50.jpeg</t>
+          <t>new_s6.jpg</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6907,30 +6907,30 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.1309999972581863</v>
+        <v>0.08910000324249268</v>
       </c>
       <c r="E203" t="n">
-        <v>0.4417000114917755</v>
+        <v>0.4386000037193298</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1946000009775162</v>
+        <v>0.3964999914169312</v>
       </c>
       <c r="G203" t="n">
-        <v>0.2345999926328659</v>
+        <v>0.1612000018358231</v>
       </c>
       <c r="H203" t="n">
-        <v>39.2</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a23.jpg</t>
+          <t>c:\ML_Project\test\Angry\a37.jpg</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>a23.jpg</t>
+          <t>a37.jpg</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6939,30 +6939,30 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.04470000043511391</v>
+        <v>0.1463000029325485</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2397000044584274</v>
+        <v>0.3371999859809875</v>
       </c>
       <c r="F204" t="n">
-        <v>0.3055999875068665</v>
+        <v>0.2416999936103821</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4524999856948853</v>
+        <v>0.4009999930858612</v>
       </c>
       <c r="H204" t="n">
-        <v>33.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Happy\new_h29.jpg</t>
+          <t>c:\ML_Project\test\Happy\h91.jpeg</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>new_h29.jpg</t>
+          <t>h91.jpeg</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6971,30 +6971,30 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.5297999978065491</v>
+        <v>0.8267999887466431</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1164999976754189</v>
+        <v>0.07109999656677246</v>
       </c>
       <c r="F205" t="n">
-        <v>0.1459999978542328</v>
+        <v>0.07419999688863754</v>
       </c>
       <c r="G205" t="n">
-        <v>0.1685000061988831</v>
+        <v>0.09839999675750732</v>
       </c>
       <c r="H205" t="n">
-        <v>69.90000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\new_a38.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a71.jpeg</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>new_a38.jpeg</t>
+          <t>a71.jpeg</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7003,94 +7003,94 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.124600000679493</v>
+        <v>0.08500000089406967</v>
       </c>
       <c r="E206" t="n">
-        <v>0.06469999998807907</v>
+        <v>0.5472000241279602</v>
       </c>
       <c r="F206" t="n">
-        <v>0.7020000219345093</v>
+        <v>0.2216999977827072</v>
       </c>
       <c r="G206" t="n">
-        <v>0.1523000001907349</v>
+        <v>0.2585999965667725</v>
       </c>
       <c r="H206" t="n">
-        <v>39.5</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s83.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a50.jpg</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>s83.jpeg</t>
+          <t>a50.jpg</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.1437000036239624</v>
+        <v>0.07180000096559525</v>
       </c>
       <c r="E207" t="n">
-        <v>0.5530999898910522</v>
+        <v>0.3339999914169312</v>
       </c>
       <c r="F207" t="n">
-        <v>0.03229999914765358</v>
+        <v>0.4618000090122223</v>
       </c>
       <c r="G207" t="n">
-        <v>0.258899986743927</v>
+        <v>0.2087000012397766</v>
       </c>
       <c r="H207" t="n">
-        <v>40</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s10.jpg</t>
+          <t>c:\ML_Project\test\Angry\a51.jpg</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>s10.jpg</t>
+          <t>a51.jpg</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.07429999858140945</v>
+        <v>0.1639000028371811</v>
       </c>
       <c r="E208" t="n">
-        <v>0.7310000061988831</v>
+        <v>0.223800003528595</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1825000047683716</v>
+        <v>0.4711000025272369</v>
       </c>
       <c r="G208" t="n">
-        <v>0.08070000261068344</v>
+        <v>0.2790000140666962</v>
       </c>
       <c r="H208" t="n">
-        <v>31.7</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Angry\a79.jpg</t>
+          <t>c:\ML_Project\test\Angry\a100.jpeg</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>a79.jpg</t>
+          <t>a100.jpeg</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7099,62 +7099,62 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.08590000122785568</v>
+        <v>0.2967999875545502</v>
       </c>
       <c r="E209" t="n">
-        <v>0.06300000101327896</v>
+        <v>0.2500999867916107</v>
       </c>
       <c r="F209" t="n">
-        <v>0.6700000166893005</v>
+        <v>0.2392999976873398</v>
       </c>
       <c r="G209" t="n">
-        <v>0.1887000054121017</v>
+        <v>0.2696000039577484</v>
       </c>
       <c r="H209" t="n">
-        <v>37.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s115.jpeg</t>
+          <t>c:\ML_Project\test\Angry\a94.webp</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>s115.jpeg</t>
+          <t>a94.webp</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Angry</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.06289999932050705</v>
+        <v>0.1054000034928322</v>
       </c>
       <c r="E210" t="n">
-        <v>0.8294000029563904</v>
+        <v>0.2471999973058701</v>
       </c>
       <c r="F210" t="n">
-        <v>0.06759999692440033</v>
+        <v>0.39410001039505</v>
       </c>
       <c r="G210" t="n">
-        <v>0.1059999987483025</v>
+        <v>0.3671000003814697</v>
       </c>
       <c r="H210" t="n">
-        <v>30.5</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>c:\ML_Project\test\Sad\s33.jpg</t>
+          <t>c:\ML_Project\test\Sad\s45.jpeg</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>s33.jpg</t>
+          <t>s45.jpeg</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7163,403 +7163,19 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.0601000003516674</v>
+        <v>0.1158000007271767</v>
       </c>
       <c r="E211" t="n">
-        <v>0.7102000117301941</v>
+        <v>0.6008999943733215</v>
       </c>
       <c r="F211" t="n">
-        <v>0.1508000046014786</v>
+        <v>0.1074000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>0.1172000020742416</v>
+        <v>0.1221999973058701</v>
       </c>
       <c r="H211" t="n">
-        <v>31.3</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Happy\h26.jpg</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>h26.jpg</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Happy</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E212" t="n">
-        <v>0.1050999984145164</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0.02889999933540821</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0.05570000037550926</v>
-      </c>
-      <c r="H212" t="n">
-        <v>88.09999999999999</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Fear\new_f30.jpeg</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>new_f30.jpeg</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Fear</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>0.05370000004768372</v>
-      </c>
-      <c r="E213" t="n">
-        <v>0.2845999896526337</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0.1049000024795532</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0.5453000068664551</v>
-      </c>
-      <c r="H213" t="n">
-        <v>35.6</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Fear\f31.jpg</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>f31.jpg</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Fear</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>0.1011999994516373</v>
-      </c>
-      <c r="E214" t="n">
-        <v>0.3190999925136566</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.1156999990344048</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0.497299998998642</v>
-      </c>
-      <c r="H214" t="n">
-        <v>38.3</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Sad\new_s6.jpg</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>new_s6.jpg</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>0.1438000053167343</v>
-      </c>
-      <c r="E215" t="n">
-        <v>0.2922999858856201</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.4512999951839447</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0.09669999778270721</v>
-      </c>
-      <c r="H215" t="n">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Angry\a37.jpg</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>a37.jpg</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>0.05270000174641609</v>
-      </c>
-      <c r="E216" t="n">
-        <v>0.7075999975204468</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.151199996471405</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.1028999984264374</v>
-      </c>
-      <c r="H216" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Happy\h91.jpeg</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>h91.jpeg</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Happy</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>0.7836999893188477</v>
-      </c>
-      <c r="E217" t="n">
-        <v>0.05649999901652336</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.08299999684095383</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0.08039999753236771</v>
-      </c>
-      <c r="H217" t="n">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Angry\a71.jpeg</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>a71.jpeg</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>0.06120000034570694</v>
-      </c>
-      <c r="E218" t="n">
-        <v>0.4119000136852264</v>
-      </c>
-      <c r="F218" t="n">
-        <v>0.2233999967575073</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0.2072000056505203</v>
-      </c>
-      <c r="H218" t="n">
-        <v>35.2</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Angry\a50.jpg</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>a50.jpg</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>0.07599999755620956</v>
-      </c>
-      <c r="E219" t="n">
-        <v>0.1481000036001205</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0.6151999831199646</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0.1495999991893768</v>
-      </c>
-      <c r="H219" t="n">
-        <v>36.1</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Angry\a51.jpg</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>a51.jpg</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>0.178399994969368</v>
-      </c>
-      <c r="E220" t="n">
-        <v>0.2205000072717667</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0.3337000012397766</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0.1030000001192093</v>
-      </c>
-      <c r="H220" t="n">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Angry\a100.jpeg</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>a100.jpeg</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>0.3890999853610992</v>
-      </c>
-      <c r="E221" t="n">
-        <v>0.1710000038146973</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0.2795999944210052</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0.1221000030636787</v>
-      </c>
-      <c r="H221" t="n">
-        <v>59.6</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Angry\a94.webp</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>a94.webp</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>0.07150000333786011</v>
-      </c>
-      <c r="E222" t="n">
-        <v>0.1978999972343445</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.7408999800682068</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0.09319999814033508</v>
-      </c>
-      <c r="H222" t="n">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>c:\ML_Project\test\Sad\s45.jpeg</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>s45.jpeg</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>0.1488000005483627</v>
-      </c>
-      <c r="E223" t="n">
-        <v>0.5906999707221985</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.160400003194809</v>
-      </c>
-      <c r="G223" t="n">
-        <v>0.06629999727010727</v>
-      </c>
-      <c r="H223" t="n">
-        <v>39.6</v>
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>
